--- a/tasklist/habitable.xlsx
+++ b/tasklist/habitable.xlsx
@@ -3,12 +3,23 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <workbookPr/>
   <bookViews>
-    <workbookView xWindow="360" yWindow="15" windowWidth="20955" windowHeight="9720" activeTab="0"/>
+    <workbookView xWindow="360" yWindow="15" windowWidth="20955" windowHeight="9720" activeTab="11"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1 (3)" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Sheet1" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Sheet1 (2)" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="水星探査" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="水星ダイソン環" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="ケンタ" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="WH第1章：時空開孔の安定化" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="WH第2章：系外インフラ自動構築" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="WH第3章：銀河蓄電池の運用" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="WHエピローグ：距離の消滅" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="ダイソン環" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="量子comp" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="HZ創出" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="PAI+DNA" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="Sheet1 (2)" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet name="Sheet1" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet name="人類消滅" sheetId="14" state="visible" r:id="rId14"/>
   </sheets>
   <calcPr/>
   <extLst>
@@ -18,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="350" uniqueCount="350">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="827" uniqueCount="827">
   <si>
     <t>課題ID</t>
   </si>
@@ -44,6 +55,1965 @@
     <t>備考</t>
   </si>
   <si>
+    <t>MER-01</t>
+  </si>
+  <si>
+    <t>水星ダイソン環</t>
+  </si>
+  <si>
+    <t>着陸・基地</t>
+  </si>
+  <si>
+    <t>水星地表着陸モジュール設計</t>
+  </si>
+  <si>
+    <t xml:space="preserve">着陸質量M_lander[kg] 水星重力g_mercury[m/s²] 着陸速度v_land[m/s]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">M[kg] g[m/s²] v[m/s]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">着陸衝撃G_land[G] 必要燃料M_fuel[kg]</t>
+  </si>
+  <si>
+    <t>水星0.38Gに対応した着陸脚・逆噴射設計</t>
+  </si>
+  <si>
+    <t>MER-02</t>
+  </si>
+  <si>
+    <t>地表基地の与圧・防熱設計</t>
+  </si>
+  <si>
+    <t xml:space="preserve">外気温T_out[℃] 内部温度T_in[℃] 基地容積V_base[m³]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">T_out[℃] T_in[℃] V[m³]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">断熱材厚d_insul[m] 空調電力P_ac[W]</t>
+  </si>
+  <si>
+    <t>昼側+430℃、夜側-180℃の温度差に対応</t>
+  </si>
+  <si>
+    <t>MER-03</t>
+  </si>
+  <si>
+    <t>地表基地の放射線遮蔽設計</t>
+  </si>
+  <si>
+    <t xml:space="preserve">太陽フレア線量D_flare[Sv/回] 遮蔽材厚d_shield[cm] 遮蔽材密度ρ[kg/m³]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">D[Sv] d[cm] ρ[kg/m³]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">遮蔽後線量D_after[Sv] 遮蔽質量M_shield[kg]</t>
+  </si>
+  <si>
+    <t>水星は太陽に近くフレア被曝が大きい</t>
+  </si>
+  <si>
+    <t>MER-04</t>
+  </si>
+  <si>
+    <t>採掘</t>
+  </si>
+  <si>
+    <t>水星表土の採掘効率</t>
+  </si>
+  <si>
+    <t xml:space="preserve">採掘機能力R_dig[ton/hr] 稼働時間T_op[hr/日] 採掘可能面積A_mine[m²]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">R[ton/hr] T[hr] A[m²]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">年間採掘量M_year[ton/年] 採掘可能年数Y_mine[年]</t>
+  </si>
+  <si>
+    <t>表土レゴリスから鉄・シリコンを分離</t>
+  </si>
+  <si>
+    <t>MER-05</t>
+  </si>
+  <si>
+    <t>鉄・シリコン分離精錬プラント設計</t>
+  </si>
+  <si>
+    <t xml:space="preserve">鉱石処理量M_ore[ton/日] 鉄含有率R_iron[%] シリコン含有率R_silicon[%]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">M[ton/日] R_iron R_silicon</t>
+  </si>
+  <si>
+    <t xml:space="preserve">鉄生産量M_iron[ton/日] シリコン生産量M_silicon[ton/日] 所要電力P_smelt[MW]</t>
+  </si>
+  <si>
+    <t>太陽熱溶解＋電気分解のハイブリッド精錬</t>
+  </si>
+  <si>
+    <t>MER-06</t>
+  </si>
+  <si>
+    <t>水星資源からの水素・炭素抽出</t>
+  </si>
+  <si>
+    <t xml:space="preserve">水星表土中の水素濃度C_hydrogen[ppm] 炭素濃度C_carbon[ppm]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C_hydrogen C_carbon</t>
+  </si>
+  <si>
+    <t xml:space="preserve">年間抽出量M_H[ton/年] M_C[ton/年] 抽出コストC_extract[USD/ton]</t>
+  </si>
+  <si>
+    <t>太陽風由来の微量水素・炭素を回収。不足分は地球輸送</t>
+  </si>
+  <si>
+    <t>26.07.09</t>
+  </si>
+  <si>
+    <t>MER-07</t>
+  </si>
+  <si>
+    <t>製造</t>
+  </si>
+  <si>
+    <t>パネル製造工場の設計</t>
+  </si>
+  <si>
+    <t xml:space="preserve">パネル生産速度R_panel[m²/日] パネル厚t[m] 密度ρ[kg/m³]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">R[m²/日] t[m] ρ[kg/m³]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">工場質量M_factory[kg] 所要電力P_factory[MW] 所要人員N_staff</t>
+  </si>
+  <si>
+    <t>自己複製ロボットによる無人運転を前提</t>
+  </si>
+  <si>
+    <t>MER-08</t>
+  </si>
+  <si>
+    <t>自己複製ロボット工場の設計</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ロボット生産速度R_robot[台/日] 1台あたり質量M_robot[kg]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">R[台/日] M[kg]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">工場質量M_factory[kg] 所要電力P_factory[MW]</t>
+  </si>
+  <si>
+    <t>ロボットがロボットを作る自己複製の要</t>
+  </si>
+  <si>
+    <t>MER-09</t>
+  </si>
+  <si>
+    <t>エネルギー</t>
+  </si>
+  <si>
+    <t>地表太陽光発電と蓄電</t>
+  </si>
+  <si>
+    <t xml:space="preserve">水星日照時間T_day[h] 夜間時間T_night[h] 発電容量P_solar[MW]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">T_day T_night P_solar</t>
+  </si>
+  <si>
+    <t xml:space="preserve">必要蓄電容量E_battery[MWh] 蓄電質量M_battery[kg]</t>
+  </si>
+  <si>
+    <t>水星は58日かけて1回転、長い夜に対応</t>
+  </si>
+  <si>
+    <t>MER-10</t>
+  </si>
+  <si>
+    <t>核融合補助電源の設計</t>
+  </si>
+  <si>
+    <t xml:space="preserve">必要出力P_req[MW] 燃料消費率R_fuel[kg/日] 運転期間T_op[年]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">P[MW] R[kg/日] T[年]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">炉心質量M_reactor[kg] 総燃料量M_fuel_total[kg]</t>
+  </si>
+  <si>
+    <t>太陽光発電だけでは夜間電力が不足。D-He3核融合を想定</t>
+  </si>
+  <si>
+    <t>MER-11</t>
+  </si>
+  <si>
+    <t>輸送</t>
+  </si>
+  <si>
+    <t>地表-軌道間の資材輸送（スペースエレベータ）</t>
+  </si>
+  <si>
+    <t xml:space="preserve">水星重力g[m/s²] エレベータ長L_cable[m] 炭素ナノチューブ強度σ[Pa]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">g L σ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ケーブル質量M_cable[kg] 輸送能力C_transport[ton/日]</t>
+  </si>
+  <si>
+    <t>水星0.38Gならエレベータ建設が現実的</t>
+  </si>
+  <si>
+    <t>MER-12</t>
+  </si>
+  <si>
+    <t>地表-軌道間の資材輸送（マスドライバー）</t>
+  </si>
+  <si>
+    <t xml:space="preserve">射出加速度a_accel[m/s²] 射出質量M_shot[kg] 射出頻度f_shot[回/日]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">a M f</t>
+  </si>
+  <si>
+    <t xml:space="preserve">必要電力P_accel[MW] 年間射出量M_year[ton/年]</t>
+  </si>
+  <si>
+    <t>大気がない水星ではマスドライバーが効率的</t>
+  </si>
+  <si>
+    <t>MER-13</t>
+  </si>
+  <si>
+    <t>維持</t>
+  </si>
+  <si>
+    <t>基地運用に必要な要員数</t>
+  </si>
+  <si>
+    <t xml:space="preserve">基地機能数N_func 自動化率R_auto[%] 交代周期T_rotation[月]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">N_func R_auto T_rotation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">最小要員数N_min[人] 総要員数N_total[人]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">完全無人化 vs 最小限有人運用の比較</t>
+  </si>
+  <si>
+    <t>MER-14</t>
+  </si>
+  <si>
+    <t>地球との通信遅延と制御方式</t>
+  </si>
+  <si>
+    <t xml:space="preserve">地球-水星距離d[AU] 光速c[m/s]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">d[AU] c</t>
+  </si>
+  <si>
+    <t xml:space="preserve">通信遅延T_delay[min] 自律制御率R_auto[%]</t>
+  </si>
+  <si>
+    <t>往復5〜22分の遅延。緊急時は自律制御が必須</t>
+  </si>
+  <si>
+    <t>MER-15</t>
+  </si>
+  <si>
+    <t>基地の生命維持システム設計</t>
+  </si>
+  <si>
+    <t xml:space="preserve">要員数N[人] 1人あたり必要酸素O2_req[kg/日] 水H2O_req[kg/日] 食料F_req[kg/日]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">N O2 H2O F</t>
+  </si>
+  <si>
+    <t xml:space="preserve">総必要量O2_total H2O_total F_total[kg/日] リサイクル率R_recycle[%]</t>
+  </si>
+  <si>
+    <t>閉鎖生態系＋地球からの補給のハイブリッド</t>
+  </si>
+  <si>
+    <t>MER-16</t>
+  </si>
+  <si>
+    <t>廃熱管理（水星の高温環境対応）</t>
+  </si>
+  <si>
+    <t xml:space="preserve">外気温T_out[℃] 内部発熱Q_int[MW] 冷却効率η_cool</t>
+  </si>
+  <si>
+    <t xml:space="preserve">T_out Q_int η_cool</t>
+  </si>
+  <si>
+    <t xml:space="preserve">必要冷却能力Q_cool[MW] 冷却水必要量M_water[ton/日]</t>
+  </si>
+  <si>
+    <t>昼側+430℃での放熱は極めて困難。ヒートポンプ必須</t>
+  </si>
+  <si>
+    <t>MER-17</t>
+  </si>
+  <si>
+    <t>リスク</t>
+  </si>
+  <si>
+    <t>太陽フレアによる基地被災リスク</t>
+  </si>
+  <si>
+    <t xml:space="preserve">フレア発生頻度F_flare[回/年] フレアエネルギーE_flare[J] 基地耐性R_base[J/m²]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">F E R</t>
+  </si>
+  <si>
+    <t xml:space="preserve">年間被害確率P_damage[%/年] 復旧コストC_repair[USD/回]</t>
+  </si>
+  <si>
+    <t>水星は太陽に近くフレアリスク大。シェルター設計必須</t>
+  </si>
+  <si>
+    <t>MER-18</t>
+  </si>
+  <si>
+    <t>微小隕石による基地損傷リスク</t>
+  </si>
+  <si>
+    <t xml:space="preserve">隕石フラックスF_meteor[個/m²/年] 基地表面積A_base[m²] 装甲厚d_armor[m]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">F A d</t>
+  </si>
+  <si>
+    <t xml:space="preserve">年間被弾回数N_hit[回/年] 補修コストC_repair[USD/年]</t>
+  </si>
+  <si>
+    <t>水星は大気がないため隕石対策が重要</t>
+  </si>
+  <si>
+    <t>MER-19</t>
+  </si>
+  <si>
+    <t>コスト</t>
+  </si>
+  <si>
+    <t>水星地表基地の総建設コスト</t>
+  </si>
+  <si>
+    <t xml:space="preserve">着陸モジュールC_lander 基地建設C_base 採掘設備C_mine 製造工場C_factory 輸送設備C_transport</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C_lander C_base C_mine C_factory C_transport</t>
+  </si>
+  <si>
+    <t xml:space="preserve">総コストC_total[USD] 運用コストC_op[USD/年]</t>
+  </si>
+  <si>
+    <t>初期投資と運用コストのバランス評価</t>
+  </si>
+  <si>
+    <t>MER-20</t>
+  </si>
+  <si>
+    <t>水星ダイソン環の投資回収期間</t>
+  </si>
+  <si>
+    <t xml:space="preserve">総建設コストC_total[USD] 年間発電収入R_power[USD/年] 年間運用コストC_op[USD/年]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C_total R_power C_op</t>
+  </si>
+  <si>
+    <t xml:space="preserve">投資回収期間T_payback[年] ROI[%]</t>
+  </si>
+  <si>
+    <t>1.2PWの発電能力によるエネルギー販売収入で回収</t>
+  </si>
+  <si>
+    <t>#1003</t>
+  </si>
+  <si>
+    <t>自己複製拡張幾何学</t>
+  </si>
+  <si>
+    <t>12TW→1200TWへの拡張収支シミュ。</t>
+  </si>
+  <si>
+    <t>済</t>
+  </si>
+  <si>
+    <t>金星から供給</t>
+  </si>
+  <si>
+    <t>26.07.10</t>
+  </si>
+  <si>
+    <t>金星母船ヘスペラスと通信</t>
+  </si>
+  <si>
+    <t>課題カテゴリ</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 計算テーマ</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 計算内容</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> ツール</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 優先度</t>
+  </si>
+  <si>
+    <t>c201</t>
+  </si>
+  <si>
+    <t>量子ビット集積化</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> ナノダイヤモンドアレイの最適配置</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> NVセンター間の光結合効率を最大化する配置の最適化</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Python + Maxima</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> ◎ 最優先</t>
+  </si>
+  <si>
+    <t>c202</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 光子損失確率の見積もり</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> ナノダイヤモンドから検出器までの光子伝搬損失を計算</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Python</t>
+  </si>
+  <si>
+    <t>c203</t>
+  </si>
+  <si>
+    <t>量子ゲート精度</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> ゲートエラー率のスピン依存性</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> NVセンターのスピン状態に依存したゲートエラー率の理論計算</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Maxima</t>
+  </si>
+  <si>
+    <t>26.06.23</t>
+  </si>
+  <si>
+    <t>c204</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 表面符号の閾値計算</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 誤り訂正に必要な物理量子ビット数と論理量子ビット数の関係</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> ○ 重要</t>
+  </si>
+  <si>
+    <t>c205</t>
+  </si>
+  <si>
+    <t>デコヒーレンス</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> NVセンターのコヒーレンス時間の温度依存性</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 9Kから室温までのコヒーレンス時間の理論曲線</t>
+  </si>
+  <si>
+    <t>26.06.22</t>
+  </si>
+  <si>
+    <t>c206</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 動的デカップリングパルスの最適化</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 量子状態を維持するためのパルスシーケンスの最適化</t>
+  </si>
+  <si>
+    <t>c207</t>
+  </si>
+  <si>
+    <t>光子検出効率</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> SNSPDの検出効率の波長依存性</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> ナノダイヤモンドの発光波長に対する超伝導検出器の効率計算</t>
+  </si>
+  <si>
+    <t>c208</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 検出器アレイの最適設計</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 必要な検出器数と配置の最適化</t>
+  </si>
+  <si>
+    <t>c209</t>
+  </si>
+  <si>
+    <t>量子メモリ</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> NVセンター電子スピンの記憶時間</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> スピン-スピン相互作用によるデコヒーレンスの理論限界</t>
+  </si>
+  <si>
+    <t>c210</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 核スピンを用いた長期記憶の可能性</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 炭素13核スピンのコヒーレンス時間の見積もり</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> △ あると良い</t>
+  </si>
+  <si>
+    <t>c211</t>
+  </si>
+  <si>
+    <t>冷却システム</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 9K冷却に必要な電力</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> プロキシマbの低温環境を活用した冷却効率の計算</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> △ 解決済みに近い</t>
+  </si>
+  <si>
+    <t>c212</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 放射冷却パネルのサイズ見積もり</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 真空中での放射冷却に必要なパネル面積</t>
+  </si>
+  <si>
+    <t>c213</t>
+  </si>
+  <si>
+    <t>放射線耐性</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> フレアによるソフトエラー率</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> プロキシマbのフレア環境下での量子ビットエラー率の推定</t>
+  </si>
+  <si>
+    <t>c214</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 地下基地の遮蔽効果</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 地下100mでの放射線低減率の計算</t>
+  </si>
+  <si>
+    <t>c215</t>
+  </si>
+  <si>
+    <t>量子-古典インターフェース</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 読み出し時間の理論限界</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> ホモダイン検出の時間分解能と読み出しエラー率の関係</t>
+  </si>
+  <si>
+    <t>c216</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 並列読み出しの最適化</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 多数の量子ビットを同時に読み出す際のクロストーク</t>
+  </si>
+  <si>
+    <t>c217</t>
+  </si>
+  <si>
+    <t>AIとの統合</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 量子ニューラルネットワークの計算量</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 時超えケンタの意思決定に必要な量子演算回数の見積もり</t>
+  </si>
+  <si>
+    <t>c218</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 量子機械学習の収束速度</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 量子勾配降下法の収束速度の理論解析</t>
+  </si>
+  <si>
+    <t>c219</t>
+  </si>
+  <si>
+    <t>自己診断</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 量子ビット故障検出の感度</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 故障した量子ビットを特定するための最小測定回数</t>
+  </si>
+  <si>
+    <t>c220</t>
+  </si>
+  <si>
+    <t>自己修復</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 冗長化に必要な量子ビット数</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 所定の故障率に対して必要な予備量子ビット数</t>
+  </si>
+  <si>
+    <t>c221</t>
+  </si>
+  <si>
+    <t>長距離量子通信</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> マイクロスロート経由の量子状態転送</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> ワームホールを通した量子テレポーテーションの成功確率</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> ◎ 最優先（#4001関連）</t>
+  </si>
+  <si>
+    <t>26.06.24</t>
+  </si>
+  <si>
+    <t>c222</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 量子中継器の必要数</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 4.2光年先との量子通信に必要な中継器数の見積もり</t>
+  </si>
+  <si>
+    <t>c223</t>
+  </si>
+  <si>
+    <t>システム統合</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 全体の消費電力見積もり</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 量子コンピュータ・冷却・検出器・制御システムの総消費電力</t>
+  </si>
+  <si>
+    <t>c224</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 計算能力のスケーリング則</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 量子ビット数に対する計算能力の理論曲線</t>
+  </si>
+  <si>
+    <t>#4001</t>
+  </si>
+  <si>
+    <t>多元宇宙穿孔（マルチ・パンクチャー）</t>
+  </si>
+  <si>
+    <t>Maxima</t>
+  </si>
+  <si>
+    <t>4.2光年以上の長距離穿孔への拡張数式</t>
+  </si>
+  <si>
+    <t>#903</t>
+  </si>
+  <si>
+    <t>銀河スケール・カルダシェフ査定</t>
+  </si>
+  <si>
+    <t>Python</t>
+  </si>
+  <si>
+    <t>タイプII文明（）への完全移行証明</t>
+  </si>
+  <si>
+    <t>HZC-01</t>
+  </si>
+  <si>
+    <t>HZ創出</t>
+  </si>
+  <si>
+    <t>構造設計</t>
+  </si>
+  <si>
+    <t>浮遊人工惑星の最小質量と重力生成</t>
+  </si>
+  <si>
+    <t xml:space="preserve">直径D_km 回転周期T_sec 目標重力g_target</t>
+  </si>
+  <si>
+    <t xml:space="preserve">D[km] T[sec] g_target[m/s²]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">必要質量M_kg 構造材強度σ_req[Pa]</t>
+  </si>
+  <si>
+    <t>カーボンナノチューブ構造を仮定</t>
+  </si>
+  <si>
+    <t>26.07.08</t>
+  </si>
+  <si>
+    <t>HZC-02</t>
+  </si>
+  <si>
+    <t>人工惑星シェル厚の最適化</t>
+  </si>
+  <si>
+    <t xml:space="preserve">直径D_km 内部気圧P_atm 放射線遮蔽要件R_shield</t>
+  </si>
+  <si>
+    <t xml:space="preserve">D[km] P_atm[atm] R_shield[g/cm²]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">シェル厚d_cm 総質量M_shell[kg]</t>
+  </si>
+  <si>
+    <t>遮蔽材は水氷＋レゴリス</t>
+  </si>
+  <si>
+    <t>HZC-03</t>
+  </si>
+  <si>
+    <t>大気工学</t>
+  </si>
+  <si>
+    <t>閉鎖生態系の最小大気量と組成</t>
+  </si>
+  <si>
+    <t xml:space="preserve">収容人数N_people 酸素消費率O2_rate 二酸化炭素排出率CO2_rate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">N[人] O2_rate[L/h] CO2_rate[L/h]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">必要大気量V_atm[m³] 酸素補充量O2_supply[kg/日]</t>
+  </si>
+  <si>
+    <t>植物による光合成循環を前提</t>
+  </si>
+  <si>
+    <t>HZC-04</t>
+  </si>
+  <si>
+    <t>人工重力下での大気保持条件</t>
+  </si>
+  <si>
+    <t xml:space="preserve">重力g 温度T 分子量M</t>
+  </si>
+  <si>
+    <t xml:space="preserve">g[m/s²] T[K] M[g/mol]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">大気散逸率R_loss[kg/s] 補充必要量M_fill[kg/年]</t>
+  </si>
+  <si>
+    <t>太陽風・放射線による散逸を考慮</t>
+  </si>
+  <si>
+    <t>HZC-05</t>
+  </si>
+  <si>
+    <t>核融合炉の必要出力と燃料消費</t>
+  </si>
+  <si>
+    <t xml:space="preserve">収容人数N 1人あたり消費電力P_person</t>
+  </si>
+  <si>
+    <t xml:space="preserve">N[人] P_person[kW]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">必要出力P_total[GW] 燃料消費量F_kg[kg/年]</t>
+  </si>
+  <si>
+    <t>D-He3核融合を仮定</t>
+  </si>
+  <si>
+    <t>HZC-06</t>
+  </si>
+  <si>
+    <t>太陽光発電の効率と必要面積</t>
+  </si>
+  <si>
+    <t xml:space="preserve">恒星光度L 距離d パネル効率η</t>
+  </si>
+  <si>
+    <t xml:space="preserve">L[L_sun] d[AU] η[%]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">発電量P_gen[GW] 必要面積A_panel[km²]</t>
+  </si>
+  <si>
+    <t>各HZの恒星スペクトルに応じた効率補正</t>
+  </si>
+  <si>
+    <t>HZC-07</t>
+  </si>
+  <si>
+    <t>生態系</t>
+  </si>
+  <si>
+    <t>閉鎖生態系の最小種数と安定性</t>
+  </si>
+  <si>
+    <t xml:space="preserve">閉鎖容積V 栄養循環速度R_nutrient</t>
+  </si>
+  <si>
+    <t xml:space="preserve">V[m³] R_nutrient[kg/日]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">最小種数N_species 崩壊確率P_collapse[%/年]</t>
+  </si>
+  <si>
+    <t>生物多様性と生態系安定性の関係式</t>
+  </si>
+  <si>
+    <t>HZC-08</t>
+  </si>
+  <si>
+    <t>食料生産に必要な農地面積</t>
+  </si>
+  <si>
+    <t xml:space="preserve">収容人数N 1人あたり必要カロリーC_req</t>
+  </si>
+  <si>
+    <t xml:space="preserve">N[人] C_req[kcal/日]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">必要農地面積A_farm[km²] 水使用量W_water[トン/日]</t>
+  </si>
+  <si>
+    <t>水耕栽培・垂直農法を前提</t>
+  </si>
+  <si>
+    <t>HZC-09</t>
+  </si>
+  <si>
+    <t>材料</t>
+  </si>
+  <si>
+    <t>小惑星からの資源採掘効率</t>
+  </si>
+  <si>
+    <t xml:space="preserve">小惑星質量M_asteroid 採掘速度R_mining</t>
+  </si>
+  <si>
+    <t xml:space="preserve">M[kg] R_mining[kg/日]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">採掘可能量M_usable[kg] 採掘期間T_years[年]</t>
+  </si>
+  <si>
+    <t>自己複製ロボットによる採掘を前提</t>
+  </si>
+  <si>
+    <t>HZC-10</t>
+  </si>
+  <si>
+    <t>人工惑星建設に必要な総資源量</t>
+  </si>
+  <si>
+    <t xml:space="preserve">直径D_km シェル厚d_cm 内部構造比率R_struct</t>
+  </si>
+  <si>
+    <t xml:space="preserve">D[km] d[cm] R_struct[%]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">総質量M_total[kg] 資源別必要量（鉄・炭素・水等）[kg]</t>
+  </si>
+  <si>
+    <t>太陽系内の小惑星帯からの調達を前提</t>
+  </si>
+  <si>
+    <t>HZC-11</t>
+  </si>
+  <si>
+    <t>熱制御</t>
+  </si>
+  <si>
+    <t>人工惑星の熱平衡温度計算</t>
+  </si>
+  <si>
+    <t xml:space="preserve">恒星光度L 距離d アルベドA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">L[L_sun] d[AU] A[0-1]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">平衡温度T_eq[K] 必要冷却能力Q_cool[GW]</t>
+  </si>
+  <si>
+    <t>内部発熱（機器・人体）も考慮</t>
+  </si>
+  <si>
+    <t>HZC-12</t>
+  </si>
+  <si>
+    <t>廃熱放射パネルの必要面積</t>
+  </si>
+  <si>
+    <t xml:space="preserve">廃熱量Q_waste 放射温度T_rad 放射率ε</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Q_waste[GW] T_rad[K] ε</t>
+  </si>
+  <si>
+    <t>必要面積A_rad[km²]</t>
+  </si>
+  <si>
+    <t>宇宙空間への放射冷却を前提</t>
+  </si>
+  <si>
+    <t>HZC-13</t>
+  </si>
+  <si>
+    <t>磁場</t>
+  </si>
+  <si>
+    <t>人工磁場シールドの必要強度とエネルギー</t>
+  </si>
+  <si>
+    <t xml:space="preserve">太陽風圧P_wind 遮蔽半径R_shield</t>
+  </si>
+  <si>
+    <t xml:space="preserve">P_wind[Pa] R_shield[m]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">必要磁場B_req[T] 消費電力P_mag[MW]</t>
+  </si>
+  <si>
+    <t>超伝導電磁石による能動シールド</t>
+  </si>
+  <si>
+    <t>HZC-14</t>
+  </si>
+  <si>
+    <t>放射線遮蔽に必要な水氷厚</t>
+  </si>
+  <si>
+    <t xml:space="preserve">入射放射線エネルギーE_rad 遮蔽率R_shield</t>
+  </si>
+  <si>
+    <t xml:space="preserve">E_rad[MeV] R_shield[%]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">必要厚d_ice[m] 質量M_ice[kg]</t>
+  </si>
+  <si>
+    <t>銀河宇宙線・太陽フレア双方を考慮</t>
+  </si>
+  <si>
+    <t>HZC-15</t>
+  </si>
+  <si>
+    <t>軌道制御</t>
+  </si>
+  <si>
+    <t>人工惑星の軌道維持と姿勢制御</t>
+  </si>
+  <si>
+    <t xml:space="preserve">太陽風圧P_wind 重力擾乱Δg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">P_wind[Pa] Δg[m/s²]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">必要推力F_thrust[N] 燃料消費量F_fuel[kg/年]</t>
+  </si>
+  <si>
+    <t>イオンエンジンによる定常制御</t>
+  </si>
+  <si>
+    <t>HZC-16</t>
+  </si>
+  <si>
+    <t>複数人工HZ間のワームホールネットワーク最適配置</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HZ数N 平均距離d_avg 通信需要C_req</t>
+  </si>
+  <si>
+    <t xml:space="preserve">N[基] d_avg[ly] C_req[bps]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">最適ネットワークトポロジー 総ワームホール数N_wh</t>
+  </si>
+  <si>
+    <t xml:space="preserve">スター型 vs メッシュ型の比較</t>
+  </si>
+  <si>
+    <t>HZC-17</t>
+  </si>
+  <si>
+    <t>社会</t>
+  </si>
+  <si>
+    <t>人口収容力と社会構造の最適化</t>
+  </si>
+  <si>
+    <t xml:space="preserve">収容人数N 年齢構成A_dist 資源消費R_person</t>
+  </si>
+  <si>
+    <t xml:space="preserve">N[人] A_dist[%] R_person[kg/年]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">最大持続可能人口N_max 必要資源備蓄量S_req[kg]</t>
+  </si>
+  <si>
+    <t>クローンPhysicalAIと生身人間の比率を変数に</t>
+  </si>
+  <si>
+    <t>HZC-18</t>
+  </si>
+  <si>
+    <t>閉鎖社会における心理的安定性評価</t>
+  </si>
+  <si>
+    <t xml:space="preserve">閉鎖期間T_years 人口N 多様性指数D</t>
+  </si>
+  <si>
+    <t xml:space="preserve">T[年] N[人] D[0-1]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">社会崩壊確率P_collapse[%] 介入頻度F_int[回/年]</t>
+  </si>
+  <si>
+    <t>過去の閉鎖実験（バイオスフィア2等）のデータを参照</t>
+  </si>
+  <si>
+    <t>HZC-19</t>
+  </si>
+  <si>
+    <t>人工HZ1基あたりの建設コスト試算</t>
+  </si>
+  <si>
+    <t xml:space="preserve">直径D_km 収容人数N 建設期間T_years</t>
+  </si>
+  <si>
+    <t xml:space="preserve">D[km] N[人] T[年]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">総コストC_total[USD] 1人あたりコストC_per_person[USD]</t>
+  </si>
+  <si>
+    <t>自己複製ロボットによる建設でコスト低減を見込む</t>
+  </si>
+  <si>
+    <t>HZC-20</t>
+  </si>
+  <si>
+    <t xml:space="preserve">天然HZ開拓 vs 人工HZ創出の費用対効果比較</t>
+  </si>
+  <si>
+    <t xml:space="preserve">天然HZコストC_natural 人工HZコストC_artificial 生存確率P_surv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C_natural[USD] C_artificial[USD] P_surv[%]</t>
+  </si>
+  <si>
+    <t>最適投資配分比R_opt</t>
+  </si>
+  <si>
+    <t>100年後の人口維持数を指標に</t>
+  </si>
+  <si>
+    <t>#1007</t>
+  </si>
+  <si>
+    <t>ｴﾋﾟﾛｰｸﾞ</t>
+  </si>
+  <si>
+    <t>ペンローズ過程</t>
+  </si>
+  <si>
+    <t>BH回転エネルギーの直接抽出</t>
+  </si>
+  <si>
+    <t>物理の壁を越えるための最終手段</t>
+  </si>
+  <si>
+    <t xml:space="preserve">#1007BZ 26.06.14</t>
+  </si>
+  <si>
+    <t>BIO-508-EXT1</t>
+  </si>
+  <si>
+    <t>記憶転送</t>
+  </si>
+  <si>
+    <t>完全性</t>
+  </si>
+  <si>
+    <t>記憶の完全転写精度</t>
+  </si>
+  <si>
+    <t>ニューロン接続数N_synapse=1e15</t>
+  </si>
+  <si>
+    <t>転写精度η</t>
+  </si>
+  <si>
+    <t>完全性指標C_integ[%]</t>
+  </si>
+  <si>
+    <t>PhysicalAIへの転写時の情報損失率。感情と理性の統合が課題</t>
+  </si>
+  <si>
+    <t>26.07.05</t>
+  </si>
+  <si>
+    <t>BIO-508-EXT2</t>
+  </si>
+  <si>
+    <t>容量</t>
+  </si>
+  <si>
+    <t>記憶データの圧縮率</t>
+  </si>
+  <si>
+    <t>生データD_raw[EB]</t>
+  </si>
+  <si>
+    <t>圧縮率R_comp</t>
+  </si>
+  <si>
+    <t>転送データ量D_trans[TB]</t>
+  </si>
+  <si>
+    <t>1.5EBの記憶をPhysicalAIに格納するための圧縮要件</t>
+  </si>
+  <si>
+    <t>BIO-508-EXT3</t>
+  </si>
+  <si>
+    <t>PhysicalAI</t>
+  </si>
+  <si>
+    <t>インターフェース</t>
+  </si>
+  <si>
+    <t>生体-機械変換効率</t>
+  </si>
+  <si>
+    <t>ニューロン発火頻度f_neuron[Hz]</t>
+  </si>
+  <si>
+    <t>変換効率η_trans</t>
+  </si>
+  <si>
+    <t>信号忠実度F_sig[%]</t>
+  </si>
+  <si>
+    <t>生体信号をPhysicalAIのデジタル信号に変換する際の忠実度</t>
+  </si>
+  <si>
+    <t>BIO-508-EXT4</t>
+  </si>
+  <si>
+    <t>耐久性</t>
+  </si>
+  <si>
+    <t>PhysicalAIの記憶保存寿命</t>
+  </si>
+  <si>
+    <t>保存期間T_years</t>
+  </si>
+  <si>
+    <t>ビット誤り率BER</t>
+  </si>
+  <si>
+    <t>データ完全性保持確率P_keep</t>
+  </si>
+  <si>
+    <t>ワームホール通過時の放射線・エキゾチック物質によるデータ劣化</t>
+  </si>
+  <si>
+    <t>BIO-508-EXT5</t>
+  </si>
+  <si>
+    <t>ワームホール</t>
+  </si>
+  <si>
+    <t>通過耐性</t>
+  </si>
+  <si>
+    <t>ワームホール通過時のデータ完全性</t>
+  </si>
+  <si>
+    <t>通過時間T_transit</t>
+  </si>
+  <si>
+    <t>エキゾチック物質影響係数E_exo</t>
+  </si>
+  <si>
+    <t>データ損失率L_data[%]</t>
+  </si>
+  <si>
+    <t>PhysicalAIがワームホール通過中に受けるデータ擾乱</t>
+  </si>
+  <si>
+    <t>地球上で転写するのか系外でするのか？両方でする？その時点での現実的選択</t>
+  </si>
+  <si>
+    <t>26.07.06</t>
+  </si>
+  <si>
+    <t>BIO-508-EXT6</t>
+  </si>
+  <si>
+    <t>時間非同期</t>
+  </si>
+  <si>
+    <t>相対論的時間遅延と記憶の整合性</t>
+  </si>
+  <si>
+    <t>ワームホール長L_wormhole[m]</t>
+  </si>
+  <si>
+    <t>時間オフセットΔt</t>
+  </si>
+  <si>
+    <t>意識連続性指標C_cont[%]</t>
+  </si>
+  <si>
+    <t>出口側での時間非同期が記憶の連続性に与える影響</t>
+  </si>
+  <si>
+    <t>BIO-508-EXT7</t>
+  </si>
+  <si>
+    <t>HZ再生</t>
+  </si>
+  <si>
+    <t>体化</t>
+  </si>
+  <si>
+    <t>PhysicalAIから生体への記憶再書き込み成功率</t>
+  </si>
+  <si>
+    <t>ニューロン再形成率R_neuro</t>
+  </si>
+  <si>
+    <t>シナプス再結合率R_syn</t>
+  </si>
+  <si>
+    <t>復元記憶完全性C_restore[%]</t>
+  </si>
+  <si>
+    <t>HZでの再生時にPhysicalAIの記憶を新しい生体に書き込む成功率</t>
+  </si>
+  <si>
+    <t>BIO-508-EXT8</t>
+  </si>
+  <si>
+    <t>個体識別</t>
+  </si>
+  <si>
+    <t>再生体のアイデンティティ同一性</t>
+  </si>
+  <si>
+    <t>元の個体情報I_orig</t>
+  </si>
+  <si>
+    <t>再生体情報I_reborn</t>
+  </si>
+  <si>
+    <t>同一性指標I_id[%]</t>
+  </si>
+  <si>
+    <t>再生された個体が元の個体と同一と言えるかの確率</t>
+  </si>
+  <si>
+    <t>BIO-508-EXT9</t>
+  </si>
+  <si>
+    <t>資源</t>
+  </si>
+  <si>
+    <t>再生に必要な資源量</t>
+  </si>
+  <si>
+    <t>再生体質量M_body[kg]</t>
+  </si>
+  <si>
+    <t>エネルギー効率η_energy</t>
+  </si>
+  <si>
+    <t>必要エネルギーE_req[J]</t>
+  </si>
+  <si>
+    <t>HZで1体の人間を再生するのに必要な資源・エネルギー</t>
+  </si>
+  <si>
+    <t>BIO-508-EXT10</t>
+  </si>
+  <si>
+    <t>統合</t>
+  </si>
+  <si>
+    <t>倫理</t>
+  </si>
+  <si>
+    <t>意識連続性と倫理的閾値</t>
+  </si>
+  <si>
+    <t>転送回数N_transfer</t>
+  </si>
+  <si>
+    <t>意識断絶時間T_gap</t>
+  </si>
+  <si>
+    <t>倫理許容度E_accept</t>
+  </si>
+  <si>
+    <t>何回の転送まで「同一人物」と認めるかの閾値</t>
+  </si>
+  <si>
+    <t>BIO-508-EXT11</t>
+  </si>
+  <si>
+    <t>チェーン全体の成功確率</t>
+  </si>
+  <si>
+    <t>各ステップ成功確率P_i</t>
+  </si>
+  <si>
+    <t>連成失敗率F_couple</t>
+  </si>
+  <si>
+    <t>総成功確率P_total</t>
+  </si>
+  <si>
+    <t>記憶転送→PhysicalAI→ワームホール→HZ再生のチェーン全体信頼性</t>
+  </si>
+  <si>
+    <t>BIO-508-EXT12</t>
+  </si>
+  <si>
+    <t>冗長化</t>
+  </si>
+  <si>
+    <t>DNA情報と記憶の二重化戦略</t>
+  </si>
+  <si>
+    <t>DNA保存完全性D_DNA</t>
+  </si>
+  <si>
+    <t>記憶保存完全性M_mem</t>
+  </si>
+  <si>
+    <t>冗長化利得G_redun</t>
+  </si>
+  <si>
+    <t>DNA（種の保存）と記憶（個人の保存）の二重化による信頼性向上</t>
+  </si>
+  <si>
+    <t>WH-01</t>
+  </si>
+  <si>
+    <t>必要負エネルギー</t>
+  </si>
+  <si>
+    <t>Morris-Thorneワームホール維持に必要な負のエネルギー</t>
+  </si>
+  <si>
+    <t>ワームホール半径r0[m]</t>
+  </si>
+  <si>
+    <t>総負エネルギーE[J]</t>
+  </si>
+  <si>
+    <t>カシミール効果の利用可能性</t>
+  </si>
+  <si>
+    <t>WH-02</t>
+  </si>
+  <si>
+    <t>生体潮汐力</t>
+  </si>
+  <si>
+    <t>ワームホール通過時の人体への潮汐力評価</t>
+  </si>
+  <si>
+    <t>身長Δr[m]</t>
+  </si>
+  <si>
+    <t>潮汐力[G]</t>
+  </si>
+  <si>
+    <t>許容限界との比較</t>
+  </si>
+  <si>
+    <t>WH-03</t>
+  </si>
+  <si>
+    <t>時間遅延効果</t>
+  </si>
+  <si>
+    <t>ワームホール内部と外部の時間差</t>
+  </si>
+  <si>
+    <t>内部質量M[kg]</t>
+  </si>
+  <si>
+    <t>半径r0[m]</t>
+  </si>
+  <si>
+    <t>時間遅延因子</t>
+  </si>
+  <si>
+    <t>転送中の生体影響</t>
+  </si>
+  <si>
+    <t>HZ-01</t>
+  </si>
+  <si>
+    <t>ハビタブルゾーン</t>
+  </si>
+  <si>
+    <t>期待発見数</t>
+  </si>
+  <si>
+    <t>20光年以内のHZ惑星期待数</t>
+  </si>
+  <si>
+    <t>恒星タイプ別発生率P</t>
+  </si>
+  <si>
+    <t>恒星数N</t>
+  </si>
+  <si>
+    <t>期待発見数[個]</t>
+  </si>
+  <si>
+    <t>観測バイアス補正前</t>
+  </si>
+  <si>
+    <t>26.07.03</t>
+  </si>
+  <si>
+    <t>HZ-02</t>
+  </si>
+  <si>
+    <t>観測バイアス補正</t>
+  </si>
+  <si>
+    <t>トランジット法・視線速度法の検出確率補正</t>
+  </si>
+  <si>
+    <t>検出確率P_detect</t>
+  </si>
+  <si>
+    <t>観測可能数[個]</t>
+  </si>
+  <si>
+    <t>補正後期待数</t>
+  </si>
+  <si>
+    <t>HZ-03</t>
+  </si>
+  <si>
+    <t>発見時間推定</t>
+  </si>
+  <si>
+    <t>HZ惑星確認に必要な観測期間</t>
+  </si>
+  <si>
+    <t>公転周期T[日]</t>
+  </si>
+  <si>
+    <t>確認トランジット数N_conf</t>
+  </si>
+  <si>
+    <t>確認時間[年]</t>
+  </si>
+  <si>
+    <t>恒星タイプ別</t>
+  </si>
+  <si>
+    <t>HZ-04</t>
+  </si>
+  <si>
+    <t>累積発見確率</t>
+  </si>
+  <si>
+    <t>経過年数に対する累積発見確率</t>
+  </si>
+  <si>
+    <t>特性時間τ[年]</t>
+  </si>
+  <si>
+    <t>観測可能総数N_obs</t>
+  </si>
+  <si>
+    <t>累積発見数[個]</t>
+  </si>
+  <si>
+    <t>グラフ出力</t>
+  </si>
+  <si>
+    <t>DNA-01</t>
+  </si>
+  <si>
+    <t>DNA情報管理</t>
+  </si>
+  <si>
+    <t>ブロックチェーン</t>
+  </si>
+  <si>
+    <t>DNA情報のブロックチェーン保存と共有</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DNAデータサイズD_size ブロックサイズB_size TX数N_tx ガス代G_cost</t>
+  </si>
+  <si>
+    <t xml:space="preserve">D_size[GB] B_size[MB] N_tx G_cost[USD]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">保存コストC_total[USD] 転送時間T_trans[sec]</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>マイクロスロートAR回線で常時接続。</t>
+    </r>
+    <r>
+      <rPr>
+        <strike/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>0.2cレーザーはバックアップ</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">26.07.03
+汎用管理ツールで対応</t>
+  </si>
+  <si>
+    <t>DNA-02</t>
+  </si>
+  <si>
+    <t>マイクロスロートAR</t>
+  </si>
+  <si>
+    <t>マイクロスロートAR回線によるDNA情報のリアルタイム共有</t>
+  </si>
+  <si>
+    <t xml:space="preserve">スロート帯域B_throat レーザー帯域B_laser DNAサイズD_size</t>
+  </si>
+  <si>
+    <t xml:space="preserve">B_throat[Tbps] B_laser[Gbps] D_size[GB]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">転送時間T_throat[sec] T_laser[sec] 遅延D[ms]</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>AR回線は瞬時（理論上）</t>
+    </r>
+    <r>
+      <rPr>
+        <strike/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> レーザーは0.2cで物理的限界</t>
+    </r>
+  </si>
+  <si>
+    <t>DNA-03</t>
+  </si>
+  <si>
+    <t>ハイブリッド転送</t>
+  </si>
+  <si>
+    <t>マイクロスロートARと0.2cレーザーのハイブリッド転送戦略</t>
+  </si>
+  <si>
+    <t xml:space="preserve">緊急度U
+データ重要度I
+サイズS 
+コストC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">U[0-1] I[0-1] S[GB] C[USD/GB]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">最適経路選択 コスト最小化</t>
+  </si>
+  <si>
+    <t xml:space="preserve">緊急・重要データはAR回線 大容量バルクデータはレーザー</t>
+  </si>
+  <si>
+    <t>DNA-04</t>
+  </si>
+  <si>
+    <t>プライバシー保護</t>
+  </si>
+  <si>
+    <t>ゼロ知識証明によるDNA情報のプライバシー保護</t>
+  </si>
+  <si>
+    <t xml:space="preserve">証明サイズP_size 検証時間V_time プライバシーレベルL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">P_size[KB] V_time[ms] L[1-5]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">オーバーヘッド比R_overhead 安全性評価S_score</t>
+  </si>
+  <si>
+    <t>AR回線の広帯域を活かし完全準同型暗号も併用</t>
+  </si>
+  <si>
+    <t>DNA-05</t>
+  </si>
+  <si>
+    <t>統合システム</t>
+  </si>
+  <si>
+    <t>全DNA情報管理システムの統合モデル</t>
+  </si>
+  <si>
+    <t xml:space="preserve">総ユーザー数N_user 1人あたりDNAサイズD_person 保存期間T_years</t>
+  </si>
+  <si>
+    <t xml:space="preserve">N_user[人] D_person[MB] T_years[年]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">総保存容量C_total[EB] 総コストCost[USD]</t>
+  </si>
+  <si>
+    <t>AR回線＋ブロックチェーン＋ゼロ知識証明の統合</t>
+  </si>
+  <si>
+    <t>DNA-06</t>
+  </si>
+  <si>
+    <t>DNA再生</t>
+  </si>
+  <si>
+    <t>技術ロードマップ</t>
+  </si>
+  <si>
+    <t>人工子宮技術の成熟度予測</t>
+  </si>
+  <si>
+    <t>年次</t>
+  </si>
+  <si>
+    <t>技術成熟度レベル</t>
+  </si>
+  <si>
+    <t>実用化時期</t>
+  </si>
+  <si>
+    <t>26.07.04</t>
+  </si>
+  <si>
+    <t>地球消滅危機による種の保存のみ再生</t>
+  </si>
+  <si>
+    <t>フェーズ</t>
+  </si>
+  <si>
+    <t>P0-01</t>
+  </si>
+  <si>
+    <t>リソース</t>
+  </si>
+  <si>
+    <t>自己複製ロボットの材料収支</t>
+  </si>
+  <si>
+    <t>初期台数N0=1e5</t>
+  </si>
+  <si>
+    <t>複製率r=0.05/day</t>
+  </si>
+  <si>
+    <t>必要材料M(t)</t>
+  </si>
+  <si>
+    <t>グラフ(t</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> M)</t>
+  </si>
+  <si>
+    <t>単位：kg</t>
+  </si>
+  <si>
+    <t>P0-02</t>
+  </si>
+  <si>
+    <t>構造</t>
+  </si>
+  <si>
+    <t>プロキシマb表面重力下の柱座屈荷重</t>
+  </si>
+  <si>
+    <t>重力g=1.2*9.8[m/s2]</t>
+  </si>
+  <si>
+    <t>ヤング率E=200GPa</t>
+  </si>
+  <si>
+    <t>安全荷重Fs[N]</t>
+  </si>
+  <si>
+    <t>数値出力</t>
+  </si>
+  <si>
+    <t>P1-01</t>
+  </si>
+  <si>
+    <t>軌道</t>
+  </si>
+  <si>
+    <t>プロキシマb表面から低軌道へのΔV</t>
+  </si>
+  <si>
+    <t>惑星半径R=0.145*地球R</t>
+  </si>
+  <si>
+    <t>大気密度ρ</t>
+  </si>
+  <si>
+    <t>ΔV[m/s]</t>
+  </si>
+  <si>
+    <t>数値</t>
+  </si>
+  <si>
+    <t>P1-02</t>
+  </si>
+  <si>
+    <t>太陽光vs核融合のEROI</t>
+  </si>
+  <si>
+    <t>日照強度S=0.05*太陽光</t>
+  </si>
+  <si>
+    <t>核融合効率η=0.2</t>
+  </si>
+  <si>
+    <t>EROI比</t>
+  </si>
+  <si>
+    <t>グラフ(距離依存)</t>
+  </si>
+  <si>
+    <t>P2-01</t>
+  </si>
+  <si>
+    <t>推進</t>
+  </si>
+  <si>
+    <t>レーザーセイルの1g定加速プロファイル</t>
+  </si>
+  <si>
+    <t>目標距離d=20[ly]</t>
+  </si>
+  <si>
+    <t>加速度a=9.8[m/s2]</t>
+  </si>
+  <si>
+    <t>到達時間t[yr]</t>
+  </si>
+  <si>
+    <t>表(静止系・船内時間)</t>
+  </si>
+  <si>
+    <t>P2-02</t>
+  </si>
+  <si>
+    <t>軌道</t>
+  </si>
+  <si>
+    <t>プロキシマb→グリーゼ581の最適軌道</t>
+  </si>
+  <si>
+    <t>出発位置r1=4.24ly</t>
+  </si>
+  <si>
+    <t>到着r2=20ly</t>
+  </si>
+  <si>
+    <t>燃料消費ΔV</t>
+  </si>
+  <si>
+    <t>比較表</t>
+  </si>
+  <si>
+    <t>P3-01</t>
+  </si>
+  <si>
+    <t>通信</t>
+  </si>
+  <si>
+    <t>光通信の往復レイテンシ</t>
+  </si>
+  <si>
+    <t>距離d[ly]</t>
+  </si>
+  <si>
+    <t>光速c</t>
+  </si>
+  <si>
+    <t>遅延時間T[yr]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">グラフ(d vs T)</t>
+  </si>
+  <si>
+    <t>P3-02</t>
+  </si>
+  <si>
+    <t>経済</t>
+  </si>
+  <si>
+    <t>3星系間の資源輸送最適化</t>
+  </si>
+  <si>
+    <t>各星系の生産量p_i</t>
+  </si>
+  <si>
+    <t>需要量d_i</t>
+  </si>
+  <si>
+    <t>輸送コストc_ij</t>
+  </si>
+  <si>
+    <t>最適フロー</t>
+  </si>
+  <si>
+    <t>線形計画</t>
+  </si>
+  <si>
+    <t>P4-01</t>
+  </si>
+  <si>
+    <t>生態</t>
+  </si>
+  <si>
+    <t>閉鎖生態系の炭素・窒素循環</t>
+  </si>
+  <si>
+    <t>人口N=1e4</t>
+  </si>
+  <si>
+    <t>植物/人間比R</t>
+  </si>
+  <si>
+    <t>物質収支バランス</t>
+  </si>
+  <si>
+    <t>時系列グラフ</t>
+  </si>
+  <si>
+    <t>P4-02</t>
+  </si>
+  <si>
+    <t>人口</t>
+  </si>
+  <si>
+    <t>有効集団サイズと遺伝的多様性</t>
+  </si>
+  <si>
+    <t>初期人口N0</t>
+  </si>
+  <si>
+    <t>世代交代時間Tg</t>
+  </si>
+  <si>
+    <t>ヘテロ接合度H(t)</t>
+  </si>
+  <si>
+    <t>グラフ(t</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> H)</t>
+  </si>
+  <si>
     <t>WAR-01</t>
   </si>
   <si>
@@ -116,9 +2086,6 @@
     <t>WAR-04</t>
   </si>
   <si>
-    <t>経済</t>
-  </si>
-  <si>
     <t>経済相互依存度と戦争確率の相関</t>
   </si>
   <si>
@@ -137,9 +2104,6 @@
     <t>WAR-05</t>
   </si>
   <si>
-    <t>資源</t>
-  </si>
-  <si>
     <t>資源競争の数理モデル</t>
   </si>
   <si>
@@ -302,9 +2266,6 @@
     <t>人口補充率R_repl</t>
   </si>
   <si>
-    <t>実用化時期</t>
-  </si>
-  <si>
     <t>ENV-01</t>
   </si>
   <si>
@@ -419,9 +2380,6 @@
     <t>ENV-06</t>
   </si>
   <si>
-    <t>エネルギー</t>
-  </si>
-  <si>
     <t>再生可能エネルギー100%移行のコスト</t>
   </si>
   <si>
@@ -482,9 +2440,6 @@
     <t>INT-01</t>
   </si>
   <si>
-    <t>統合</t>
-  </si>
-  <si>
     <t>全体</t>
   </si>
   <si>
@@ -591,490 +2546,13 @@
   </si>
   <si>
     <t>システム設計</t>
-  </si>
-  <si>
-    <t>フェーズ</t>
-  </si>
-  <si>
-    <t>P0-01</t>
-  </si>
-  <si>
-    <t>リソース</t>
-  </si>
-  <si>
-    <t>自己複製ロボットの材料収支</t>
-  </si>
-  <si>
-    <t>初期台数N0=1e5</t>
-  </si>
-  <si>
-    <t>複製率r=0.05/day</t>
-  </si>
-  <si>
-    <t>必要材料M(t)</t>
-  </si>
-  <si>
-    <t>グラフ(t</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> M)</t>
-  </si>
-  <si>
-    <t>単位：kg</t>
-  </si>
-  <si>
-    <t>P0-02</t>
-  </si>
-  <si>
-    <t>構造</t>
-  </si>
-  <si>
-    <t>プロキシマb表面重力下の柱座屈荷重</t>
-  </si>
-  <si>
-    <t>重力g=1.2*9.8[m/s2]</t>
-  </si>
-  <si>
-    <t>ヤング率E=200GPa</t>
-  </si>
-  <si>
-    <t>安全荷重Fs[N]</t>
-  </si>
-  <si>
-    <t>数値出力</t>
-  </si>
-  <si>
-    <t>P1-01</t>
-  </si>
-  <si>
-    <t>軌道</t>
-  </si>
-  <si>
-    <t>プロキシマb表面から低軌道へのΔV</t>
-  </si>
-  <si>
-    <t>惑星半径R=0.145*地球R</t>
-  </si>
-  <si>
-    <t>大気密度ρ</t>
-  </si>
-  <si>
-    <t>ΔV[m/s]</t>
-  </si>
-  <si>
-    <t>数値</t>
-  </si>
-  <si>
-    <t>P1-02</t>
-  </si>
-  <si>
-    <t>太陽光vs核融合のEROI</t>
-  </si>
-  <si>
-    <t>日照強度S=0.05*太陽光</t>
-  </si>
-  <si>
-    <t>核融合効率η=0.2</t>
-  </si>
-  <si>
-    <t>EROI比</t>
-  </si>
-  <si>
-    <t>グラフ(距離依存)</t>
-  </si>
-  <si>
-    <t>P2-01</t>
-  </si>
-  <si>
-    <t>推進</t>
-  </si>
-  <si>
-    <t>レーザーセイルの1g定加速プロファイル</t>
-  </si>
-  <si>
-    <t>目標距離d=20[ly]</t>
-  </si>
-  <si>
-    <t>加速度a=9.8[m/s2]</t>
-  </si>
-  <si>
-    <t>到達時間t[yr]</t>
-  </si>
-  <si>
-    <t>表(静止系・船内時間)</t>
-  </si>
-  <si>
-    <t>P2-02</t>
-  </si>
-  <si>
-    <t>軌道</t>
-  </si>
-  <si>
-    <t>プロキシマb→グリーゼ581の最適軌道</t>
-  </si>
-  <si>
-    <t>出発位置r1=4.24ly</t>
-  </si>
-  <si>
-    <t>到着r2=20ly</t>
-  </si>
-  <si>
-    <t>燃料消費ΔV</t>
-  </si>
-  <si>
-    <t>比較表</t>
-  </si>
-  <si>
-    <t>P3-01</t>
-  </si>
-  <si>
-    <t>通信</t>
-  </si>
-  <si>
-    <t>光通信の往復レイテンシ</t>
-  </si>
-  <si>
-    <t>距離d[ly]</t>
-  </si>
-  <si>
-    <t>光速c</t>
-  </si>
-  <si>
-    <t>遅延時間T[yr]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">グラフ(d vs T)</t>
-  </si>
-  <si>
-    <t>P3-02</t>
-  </si>
-  <si>
-    <t>3星系間の資源輸送最適化</t>
-  </si>
-  <si>
-    <t>各星系の生産量p_i</t>
-  </si>
-  <si>
-    <t>需要量d_i</t>
-  </si>
-  <si>
-    <t>輸送コストc_ij</t>
-  </si>
-  <si>
-    <t>最適フロー</t>
-  </si>
-  <si>
-    <t>線形計画</t>
-  </si>
-  <si>
-    <t>P4-01</t>
-  </si>
-  <si>
-    <t>生態</t>
-  </si>
-  <si>
-    <t>閉鎖生態系の炭素・窒素循環</t>
-  </si>
-  <si>
-    <t>人口N=1e4</t>
-  </si>
-  <si>
-    <t>植物/人間比R</t>
-  </si>
-  <si>
-    <t>物質収支バランス</t>
-  </si>
-  <si>
-    <t>時系列グラフ</t>
-  </si>
-  <si>
-    <t>P4-02</t>
-  </si>
-  <si>
-    <t>人口</t>
-  </si>
-  <si>
-    <t>有効集団サイズと遺伝的多様性</t>
-  </si>
-  <si>
-    <t>初期人口N0</t>
-  </si>
-  <si>
-    <t>世代交代時間Tg</t>
-  </si>
-  <si>
-    <t>ヘテロ接合度H(t)</t>
-  </si>
-  <si>
-    <t>グラフ(t</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> H)</t>
-  </si>
-  <si>
-    <t>WH-01</t>
-  </si>
-  <si>
-    <t>ワームホール</t>
-  </si>
-  <si>
-    <t>必要負エネルギー</t>
-  </si>
-  <si>
-    <t>Morris-Thorneワームホール維持に必要な負のエネルギー</t>
-  </si>
-  <si>
-    <t>ワームホール半径r0[m]</t>
-  </si>
-  <si>
-    <t>総負エネルギーE[J]</t>
-  </si>
-  <si>
-    <t>カシミール効果の利用可能性</t>
-  </si>
-  <si>
-    <t>WH-02</t>
-  </si>
-  <si>
-    <t>生体潮汐力</t>
-  </si>
-  <si>
-    <t>ワームホール通過時の人体への潮汐力評価</t>
-  </si>
-  <si>
-    <t>身長Δr[m]</t>
-  </si>
-  <si>
-    <t>潮汐力[G]</t>
-  </si>
-  <si>
-    <t>許容限界との比較</t>
-  </si>
-  <si>
-    <t>WH-03</t>
-  </si>
-  <si>
-    <t>時間遅延効果</t>
-  </si>
-  <si>
-    <t>ワームホール内部と外部の時間差</t>
-  </si>
-  <si>
-    <t>内部質量M[kg]</t>
-  </si>
-  <si>
-    <t>半径r0[m]</t>
-  </si>
-  <si>
-    <t>時間遅延因子</t>
-  </si>
-  <si>
-    <t>転送中の生体影響</t>
-  </si>
-  <si>
-    <t>HZ-01</t>
-  </si>
-  <si>
-    <t>ハビタブルゾーン</t>
-  </si>
-  <si>
-    <t>期待発見数</t>
-  </si>
-  <si>
-    <t>20光年以内のHZ惑星期待数</t>
-  </si>
-  <si>
-    <t>恒星タイプ別発生率P</t>
-  </si>
-  <si>
-    <t>恒星数N</t>
-  </si>
-  <si>
-    <t>期待発見数[個]</t>
-  </si>
-  <si>
-    <t>観測バイアス補正前</t>
-  </si>
-  <si>
-    <t>HZ-02</t>
-  </si>
-  <si>
-    <t>観測バイアス補正</t>
-  </si>
-  <si>
-    <t>トランジット法・視線速度法の検出確率補正</t>
-  </si>
-  <si>
-    <t>検出確率P_detect</t>
-  </si>
-  <si>
-    <t>観測可能数[個]</t>
-  </si>
-  <si>
-    <t>補正後期待数</t>
-  </si>
-  <si>
-    <t>HZ-03</t>
-  </si>
-  <si>
-    <t>発見時間推定</t>
-  </si>
-  <si>
-    <t>HZ惑星確認に必要な観測期間</t>
-  </si>
-  <si>
-    <t>公転周期T[日]</t>
-  </si>
-  <si>
-    <t>確認トランジット数N_conf</t>
-  </si>
-  <si>
-    <t>確認時間[年]</t>
-  </si>
-  <si>
-    <t>恒星タイプ別</t>
-  </si>
-  <si>
-    <t>HZ-04</t>
-  </si>
-  <si>
-    <t>累積発見確率</t>
-  </si>
-  <si>
-    <t>経過年数に対する累積発見確率</t>
-  </si>
-  <si>
-    <t>特性時間τ[年]</t>
-  </si>
-  <si>
-    <t>観測可能総数N_obs</t>
-  </si>
-  <si>
-    <t>累積発見数[個]</t>
-  </si>
-  <si>
-    <t>グラフ出力</t>
-  </si>
-  <si>
-    <t>DNA-01</t>
-  </si>
-  <si>
-    <t>DNA保存</t>
-  </si>
-  <si>
-    <t>情報容量計算</t>
-  </si>
-  <si>
-    <t>全人類ゲノムの情報容量</t>
-  </si>
-  <si>
-    <t>塩基対数/bp</t>
-  </si>
-  <si>
-    <t>総容量[byte]</t>
-  </si>
-  <si>
-    <t>圧縮効果の検討</t>
-  </si>
-  <si>
-    <t>DNA-02</t>
-  </si>
-  <si>
-    <t>保存媒体質量</t>
-  </si>
-  <si>
-    <t>DNA・シリコン保存の必要質量</t>
-  </si>
-  <si>
-    <t>保存密度[byte/g]</t>
-  </si>
-  <si>
-    <t>必要質量[kg]</t>
-  </si>
-  <si>
-    <t>DNA-03</t>
-  </si>
-  <si>
-    <t>保存期間評価</t>
-  </si>
-  <si>
-    <t>温度別DNA半減期</t>
-  </si>
-  <si>
-    <t>保存温度T[℃]</t>
-  </si>
-  <si>
-    <t>半減期[年]</t>
-  </si>
-  <si>
-    <t>液体窒素・常温</t>
-  </si>
-  <si>
-    <t>DNA-04</t>
-  </si>
-  <si>
-    <t>DNA転送</t>
-  </si>
-  <si>
-    <t>転送時間</t>
-  </si>
-  <si>
-    <t>レーザー通信での転送時間</t>
-  </si>
-  <si>
-    <t>通信速度v[c]</t>
-  </si>
-  <si>
-    <t>転送時間[年]</t>
-  </si>
-  <si>
-    <t>圧縮効果含む</t>
-  </si>
-  <si>
-    <t>DNA-05</t>
-  </si>
-  <si>
-    <t>転送エネルギー</t>
-  </si>
-  <si>
-    <t>情報転送に必要なエネルギー</t>
-  </si>
-  <si>
-    <t>総ビット数N_bits</t>
-  </si>
-  <si>
-    <t>エネルギー/ビット[J]</t>
-  </si>
-  <si>
-    <t>総エネルギー[TWh]</t>
-  </si>
-  <si>
-    <t>理論限界と現実値</t>
-  </si>
-  <si>
-    <t>DNA-06</t>
-  </si>
-  <si>
-    <t>DNA再生</t>
-  </si>
-  <si>
-    <t>技術ロードマップ</t>
-  </si>
-  <si>
-    <t>人工子宮技術の成熟度予測</t>
-  </si>
-  <si>
-    <t>年次</t>
-  </si>
-  <si>
-    <t>技術成熟度レベル</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="3">
+  <fonts count="7">
     <font>
       <sz val="11.000000"/>
       <name val="Calibri"/>
@@ -1084,6 +2562,28 @@
       <sz val="11.000000"/>
       <color indexed="2"/>
       <name val="Calibri"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10.500000"/>
+      <color indexed="2"/>
+      <name val="IPAGothic"/>
+    </font>
+    <font>
+      <sz val="10.500000"/>
+      <color indexed="2"/>
+      <name val="IPAGothic"/>
+    </font>
+    <font>
+      <strike/>
+      <sz val="11.000000"/>
+      <name val="Calibri"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <color theme="1"/>
+      <name val="Arial"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -1112,7 +2612,7 @@
   <cellStyleXfs count="1">
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="10">
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0"/>
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
@@ -1121,10 +2621,27 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf fontId="2" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+      <protection hidden="0" locked="1"/>
+    </xf>
+    <xf fontId="3" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+      <protection hidden="0" locked="1"/>
+    </xf>
+    <xf fontId="4" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf fontId="5" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment readingOrder="0" vertical="top" wrapText="1"/>
+    </xf>
+    <xf fontId="5" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf fontId="1" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf fontId="6" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1586,6 +3103,2250 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac">
   <sheetFormatPr baseColWidth="9" defaultRowHeight="14.25"/>
   <cols>
+    <col min="1" max="16384" style="1" width="10.28125"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28.5">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2" ht="128.25">
+      <c r="A2" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="3" ht="99.75">
+      <c r="A3" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="G3" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="H3" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="4" ht="128.25">
+      <c r="A4" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="G4" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="H4" s="1" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="5" ht="142.5">
+      <c r="A5" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="F5" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="G5" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="H5" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="I5" s="1"/>
+    </row>
+    <row r="6" ht="142.5">
+      <c r="A6" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="F6" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="G6" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="H6" s="1" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="7" ht="128.25">
+      <c r="A7" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="F7" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="G7" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="H7" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="I7" s="1" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="8" ht="114">
+      <c r="A8" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="F8" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="G8" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="H8" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="I8" s="1" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="9" ht="114">
+      <c r="A9" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="E9" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="F9" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="G9" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="H9" s="1" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="10" ht="114">
+      <c r="A10" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="E10" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="F10" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="G10" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="H10" s="1" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="11" ht="114">
+      <c r="A11" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="E11" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="F11" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="G11" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="H11" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="I11" s="2"/>
+    </row>
+    <row r="12" ht="114">
+      <c r="A12" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="E12" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="F12" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="G12" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="H12" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="I12" s="2"/>
+      <c r="J12" s="1"/>
+    </row>
+    <row r="13" ht="128.25">
+      <c r="A13" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="D13" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="E13" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="F13" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="G13" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="H13" s="1" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="14" ht="99.75">
+      <c r="A14" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="D14" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="E14" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="F14" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="G14" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="H14" s="1" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="15" ht="71.25">
+      <c r="A15" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="D15" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="E15" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="F15" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="G15" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="H15" s="1" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="16" ht="142.5">
+      <c r="A16" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="D16" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="E16" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="F16" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="G16" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="H16" s="1" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="17" ht="99.75">
+      <c r="A17" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="D17" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="E17" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="F17" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="G17" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="H17" s="1" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="18" ht="142.5">
+      <c r="A18" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="D18" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="E18" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="F18" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="G18" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="H18" s="1" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="19" ht="142.5">
+      <c r="A19" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C19" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="D19" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="E19" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="F19" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="G19" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="H19" s="1" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="20" ht="171">
+      <c r="A20" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C20" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="D20" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="E20" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="F20" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="G20" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="H20" s="1" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="21" ht="156.75">
+      <c r="A21" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C21" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="D21" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="E21" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="F21" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="G21" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="H21" s="1" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="22" ht="51">
+      <c r="A22" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="B22" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="C22" s="4" t="s">
+        <v>139</v>
+      </c>
+      <c r="D22" s="4" t="s">
+        <v>140</v>
+      </c>
+      <c r="E22" s="4" t="s">
+        <v>141</v>
+      </c>
+    </row>
+  </sheetData>
+  <printOptions headings="0" gridLines="0"/>
+  <pageMargins left="0.70078740157480324" right="0.70078740157480324" top="0.75196850393700787" bottom="0.75196850393700787" header="0.29999999999999999" footer="0.29999999999999999"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" cellComments="none" useFirstPageNumber="0" errors="displayed" horizontalDpi="600" verticalDpi="600" copies="1"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac">
+  <sheetFormatPr baseColWidth="9" defaultRowHeight="14.25"/>
+  <cols>
+    <col min="1" max="16384" style="1" width="10.28125"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28.5">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2" ht="71.25">
+      <c r="A2" s="1" t="s">
+        <v>254</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>255</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>256</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>257</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>258</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>259</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>260</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>261</v>
+      </c>
+      <c r="I2" s="1" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="3" ht="85.5">
+      <c r="A3" s="1" t="s">
+        <v>263</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>255</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>256</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>264</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>265</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>266</v>
+      </c>
+      <c r="G3" s="1" t="s">
+        <v>267</v>
+      </c>
+      <c r="H3" s="1" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="4" ht="99.75">
+      <c r="A4" s="1" t="s">
+        <v>269</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>255</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>270</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>271</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>272</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>273</v>
+      </c>
+      <c r="G4" s="1" t="s">
+        <v>274</v>
+      </c>
+      <c r="H4" s="1" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="5" ht="99.75">
+      <c r="A5" s="1" t="s">
+        <v>276</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>255</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>270</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>277</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>278</v>
+      </c>
+      <c r="F5" s="1" t="s">
+        <v>279</v>
+      </c>
+      <c r="G5" s="1" t="s">
+        <v>280</v>
+      </c>
+      <c r="H5" s="1" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="6" ht="85.5">
+      <c r="A6" s="1" t="s">
+        <v>282</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>255</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>283</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>284</v>
+      </c>
+      <c r="F6" s="1" t="s">
+        <v>285</v>
+      </c>
+      <c r="G6" s="1" t="s">
+        <v>286</v>
+      </c>
+      <c r="H6" s="1" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="7" ht="71.25">
+      <c r="A7" s="1" t="s">
+        <v>288</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>255</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>289</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>290</v>
+      </c>
+      <c r="F7" s="1" t="s">
+        <v>291</v>
+      </c>
+      <c r="G7" s="1" t="s">
+        <v>292</v>
+      </c>
+      <c r="H7" s="1" t="s">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="8" ht="71.25">
+      <c r="A8" s="1" t="s">
+        <v>294</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>255</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>295</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>296</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>297</v>
+      </c>
+      <c r="F8" s="1" t="s">
+        <v>298</v>
+      </c>
+      <c r="G8" s="1" t="s">
+        <v>299</v>
+      </c>
+      <c r="H8" s="1" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="9" ht="99.75">
+      <c r="A9" s="1" t="s">
+        <v>301</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>255</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>295</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>302</v>
+      </c>
+      <c r="E9" s="1" t="s">
+        <v>303</v>
+      </c>
+      <c r="F9" s="1" t="s">
+        <v>304</v>
+      </c>
+      <c r="G9" s="1" t="s">
+        <v>305</v>
+      </c>
+      <c r="H9" s="1" t="s">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="10" ht="99.75">
+      <c r="A10" s="1" t="s">
+        <v>307</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>255</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>308</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>309</v>
+      </c>
+      <c r="E10" s="1" t="s">
+        <v>310</v>
+      </c>
+      <c r="F10" s="1" t="s">
+        <v>311</v>
+      </c>
+      <c r="G10" s="1" t="s">
+        <v>312</v>
+      </c>
+      <c r="H10" s="1" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="11" ht="85.5">
+      <c r="A11" s="1" t="s">
+        <v>314</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>255</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>308</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>315</v>
+      </c>
+      <c r="E11" s="1" t="s">
+        <v>316</v>
+      </c>
+      <c r="F11" s="1" t="s">
+        <v>317</v>
+      </c>
+      <c r="G11" s="1" t="s">
+        <v>318</v>
+      </c>
+      <c r="H11" s="1" t="s">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="12" ht="85.5">
+      <c r="A12" s="1" t="s">
+        <v>320</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>255</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>321</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>322</v>
+      </c>
+      <c r="E12" s="1" t="s">
+        <v>323</v>
+      </c>
+      <c r="F12" s="1" t="s">
+        <v>324</v>
+      </c>
+      <c r="G12" s="1" t="s">
+        <v>325</v>
+      </c>
+      <c r="H12" s="1" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="13" ht="71.25">
+      <c r="A13" s="1" t="s">
+        <v>327</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>255</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>321</v>
+      </c>
+      <c r="D13" s="1" t="s">
+        <v>328</v>
+      </c>
+      <c r="E13" s="1" t="s">
+        <v>329</v>
+      </c>
+      <c r="F13" s="1" t="s">
+        <v>330</v>
+      </c>
+      <c r="G13" s="1" t="s">
+        <v>331</v>
+      </c>
+      <c r="H13" s="1" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="14" ht="71.25">
+      <c r="A14" s="1" t="s">
+        <v>333</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>255</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>334</v>
+      </c>
+      <c r="D14" s="1" t="s">
+        <v>335</v>
+      </c>
+      <c r="E14" s="1" t="s">
+        <v>336</v>
+      </c>
+      <c r="F14" s="1" t="s">
+        <v>337</v>
+      </c>
+      <c r="G14" s="1" t="s">
+        <v>338</v>
+      </c>
+      <c r="H14" s="1" t="s">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="15" ht="71.25">
+      <c r="A15" s="1" t="s">
+        <v>340</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>255</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>334</v>
+      </c>
+      <c r="D15" s="1" t="s">
+        <v>341</v>
+      </c>
+      <c r="E15" s="1" t="s">
+        <v>342</v>
+      </c>
+      <c r="F15" s="1" t="s">
+        <v>343</v>
+      </c>
+      <c r="G15" s="1" t="s">
+        <v>344</v>
+      </c>
+      <c r="H15" s="1" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="16" ht="85.5">
+      <c r="A16" s="1" t="s">
+        <v>346</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>255</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>347</v>
+      </c>
+      <c r="D16" s="1" t="s">
+        <v>348</v>
+      </c>
+      <c r="E16" s="1" t="s">
+        <v>349</v>
+      </c>
+      <c r="F16" s="1" t="s">
+        <v>350</v>
+      </c>
+      <c r="G16" s="1" t="s">
+        <v>351</v>
+      </c>
+      <c r="H16" s="1" t="s">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="17" ht="85.5">
+      <c r="A17" s="1" t="s">
+        <v>353</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>255</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>347</v>
+      </c>
+      <c r="D17" s="1" t="s">
+        <v>354</v>
+      </c>
+      <c r="E17" s="1" t="s">
+        <v>355</v>
+      </c>
+      <c r="F17" s="1" t="s">
+        <v>356</v>
+      </c>
+      <c r="G17" s="1" t="s">
+        <v>357</v>
+      </c>
+      <c r="H17" s="1" t="s">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="18" ht="85.5">
+      <c r="A18" s="1" t="s">
+        <v>359</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>255</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>360</v>
+      </c>
+      <c r="D18" s="1" t="s">
+        <v>361</v>
+      </c>
+      <c r="E18" s="1" t="s">
+        <v>362</v>
+      </c>
+      <c r="F18" s="1" t="s">
+        <v>363</v>
+      </c>
+      <c r="G18" s="1" t="s">
+        <v>364</v>
+      </c>
+      <c r="H18" s="1" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="19" ht="99.75">
+      <c r="A19" s="1" t="s">
+        <v>366</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>255</v>
+      </c>
+      <c r="C19" s="1" t="s">
+        <v>360</v>
+      </c>
+      <c r="D19" s="1" t="s">
+        <v>367</v>
+      </c>
+      <c r="E19" s="1" t="s">
+        <v>368</v>
+      </c>
+      <c r="F19" s="1" t="s">
+        <v>369</v>
+      </c>
+      <c r="G19" s="1" t="s">
+        <v>370</v>
+      </c>
+      <c r="H19" s="1" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="20" ht="99.75">
+      <c r="A20" s="1" t="s">
+        <v>372</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>255</v>
+      </c>
+      <c r="C20" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="D20" s="1" t="s">
+        <v>373</v>
+      </c>
+      <c r="E20" s="1" t="s">
+        <v>374</v>
+      </c>
+      <c r="F20" s="1" t="s">
+        <v>375</v>
+      </c>
+      <c r="G20" s="1" t="s">
+        <v>376</v>
+      </c>
+      <c r="H20" s="1" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="21" ht="114">
+      <c r="A21" s="1" t="s">
+        <v>378</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>255</v>
+      </c>
+      <c r="C21" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="D21" s="1" t="s">
+        <v>379</v>
+      </c>
+      <c r="E21" s="1" t="s">
+        <v>380</v>
+      </c>
+      <c r="F21" s="1" t="s">
+        <v>381</v>
+      </c>
+      <c r="G21" s="1" t="s">
+        <v>382</v>
+      </c>
+      <c r="H21" s="1" t="s">
+        <v>383</v>
+      </c>
+    </row>
+    <row r="22" ht="51">
+      <c r="A22" s="3" t="s">
+        <v>384</v>
+      </c>
+      <c r="B22" s="4" t="s">
+        <v>385</v>
+      </c>
+      <c r="C22" s="3" t="s">
+        <v>386</v>
+      </c>
+      <c r="D22" s="4" t="s">
+        <v>387</v>
+      </c>
+      <c r="E22" s="4" t="s">
+        <v>388</v>
+      </c>
+      <c r="F22" s="4" t="s">
+        <v>141</v>
+      </c>
+      <c r="G22" s="4" t="s">
+        <v>389</v>
+      </c>
+    </row>
+    <row r="23" ht="14.25">
+      <c r="A23" s="1"/>
+      <c r="B23" s="1"/>
+      <c r="C23" s="1"/>
+      <c r="D23" s="1"/>
+      <c r="E23" s="1"/>
+      <c r="F23" s="1"/>
+      <c r="G23" s="1"/>
+    </row>
+  </sheetData>
+  <printOptions headings="0" gridLines="0"/>
+  <pageMargins left="0.70078740157480324" right="0.70078740157480324" top="0.75196850393700787" bottom="0.75196850393700787" header="0.29999999999999999" footer="0.29999999999999999"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" cellComments="none" useFirstPageNumber="0" errors="displayed" horizontalDpi="600" verticalDpi="600" copies="1"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac">
+  <sheetFormatPr baseColWidth="9" defaultRowHeight="14.25"/>
+  <cols>
+    <col min="1" max="7" style="1" width="10.28125"/>
+    <col customWidth="1" min="8" max="8" style="1" width="16.57421875"/>
+    <col customWidth="1" min="9" max="9" style="1" width="19.421875"/>
+    <col customWidth="1" min="10" max="10" style="1" width="15.57421875"/>
+    <col customWidth="1" min="11" max="11" style="1" width="13.8515625"/>
+    <col min="12" max="16384" style="1" width="10.28125"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28.5">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2" ht="57">
+      <c r="A2" s="1" t="s">
+        <v>390</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>391</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>392</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>393</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>394</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>395</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>396</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>397</v>
+      </c>
+      <c r="I2" s="1" t="s">
+        <v>398</v>
+      </c>
+      <c r="J2" s="1"/>
+    </row>
+    <row r="3" ht="57">
+      <c r="A3" s="1" t="s">
+        <v>399</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>391</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>400</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>401</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>402</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>403</v>
+      </c>
+      <c r="G3" s="1" t="s">
+        <v>404</v>
+      </c>
+      <c r="H3" s="1" t="s">
+        <v>405</v>
+      </c>
+    </row>
+    <row r="4" ht="71.25">
+      <c r="A4" s="1" t="s">
+        <v>406</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>407</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>408</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>409</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>410</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>411</v>
+      </c>
+      <c r="G4" s="1" t="s">
+        <v>412</v>
+      </c>
+      <c r="H4" s="1" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="5" ht="71.25">
+      <c r="A5" s="1" t="s">
+        <v>414</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>407</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>415</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>416</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>417</v>
+      </c>
+      <c r="F5" s="1" t="s">
+        <v>418</v>
+      </c>
+      <c r="G5" s="1" t="s">
+        <v>419</v>
+      </c>
+      <c r="H5" s="1" t="s">
+        <v>420</v>
+      </c>
+    </row>
+    <row r="6" ht="71.25">
+      <c r="A6" s="1" t="s">
+        <v>421</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>422</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>423</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>424</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>425</v>
+      </c>
+      <c r="F6" s="1" t="s">
+        <v>426</v>
+      </c>
+      <c r="G6" s="1" t="s">
+        <v>427</v>
+      </c>
+      <c r="H6" s="1" t="s">
+        <v>428</v>
+      </c>
+      <c r="I6" s="1" t="s">
+        <v>429</v>
+      </c>
+      <c r="J6" s="1" t="s">
+        <v>430</v>
+      </c>
+      <c r="K6" s="1"/>
+    </row>
+    <row r="7" ht="57">
+      <c r="A7" s="1" t="s">
+        <v>431</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>422</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>432</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>433</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>434</v>
+      </c>
+      <c r="F7" s="1" t="s">
+        <v>435</v>
+      </c>
+      <c r="G7" s="1" t="s">
+        <v>436</v>
+      </c>
+      <c r="H7" s="1" t="s">
+        <v>437</v>
+      </c>
+    </row>
+    <row r="8" ht="71.25">
+      <c r="A8" s="1" t="s">
+        <v>438</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>439</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>440</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>441</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>442</v>
+      </c>
+      <c r="F8" s="1" t="s">
+        <v>443</v>
+      </c>
+      <c r="G8" s="1" t="s">
+        <v>444</v>
+      </c>
+      <c r="H8" s="1" t="s">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="9" ht="57">
+      <c r="A9" s="1" t="s">
+        <v>446</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>439</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>447</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>448</v>
+      </c>
+      <c r="E9" s="1" t="s">
+        <v>449</v>
+      </c>
+      <c r="F9" s="1" t="s">
+        <v>450</v>
+      </c>
+      <c r="G9" s="1" t="s">
+        <v>451</v>
+      </c>
+      <c r="H9" s="1" t="s">
+        <v>452</v>
+      </c>
+    </row>
+    <row r="10" ht="57">
+      <c r="A10" s="1" t="s">
+        <v>453</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>439</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>454</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>455</v>
+      </c>
+      <c r="E10" s="1" t="s">
+        <v>456</v>
+      </c>
+      <c r="F10" s="1" t="s">
+        <v>457</v>
+      </c>
+      <c r="G10" s="1" t="s">
+        <v>458</v>
+      </c>
+      <c r="H10" s="1" t="s">
+        <v>459</v>
+      </c>
+    </row>
+    <row r="11" ht="42.75">
+      <c r="A11" s="1" t="s">
+        <v>460</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>461</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>462</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>463</v>
+      </c>
+      <c r="E11" s="1" t="s">
+        <v>464</v>
+      </c>
+      <c r="F11" s="1" t="s">
+        <v>465</v>
+      </c>
+      <c r="G11" s="1" t="s">
+        <v>466</v>
+      </c>
+      <c r="H11" s="1" t="s">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="12" ht="71.25">
+      <c r="A12" s="1" t="s">
+        <v>468</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>461</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>469</v>
+      </c>
+      <c r="E12" s="1" t="s">
+        <v>470</v>
+      </c>
+      <c r="F12" s="1" t="s">
+        <v>471</v>
+      </c>
+      <c r="G12" s="1" t="s">
+        <v>472</v>
+      </c>
+      <c r="H12" s="1" t="s">
+        <v>473</v>
+      </c>
+    </row>
+    <row r="13" ht="71.25">
+      <c r="A13" s="1" t="s">
+        <v>474</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>461</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>475</v>
+      </c>
+      <c r="D13" s="1" t="s">
+        <v>476</v>
+      </c>
+      <c r="E13" s="1" t="s">
+        <v>477</v>
+      </c>
+      <c r="F13" s="1" t="s">
+        <v>478</v>
+      </c>
+      <c r="G13" s="1" t="s">
+        <v>479</v>
+      </c>
+      <c r="H13" s="1" t="s">
+        <v>480</v>
+      </c>
+    </row>
+  </sheetData>
+  <printOptions headings="0" gridLines="0"/>
+  <pageMargins left="0.70078740157480324" right="0.70078740157480324" top="0.75196850393700787" bottom="0.75196850393700787" header="0.29999999999999999" footer="0.29999999999999999"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" cellComments="none" useFirstPageNumber="0" errors="displayed" horizontalDpi="600" verticalDpi="600" copies="1"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac">
+  <sheetFormatPr baseColWidth="9" defaultRowHeight="14.25"/>
+  <cols>
+    <col min="1" max="4" style="1" width="10.28125"/>
+    <col customWidth="1" min="5" max="5" style="1" width="14.421875"/>
+    <col min="6" max="16384" style="1" width="10.28125"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="14.25">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2" ht="99.75">
+      <c r="A2" s="1" t="s">
+        <v>481</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>422</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>482</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>483</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>484</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>485</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>486</v>
+      </c>
+    </row>
+    <row r="3" ht="71.25">
+      <c r="A3" s="1" t="s">
+        <v>487</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>422</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>488</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>489</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>490</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>484</v>
+      </c>
+      <c r="G3" s="1" t="s">
+        <v>491</v>
+      </c>
+      <c r="H3" s="1" t="s">
+        <v>492</v>
+      </c>
+    </row>
+    <row r="4" ht="57">
+      <c r="A4" s="1" t="s">
+        <v>493</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>422</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>494</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>495</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>496</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>497</v>
+      </c>
+      <c r="G4" s="1" t="s">
+        <v>498</v>
+      </c>
+      <c r="H4" s="1" t="s">
+        <v>499</v>
+      </c>
+    </row>
+    <row r="5" ht="42.75">
+      <c r="A5" s="1" t="s">
+        <v>500</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>501</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>502</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>503</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>504</v>
+      </c>
+      <c r="F5" s="1" t="s">
+        <v>505</v>
+      </c>
+      <c r="G5" s="1" t="s">
+        <v>506</v>
+      </c>
+      <c r="H5" s="1" t="s">
+        <v>507</v>
+      </c>
+      <c r="I5" s="1" t="s">
+        <v>508</v>
+      </c>
+    </row>
+    <row r="6" ht="71.25">
+      <c r="A6" s="1" t="s">
+        <v>509</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>501</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>510</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>511</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>512</v>
+      </c>
+      <c r="F6" s="1" t="s">
+        <v>513</v>
+      </c>
+      <c r="G6" s="1" t="s">
+        <v>514</v>
+      </c>
+    </row>
+    <row r="7" ht="57">
+      <c r="A7" s="1" t="s">
+        <v>515</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>501</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>516</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>517</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>518</v>
+      </c>
+      <c r="F7" s="1" t="s">
+        <v>519</v>
+      </c>
+      <c r="G7" s="1" t="s">
+        <v>520</v>
+      </c>
+      <c r="H7" s="1" t="s">
+        <v>521</v>
+      </c>
+    </row>
+    <row r="8" ht="57">
+      <c r="A8" s="1" t="s">
+        <v>522</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>501</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>523</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>524</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>525</v>
+      </c>
+      <c r="F8" s="1" t="s">
+        <v>526</v>
+      </c>
+      <c r="G8" s="1" t="s">
+        <v>527</v>
+      </c>
+      <c r="H8" s="1" t="s">
+        <v>528</v>
+      </c>
+    </row>
+    <row r="9" ht="114">
+      <c r="A9" s="1" t="s">
+        <v>529</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>530</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>531</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>532</v>
+      </c>
+      <c r="E9" s="1" t="s">
+        <v>533</v>
+      </c>
+      <c r="F9" s="1" t="s">
+        <v>534</v>
+      </c>
+      <c r="G9" s="1" t="s">
+        <v>535</v>
+      </c>
+      <c r="H9" s="1" t="s">
+        <v>536</v>
+      </c>
+      <c r="I9" s="1" t="s">
+        <v>537</v>
+      </c>
+    </row>
+    <row r="10" ht="99.75">
+      <c r="A10" s="1" t="s">
+        <v>538</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>530</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>539</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>540</v>
+      </c>
+      <c r="E10" s="1" t="s">
+        <v>541</v>
+      </c>
+      <c r="F10" s="1" t="s">
+        <v>542</v>
+      </c>
+      <c r="G10" s="1" t="s">
+        <v>543</v>
+      </c>
+      <c r="H10" s="1" t="s">
+        <v>544</v>
+      </c>
+    </row>
+    <row r="11" s="5" customFormat="1" ht="99.75">
+      <c r="A11" s="5" t="s">
+        <v>545</v>
+      </c>
+      <c r="B11" s="5" t="s">
+        <v>530</v>
+      </c>
+      <c r="C11" s="5" t="s">
+        <v>546</v>
+      </c>
+      <c r="D11" s="5" t="s">
+        <v>547</v>
+      </c>
+      <c r="E11" s="5" t="s">
+        <v>548</v>
+      </c>
+      <c r="F11" s="5" t="s">
+        <v>549</v>
+      </c>
+      <c r="G11" s="5" t="s">
+        <v>550</v>
+      </c>
+      <c r="H11" s="5" t="s">
+        <v>551</v>
+      </c>
+    </row>
+    <row r="12" ht="85.5">
+      <c r="A12" s="1" t="s">
+        <v>552</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>530</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>553</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>554</v>
+      </c>
+      <c r="E12" s="1" t="s">
+        <v>555</v>
+      </c>
+      <c r="F12" s="1" t="s">
+        <v>556</v>
+      </c>
+      <c r="G12" s="1" t="s">
+        <v>557</v>
+      </c>
+      <c r="H12" s="1" t="s">
+        <v>558</v>
+      </c>
+    </row>
+    <row r="13" ht="85.5">
+      <c r="A13" s="1" t="s">
+        <v>559</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>530</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>560</v>
+      </c>
+      <c r="D13" s="1" t="s">
+        <v>561</v>
+      </c>
+      <c r="E13" s="1" t="s">
+        <v>562</v>
+      </c>
+      <c r="F13" s="1" t="s">
+        <v>563</v>
+      </c>
+      <c r="G13" s="1" t="s">
+        <v>564</v>
+      </c>
+      <c r="H13" s="1" t="s">
+        <v>565</v>
+      </c>
+    </row>
+    <row r="14" s="2" customFormat="1" ht="42.75">
+      <c r="A14" s="2" t="s">
+        <v>566</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>567</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>568</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>569</v>
+      </c>
+      <c r="E14" s="2" t="s">
+        <v>570</v>
+      </c>
+      <c r="F14" s="2" t="s">
+        <v>571</v>
+      </c>
+      <c r="G14" s="2" t="s">
+        <v>572</v>
+      </c>
+      <c r="I14" s="2" t="s">
+        <v>573</v>
+      </c>
+      <c r="J14" s="8" t="s">
+        <v>574</v>
+      </c>
+    </row>
+  </sheetData>
+  <printOptions headings="0" gridLines="0"/>
+  <pageMargins left="0.70078740157480324" right="0.70078740157480324" top="0.75196850393700787" bottom="0.75196850393700787" header="0.29999999999999999" footer="0.29999999999999999"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" cellComments="none" useFirstPageNumber="0" errors="displayed" horizontalDpi="600" verticalDpi="600" copies="1"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac">
+  <sheetFormatPr baseColWidth="9" defaultRowHeight="14.25"/>
+  <cols>
+    <col min="1" max="16384" style="1" width="10.28125"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>575</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2" ht="57">
+      <c r="A2" s="1" t="s">
+        <v>576</v>
+      </c>
+      <c r="B2" s="1">
+        <v>0</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>577</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>578</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>579</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>580</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>581</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>582</v>
+      </c>
+      <c r="I2" s="1" t="s">
+        <v>583</v>
+      </c>
+      <c r="J2" s="1" t="s">
+        <v>584</v>
+      </c>
+    </row>
+    <row r="3" ht="71.25">
+      <c r="A3" s="1" t="s">
+        <v>585</v>
+      </c>
+      <c r="B3" s="1">
+        <v>0</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>586</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>587</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>588</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>589</v>
+      </c>
+      <c r="G3" s="1" t="s">
+        <v>590</v>
+      </c>
+      <c r="H3" s="1" t="s">
+        <v>591</v>
+      </c>
+    </row>
+    <row r="4" ht="57">
+      <c r="A4" s="1" t="s">
+        <v>592</v>
+      </c>
+      <c r="B4" s="1">
+        <v>1</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>593</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>594</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>595</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>596</v>
+      </c>
+      <c r="G4" s="1" t="s">
+        <v>597</v>
+      </c>
+      <c r="H4" s="1" t="s">
+        <v>598</v>
+      </c>
+    </row>
+    <row r="5" ht="42.75">
+      <c r="A5" s="1" t="s">
+        <v>599</v>
+      </c>
+      <c r="B5" s="1">
+        <v>1</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>600</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>601</v>
+      </c>
+      <c r="F5" s="1" t="s">
+        <v>602</v>
+      </c>
+      <c r="G5" s="1" t="s">
+        <v>603</v>
+      </c>
+      <c r="H5" s="1" t="s">
+        <v>604</v>
+      </c>
+    </row>
+    <row r="6" ht="71.25">
+      <c r="A6" s="1" t="s">
+        <v>605</v>
+      </c>
+      <c r="B6" s="1">
+        <v>2</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>606</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>607</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>608</v>
+      </c>
+      <c r="F6" s="1" t="s">
+        <v>609</v>
+      </c>
+      <c r="G6" s="1" t="s">
+        <v>610</v>
+      </c>
+      <c r="H6" s="1" t="s">
+        <v>611</v>
+      </c>
+    </row>
+    <row r="7" ht="57">
+      <c r="A7" s="1" t="s">
+        <v>612</v>
+      </c>
+      <c r="B7" s="1">
+        <v>2</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>613</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>614</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>615</v>
+      </c>
+      <c r="F7" s="1" t="s">
+        <v>616</v>
+      </c>
+      <c r="G7" s="1" t="s">
+        <v>617</v>
+      </c>
+      <c r="H7" s="1" t="s">
+        <v>618</v>
+      </c>
+    </row>
+    <row r="8" ht="42.75">
+      <c r="A8" s="1" t="s">
+        <v>619</v>
+      </c>
+      <c r="B8" s="1">
+        <v>3</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>620</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>621</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>622</v>
+      </c>
+      <c r="F8" s="1" t="s">
+        <v>623</v>
+      </c>
+      <c r="G8" s="1" t="s">
+        <v>624</v>
+      </c>
+      <c r="H8" s="1" t="s">
+        <v>625</v>
+      </c>
+    </row>
+    <row r="9" ht="42.75">
+      <c r="A9" s="1" t="s">
+        <v>626</v>
+      </c>
+      <c r="B9" s="1">
+        <v>3</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>627</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>628</v>
+      </c>
+      <c r="E9" s="1" t="s">
+        <v>629</v>
+      </c>
+      <c r="F9" s="1" t="s">
+        <v>630</v>
+      </c>
+      <c r="G9" s="1" t="s">
+        <v>631</v>
+      </c>
+      <c r="H9" s="1" t="s">
+        <v>632</v>
+      </c>
+      <c r="I9" s="1" t="s">
+        <v>633</v>
+      </c>
+    </row>
+    <row r="10" ht="57">
+      <c r="A10" s="1" t="s">
+        <v>634</v>
+      </c>
+      <c r="B10" s="1">
+        <v>4</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>635</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>636</v>
+      </c>
+      <c r="E10" s="1" t="s">
+        <v>637</v>
+      </c>
+      <c r="F10" s="1" t="s">
+        <v>638</v>
+      </c>
+      <c r="G10" s="1" t="s">
+        <v>639</v>
+      </c>
+      <c r="H10" s="1" t="s">
+        <v>640</v>
+      </c>
+    </row>
+    <row r="11" ht="57">
+      <c r="A11" s="1" t="s">
+        <v>641</v>
+      </c>
+      <c r="B11" s="1">
+        <v>4</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>642</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>643</v>
+      </c>
+      <c r="E11" s="1" t="s">
+        <v>644</v>
+      </c>
+      <c r="F11" s="1" t="s">
+        <v>645</v>
+      </c>
+      <c r="G11" s="1" t="s">
+        <v>646</v>
+      </c>
+      <c r="H11" s="1" t="s">
+        <v>647</v>
+      </c>
+      <c r="I11" s="1" t="s">
+        <v>648</v>
+      </c>
+    </row>
+  </sheetData>
+  <printOptions headings="0" gridLines="0"/>
+  <pageMargins left="0.70078740157480324" right="0.70078740157480324" top="0.75196850393700787" bottom="0.75196850393700787" header="0.29999999999999999" footer="0.29999999999999999"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" cellComments="none" useFirstPageNumber="0" errors="displayed" horizontalDpi="600" verticalDpi="600" copies="1"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac">
+  <sheetFormatPr baseColWidth="9" defaultRowHeight="14.25"/>
+  <cols>
     <col min="1" max="8" style="1" width="10.28125"/>
     <col customWidth="1" min="9" max="9" style="1" width="13.7109375"/>
     <col min="10" max="16384" style="1" width="10.28125"/>
@@ -1619,682 +5380,682 @@
     </row>
     <row r="2" ht="57">
       <c r="A2" s="1" t="s">
-        <v>8</v>
+        <v>649</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>9</v>
+        <v>650</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>10</v>
+        <v>651</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>11</v>
+        <v>652</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>12</v>
+        <v>653</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>13</v>
+        <v>654</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>14</v>
+        <v>655</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>15</v>
+        <v>656</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>16</v>
+        <v>657</v>
       </c>
     </row>
     <row r="3" ht="57">
       <c r="A3" s="1" t="s">
-        <v>17</v>
+        <v>658</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>9</v>
+        <v>650</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>18</v>
+        <v>659</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>19</v>
+        <v>660</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>20</v>
+        <v>661</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>21</v>
+        <v>662</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>22</v>
+        <v>663</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>23</v>
+        <v>664</v>
       </c>
     </row>
     <row r="4" ht="57">
       <c r="A4" s="1" t="s">
-        <v>24</v>
+        <v>665</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>9</v>
+        <v>650</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>25</v>
+        <v>666</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>26</v>
+        <v>667</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>27</v>
+        <v>668</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>28</v>
+        <v>669</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>29</v>
+        <v>670</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>30</v>
+        <v>671</v>
       </c>
     </row>
     <row r="5" ht="57">
       <c r="A5" s="1" t="s">
-        <v>31</v>
+        <v>672</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>9</v>
+        <v>650</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>32</v>
+        <v>627</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>33</v>
+        <v>673</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>34</v>
+        <v>674</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>35</v>
+        <v>675</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>36</v>
+        <v>676</v>
       </c>
       <c r="H5" s="1" t="s">
-        <v>37</v>
+        <v>677</v>
       </c>
     </row>
     <row r="6" ht="42.75">
       <c r="A6" s="1" t="s">
-        <v>38</v>
+        <v>678</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>9</v>
+        <v>650</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>39</v>
+        <v>454</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>40</v>
+        <v>679</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>41</v>
+        <v>680</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>42</v>
+        <v>681</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>43</v>
+        <v>682</v>
       </c>
       <c r="H6" s="1" t="s">
-        <v>44</v>
+        <v>683</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>45</v>
+        <v>684</v>
       </c>
     </row>
     <row r="7" ht="57">
       <c r="A7" s="1" t="s">
-        <v>46</v>
+        <v>685</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>9</v>
+        <v>650</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>47</v>
+        <v>686</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>48</v>
+        <v>687</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>49</v>
+        <v>688</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>50</v>
+        <v>689</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>51</v>
+        <v>690</v>
       </c>
       <c r="H7" s="1" t="s">
-        <v>52</v>
+        <v>691</v>
       </c>
     </row>
     <row r="8" ht="42.75">
       <c r="A8" s="1" t="s">
-        <v>53</v>
+        <v>692</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>54</v>
+        <v>693</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>32</v>
+        <v>627</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>55</v>
+        <v>694</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>56</v>
+        <v>695</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>57</v>
+        <v>696</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>58</v>
+        <v>697</v>
       </c>
       <c r="H8" s="1" t="s">
-        <v>59</v>
+        <v>698</v>
       </c>
     </row>
     <row r="9" ht="57">
       <c r="A9" s="1" t="s">
-        <v>60</v>
+        <v>699</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>54</v>
+        <v>693</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>61</v>
+        <v>700</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>62</v>
+        <v>701</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>63</v>
+        <v>702</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>64</v>
+        <v>703</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>65</v>
+        <v>704</v>
       </c>
       <c r="H9" s="1" t="s">
-        <v>66</v>
+        <v>705</v>
       </c>
     </row>
     <row r="10" ht="42.75">
       <c r="A10" s="1" t="s">
-        <v>67</v>
+        <v>706</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>54</v>
+        <v>693</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>68</v>
+        <v>707</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>69</v>
+        <v>708</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>70</v>
+        <v>709</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>71</v>
+        <v>710</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>72</v>
+        <v>711</v>
       </c>
       <c r="H10" s="1" t="s">
-        <v>73</v>
+        <v>712</v>
       </c>
     </row>
     <row r="11" ht="57">
       <c r="A11" s="1" t="s">
-        <v>74</v>
+        <v>713</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>54</v>
+        <v>693</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>75</v>
+        <v>714</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>76</v>
+        <v>715</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>77</v>
+        <v>716</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>78</v>
+        <v>717</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>79</v>
+        <v>718</v>
       </c>
       <c r="H11" s="1" t="s">
-        <v>80</v>
+        <v>719</v>
       </c>
     </row>
     <row r="12" ht="57">
       <c r="A12" s="1" t="s">
-        <v>81</v>
+        <v>720</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>54</v>
+        <v>693</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>82</v>
+        <v>721</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>83</v>
+        <v>722</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>84</v>
+        <v>723</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>85</v>
+        <v>724</v>
       </c>
       <c r="G12" s="1" t="s">
-        <v>86</v>
+        <v>725</v>
       </c>
       <c r="H12" s="1" t="s">
-        <v>87</v>
+        <v>726</v>
       </c>
     </row>
     <row r="13" ht="57">
       <c r="A13" s="1" t="s">
-        <v>88</v>
+        <v>727</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>54</v>
+        <v>693</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>89</v>
+        <v>728</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>90</v>
+        <v>729</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>91</v>
+        <v>730</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>92</v>
+        <v>731</v>
       </c>
       <c r="G13" s="1" t="s">
-        <v>93</v>
+        <v>732</v>
       </c>
       <c r="H13" s="1" t="s">
-        <v>94</v>
+        <v>572</v>
       </c>
     </row>
     <row r="14" ht="60">
       <c r="A14" s="1" t="s">
-        <v>95</v>
+        <v>733</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>96</v>
+        <v>734</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>97</v>
+        <v>735</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>98</v>
+        <v>736</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>99</v>
+        <v>737</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>100</v>
+        <v>738</v>
       </c>
       <c r="G14" s="1" t="s">
-        <v>101</v>
+        <v>739</v>
       </c>
       <c r="H14" s="1" t="s">
-        <v>102</v>
-      </c>
-      <c r="I14" s="3" t="s">
-        <v>103</v>
+        <v>740</v>
+      </c>
+      <c r="I14" s="9" t="s">
+        <v>741</v>
       </c>
     </row>
     <row r="15" ht="60">
       <c r="A15" s="1" t="s">
-        <v>104</v>
+        <v>742</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>96</v>
+        <v>734</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>105</v>
+        <v>743</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>106</v>
+        <v>744</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>107</v>
+        <v>745</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>108</v>
+        <v>746</v>
       </c>
       <c r="G15" s="1" t="s">
-        <v>109</v>
+        <v>747</v>
       </c>
       <c r="H15" s="1" t="s">
-        <v>110</v>
-      </c>
-      <c r="I15" s="3" t="s">
-        <v>103</v>
+        <v>748</v>
+      </c>
+      <c r="I15" s="9" t="s">
+        <v>741</v>
       </c>
     </row>
     <row r="16" ht="60">
       <c r="A16" s="1" t="s">
-        <v>111</v>
+        <v>749</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>96</v>
+        <v>734</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>112</v>
+        <v>750</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>113</v>
+        <v>751</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>114</v>
+        <v>752</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>115</v>
+        <v>753</v>
       </c>
       <c r="G16" s="1" t="s">
-        <v>116</v>
+        <v>754</v>
       </c>
       <c r="H16" s="1" t="s">
-        <v>117</v>
-      </c>
-      <c r="I16" s="3" t="s">
-        <v>103</v>
+        <v>755</v>
+      </c>
+      <c r="I16" s="9" t="s">
+        <v>741</v>
       </c>
     </row>
     <row r="17" ht="60">
       <c r="A17" s="1" t="s">
-        <v>118</v>
+        <v>756</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>96</v>
+        <v>734</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>119</v>
+        <v>757</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>120</v>
+        <v>758</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>121</v>
+        <v>759</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>122</v>
+        <v>760</v>
       </c>
       <c r="G17" s="1" t="s">
-        <v>123</v>
+        <v>761</v>
       </c>
       <c r="H17" s="1" t="s">
-        <v>124</v>
-      </c>
-      <c r="I17" s="3" t="s">
-        <v>103</v>
+        <v>762</v>
+      </c>
+      <c r="I17" s="9" t="s">
+        <v>741</v>
       </c>
     </row>
     <row r="18" ht="71.25">
       <c r="A18" s="1" t="s">
-        <v>125</v>
+        <v>763</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>96</v>
+        <v>734</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>126</v>
+        <v>764</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>127</v>
+        <v>765</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>128</v>
+        <v>766</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>129</v>
+        <v>767</v>
       </c>
       <c r="G18" s="1" t="s">
-        <v>130</v>
+        <v>768</v>
       </c>
       <c r="H18" s="1" t="s">
-        <v>131</v>
+        <v>769</v>
       </c>
     </row>
     <row r="19" ht="71.25">
       <c r="A19" s="1" t="s">
-        <v>132</v>
+        <v>770</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>96</v>
+        <v>734</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>133</v>
+        <v>62</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>134</v>
+        <v>771</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>135</v>
+        <v>772</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>136</v>
+        <v>773</v>
       </c>
       <c r="G19" s="1" t="s">
-        <v>137</v>
+        <v>774</v>
       </c>
       <c r="H19" s="1" t="s">
-        <v>138</v>
+        <v>775</v>
       </c>
     </row>
     <row r="20" ht="60">
       <c r="A20" s="1" t="s">
-        <v>139</v>
+        <v>776</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>96</v>
+        <v>734</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>140</v>
+        <v>777</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>141</v>
+        <v>778</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>142</v>
+        <v>779</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>143</v>
+        <v>780</v>
       </c>
       <c r="G20" s="1" t="s">
-        <v>144</v>
+        <v>781</v>
       </c>
       <c r="H20" s="1" t="s">
-        <v>145</v>
-      </c>
-      <c r="I20" s="3" t="s">
-        <v>103</v>
+        <v>782</v>
+      </c>
+      <c r="I20" s="9" t="s">
+        <v>741</v>
       </c>
     </row>
     <row r="21" ht="60">
       <c r="A21" s="1" t="s">
-        <v>146</v>
+        <v>783</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>96</v>
+        <v>734</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>147</v>
+        <v>784</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>148</v>
+        <v>785</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>149</v>
+        <v>786</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>150</v>
+        <v>787</v>
       </c>
       <c r="G21" s="1" t="s">
-        <v>151</v>
+        <v>788</v>
       </c>
       <c r="H21" s="1" t="s">
-        <v>152</v>
-      </c>
-      <c r="I21" s="3" t="s">
-        <v>103</v>
+        <v>789</v>
+      </c>
+      <c r="I21" s="9" t="s">
+        <v>741</v>
       </c>
     </row>
     <row r="22" ht="57">
       <c r="A22" s="1" t="s">
-        <v>153</v>
+        <v>790</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>154</v>
+        <v>461</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>155</v>
+        <v>791</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>156</v>
+        <v>792</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>157</v>
+        <v>793</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>158</v>
+        <v>794</v>
       </c>
       <c r="G22" s="1" t="s">
-        <v>159</v>
+        <v>795</v>
       </c>
       <c r="H22" s="1" t="s">
-        <v>160</v>
+        <v>796</v>
       </c>
       <c r="I22" s="1" t="s">
-        <v>161</v>
+        <v>797</v>
       </c>
     </row>
     <row r="23" ht="42.75">
       <c r="A23" s="1" t="s">
-        <v>162</v>
+        <v>798</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>154</v>
+        <v>461</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>163</v>
+        <v>799</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>164</v>
+        <v>800</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>165</v>
+        <v>801</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>166</v>
+        <v>802</v>
       </c>
       <c r="G23" s="1" t="s">
-        <v>167</v>
+        <v>803</v>
       </c>
       <c r="H23" s="1" t="s">
-        <v>168</v>
+        <v>804</v>
       </c>
     </row>
     <row r="24" ht="57">
       <c r="A24" s="1" t="s">
-        <v>169</v>
+        <v>805</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>154</v>
+        <v>461</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>170</v>
+        <v>806</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>171</v>
+        <v>807</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>172</v>
+        <v>808</v>
       </c>
       <c r="F24" s="1" t="s">
-        <v>173</v>
+        <v>809</v>
       </c>
       <c r="G24" s="1" t="s">
-        <v>174</v>
+        <v>810</v>
       </c>
       <c r="H24" s="1" t="s">
-        <v>175</v>
+        <v>811</v>
       </c>
       <c r="I24" s="1" t="s">
-        <v>176</v>
+        <v>812</v>
       </c>
     </row>
     <row r="25" ht="57">
       <c r="A25" s="1" t="s">
-        <v>177</v>
+        <v>813</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>154</v>
+        <v>461</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>178</v>
+        <v>814</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>179</v>
+        <v>815</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>180</v>
+        <v>816</v>
       </c>
       <c r="F25" s="1" t="s">
-        <v>181</v>
+        <v>817</v>
       </c>
       <c r="G25" s="1" t="s">
-        <v>182</v>
+        <v>818</v>
       </c>
       <c r="H25" s="1" t="s">
-        <v>183</v>
+        <v>819</v>
       </c>
     </row>
     <row r="26" ht="57">
       <c r="A26" s="1" t="s">
-        <v>184</v>
+        <v>820</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>154</v>
+        <v>461</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>185</v>
+        <v>821</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>186</v>
+        <v>822</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>187</v>
+        <v>823</v>
       </c>
       <c r="F26" s="1" t="s">
-        <v>188</v>
+        <v>824</v>
       </c>
       <c r="G26" s="1" t="s">
-        <v>189</v>
+        <v>825</v>
       </c>
       <c r="H26" s="1" t="s">
-        <v>190</v>
+        <v>826</v>
       </c>
     </row>
   </sheetData>
@@ -2309,302 +6070,585 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac">
   <sheetFormatPr baseColWidth="9" defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="16384" style="4" width="10.28125"/>
+    <col min="1" max="16384" style="1" width="10.28125"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="4" t="s">
+    <row r="1" ht="28.5">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="4" t="s">
-        <v>191</v>
-      </c>
-      <c r="C1" s="4" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="4" t="s">
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="E1" s="4" t="s">
+      <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="F1" s="4" t="s">
+      <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="G1" s="4" t="s">
+      <c r="H1" s="1" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="2" ht="57">
-      <c r="A2" s="4" t="s">
-        <v>192</v>
-      </c>
-      <c r="B2" s="4">
-        <v>0</v>
-      </c>
-      <c r="C2" s="4" t="s">
-        <v>193</v>
-      </c>
-      <c r="D2" s="4" t="s">
-        <v>194</v>
-      </c>
-      <c r="E2" s="4" t="s">
-        <v>195</v>
-      </c>
-      <c r="F2" s="4" t="s">
-        <v>196</v>
-      </c>
-      <c r="G2" s="4" t="s">
-        <v>197</v>
-      </c>
-      <c r="H2" s="4" t="s">
-        <v>198</v>
-      </c>
-      <c r="I2" s="4" t="s">
-        <v>199</v>
-      </c>
-      <c r="J2" s="4" t="s">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="3" ht="71.25">
-      <c r="A3" s="4" t="s">
-        <v>201</v>
-      </c>
-      <c r="B3" s="4">
-        <v>0</v>
-      </c>
-      <c r="C3" s="4" t="s">
-        <v>202</v>
-      </c>
-      <c r="D3" s="4" t="s">
-        <v>203</v>
-      </c>
-      <c r="E3" s="4" t="s">
-        <v>204</v>
-      </c>
-      <c r="F3" s="4" t="s">
-        <v>205</v>
-      </c>
-      <c r="G3" s="4" t="s">
-        <v>206</v>
-      </c>
-      <c r="H3" s="4" t="s">
-        <v>207</v>
-      </c>
-    </row>
-    <row r="4" ht="57">
-      <c r="A4" s="4" t="s">
-        <v>208</v>
-      </c>
-      <c r="B4" s="4">
-        <v>1</v>
-      </c>
-      <c r="C4" s="4" t="s">
-        <v>209</v>
-      </c>
-      <c r="D4" s="4" t="s">
-        <v>210</v>
-      </c>
-      <c r="E4" s="4" t="s">
-        <v>211</v>
-      </c>
-      <c r="F4" s="4" t="s">
-        <v>212</v>
-      </c>
-      <c r="G4" s="4" t="s">
-        <v>213</v>
-      </c>
-      <c r="H4" s="4" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="5" ht="42.75">
-      <c r="A5" s="4" t="s">
-        <v>215</v>
-      </c>
-      <c r="B5" s="4">
-        <v>1</v>
-      </c>
-      <c r="C5" s="4" t="s">
+    <row r="2" ht="128.25">
+      <c r="A2" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="3" ht="99.75">
+      <c r="A3" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="G3" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="H3" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="4" ht="128.25">
+      <c r="A4" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="G4" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="H4" s="1" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="5" ht="142.5">
+      <c r="A5" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="F5" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="G5" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="H5" s="1" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="6" ht="142.5">
+      <c r="A6" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="F6" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="G6" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="H6" s="1" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="7" ht="128.25">
+      <c r="A7" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="F7" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="G7" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="H7" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="I7" s="1" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="8" ht="114">
+      <c r="A8" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="F8" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="G8" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="H8" s="1" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="9" ht="114">
+      <c r="A9" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="E9" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="F9" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="G9" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="H9" s="1" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="10" ht="114">
+      <c r="A10" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="E10" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="F10" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="G10" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="H10" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="I10" s="1" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="11" ht="114">
+      <c r="A11" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="E11" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="F11" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="G11" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="H11" s="1" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="12" ht="114">
+      <c r="A12" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="E12" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="F12" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="G12" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="H12" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="I12" s="2" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="13" ht="128.25">
+      <c r="A13" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="D13" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="E13" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="F13" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="G13" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="H13" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="I13" s="2" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="14" ht="99.75">
+      <c r="A14" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="D14" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="E14" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="F14" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="G14" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="H14" s="1" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="15" ht="71.25">
+      <c r="A15" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="D15" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="E15" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="F15" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="G15" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="H15" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="I15" s="1" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="16" s="5" customFormat="1" ht="142.5">
+      <c r="A16" s="5" t="s">
+        <v>100</v>
+      </c>
+      <c r="B16" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C16" s="5" t="s">
+        <v>88</v>
+      </c>
+      <c r="D16" s="5" t="s">
+        <v>101</v>
+      </c>
+      <c r="E16" s="5" t="s">
+        <v>102</v>
+      </c>
+      <c r="F16" s="5" t="s">
+        <v>103</v>
+      </c>
+      <c r="G16" s="5" t="s">
+        <v>104</v>
+      </c>
+      <c r="H16" s="5" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="17" ht="99.75">
+      <c r="A17" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="D17" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="E17" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="F17" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="G17" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="H17" s="1" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="18" ht="142.5">
+      <c r="A18" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="D18" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="E18" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="F18" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="G18" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="H18" s="1" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="19" ht="142.5">
+      <c r="A19" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C19" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="D19" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="E19" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="F19" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="G19" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="H19" s="1" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="20" ht="171">
+      <c r="A20" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C20" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="D20" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="E20" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="F20" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="G20" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="H20" s="1" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="21" ht="156.75">
+      <c r="A21" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C21" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="D21" s="1" t="s">
         <v>133</v>
       </c>
-      <c r="D5" s="4" t="s">
-        <v>216</v>
-      </c>
-      <c r="E5" s="4" t="s">
-        <v>217</v>
-      </c>
-      <c r="F5" s="4" t="s">
-        <v>218</v>
-      </c>
-      <c r="G5" s="4" t="s">
-        <v>219</v>
-      </c>
-      <c r="H5" s="4" t="s">
-        <v>220</v>
-      </c>
-    </row>
-    <row r="6" ht="71.25">
-      <c r="A6" s="4" t="s">
-        <v>221</v>
-      </c>
-      <c r="B6" s="4">
-        <v>2</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>222</v>
-      </c>
-      <c r="D6" s="4" t="s">
-        <v>223</v>
-      </c>
-      <c r="E6" s="4" t="s">
-        <v>224</v>
-      </c>
-      <c r="F6" s="4" t="s">
-        <v>225</v>
-      </c>
-      <c r="G6" s="4" t="s">
-        <v>226</v>
-      </c>
-      <c r="H6" s="4" t="s">
-        <v>227</v>
-      </c>
-    </row>
-    <row r="7" ht="57">
-      <c r="A7" s="4" t="s">
-        <v>228</v>
-      </c>
-      <c r="B7" s="4">
-        <v>2</v>
-      </c>
-      <c r="C7" s="4" t="s">
-        <v>229</v>
-      </c>
-      <c r="D7" s="4" t="s">
-        <v>230</v>
-      </c>
-      <c r="E7" s="4" t="s">
-        <v>231</v>
-      </c>
-      <c r="F7" s="4" t="s">
-        <v>232</v>
-      </c>
-      <c r="G7" s="4" t="s">
-        <v>233</v>
-      </c>
-      <c r="H7" s="4" t="s">
-        <v>234</v>
-      </c>
-    </row>
-    <row r="8" ht="42.75">
-      <c r="A8" s="4" t="s">
-        <v>235</v>
-      </c>
-      <c r="B8" s="4">
-        <v>3</v>
-      </c>
-      <c r="C8" s="4" t="s">
-        <v>236</v>
-      </c>
-      <c r="D8" s="4" t="s">
-        <v>237</v>
-      </c>
-      <c r="E8" s="4" t="s">
-        <v>238</v>
-      </c>
-      <c r="F8" s="4" t="s">
-        <v>239</v>
-      </c>
-      <c r="G8" s="4" t="s">
-        <v>240</v>
-      </c>
-      <c r="H8" s="4" t="s">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="9" ht="42.75">
-      <c r="A9" s="4" t="s">
-        <v>242</v>
-      </c>
-      <c r="B9" s="4">
-        <v>3</v>
-      </c>
-      <c r="C9" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="D9" s="4" t="s">
-        <v>243</v>
-      </c>
-      <c r="E9" s="4" t="s">
-        <v>244</v>
-      </c>
-      <c r="F9" s="4" t="s">
-        <v>245</v>
-      </c>
-      <c r="G9" s="4" t="s">
-        <v>246</v>
-      </c>
-      <c r="H9" s="4" t="s">
-        <v>247</v>
-      </c>
-      <c r="I9" s="4" t="s">
-        <v>248</v>
-      </c>
-    </row>
-    <row r="10" ht="57">
-      <c r="A10" s="4" t="s">
-        <v>249</v>
-      </c>
-      <c r="B10" s="4">
-        <v>4</v>
-      </c>
-      <c r="C10" s="4" t="s">
-        <v>250</v>
-      </c>
-      <c r="D10" s="4" t="s">
-        <v>251</v>
-      </c>
-      <c r="E10" s="4" t="s">
-        <v>252</v>
-      </c>
-      <c r="F10" s="4" t="s">
-        <v>253</v>
-      </c>
-      <c r="G10" s="4" t="s">
-        <v>254</v>
-      </c>
-      <c r="H10" s="4" t="s">
-        <v>255</v>
-      </c>
-    </row>
-    <row r="11" ht="57">
-      <c r="A11" s="4" t="s">
-        <v>256</v>
-      </c>
-      <c r="B11" s="4">
-        <v>4</v>
-      </c>
-      <c r="C11" s="4" t="s">
-        <v>257</v>
-      </c>
-      <c r="D11" s="4" t="s">
-        <v>258</v>
-      </c>
-      <c r="E11" s="4" t="s">
-        <v>259</v>
-      </c>
-      <c r="F11" s="4" t="s">
-        <v>260</v>
-      </c>
-      <c r="G11" s="4" t="s">
-        <v>261</v>
-      </c>
-      <c r="H11" s="4" t="s">
-        <v>262</v>
-      </c>
-      <c r="I11" s="4" t="s">
-        <v>263</v>
+      <c r="E21" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="F21" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="G21" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="H21" s="1" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="22" ht="51">
+      <c r="A22" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="B22" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="C22" s="4" t="s">
+        <v>139</v>
+      </c>
+      <c r="D22" s="4" t="s">
+        <v>140</v>
+      </c>
+      <c r="E22" s="4" t="s">
+        <v>141</v>
       </c>
     </row>
   </sheetData>
@@ -2619,356 +6663,1940 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac">
   <sheetFormatPr baseColWidth="9" defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="16384" style="1" width="10.28125"/>
+    <col min="1" max="3" style="1" width="10.28125"/>
+    <col customWidth="1" min="4" max="4" style="1" width="16.421875"/>
+    <col min="5" max="16384" style="1" width="10.28125"/>
   </cols>
   <sheetData>
-    <row r="1" ht="14.25">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
+    <row r="1" ht="28.5">
       <c r="B1" s="1" t="s">
-        <v>1</v>
+        <v>145</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>3</v>
+        <v>146</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>4</v>
+        <v>147</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>5</v>
+        <v>148</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="2" ht="99.75">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="2" ht="57">
       <c r="A2" s="1" t="s">
-        <v>264</v>
+        <v>150</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>265</v>
+        <v>151</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>266</v>
+        <v>152</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>267</v>
+        <v>153</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>268</v>
+        <v>154</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>269</v>
-      </c>
-      <c r="G2" s="1" t="s">
-        <v>270</v>
-      </c>
-    </row>
-    <row r="3" ht="71.25">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="3" ht="57">
       <c r="A3" s="1" t="s">
-        <v>271</v>
+        <v>156</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>265</v>
+        <v>151</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>272</v>
+        <v>157</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>273</v>
+        <v>158</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>274</v>
+        <v>159</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>268</v>
-      </c>
-      <c r="G3" s="1" t="s">
-        <v>275</v>
-      </c>
-      <c r="H3" s="1" t="s">
-        <v>276</v>
+        <v>155</v>
       </c>
     </row>
     <row r="4" ht="57">
       <c r="A4" s="1" t="s">
-        <v>277</v>
+        <v>160</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>265</v>
+        <v>161</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>278</v>
+        <v>162</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>279</v>
+        <v>163</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>280</v>
-      </c>
-      <c r="F4" s="1" t="s">
-        <v>281</v>
+        <v>164</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>155</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>282</v>
-      </c>
-      <c r="H4" s="1" t="s">
-        <v>283</v>
-      </c>
-    </row>
-    <row r="5" ht="42.75">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="5" ht="57">
       <c r="A5" s="1" t="s">
-        <v>284</v>
+        <v>166</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>285</v>
+        <v>161</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>286</v>
+        <v>167</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>287</v>
+        <v>168</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>288</v>
+        <v>159</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>289</v>
-      </c>
-      <c r="G5" s="1" t="s">
-        <v>290</v>
-      </c>
-      <c r="H5" s="1" t="s">
-        <v>291</v>
+        <v>169</v>
       </c>
     </row>
     <row r="6" ht="71.25">
       <c r="A6" s="1" t="s">
-        <v>292</v>
+        <v>170</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>285</v>
+        <v>171</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>293</v>
+        <v>172</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>294</v>
+        <v>173</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>295</v>
-      </c>
-      <c r="F6" s="1" t="s">
-        <v>296</v>
+        <v>164</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>155</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>297</v>
+        <v>174</v>
       </c>
     </row>
     <row r="7" ht="57">
       <c r="A7" s="1" t="s">
-        <v>298</v>
+        <v>175</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>285</v>
+        <v>171</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>299</v>
+        <v>176</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>300</v>
+        <v>177</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>301</v>
+        <v>164</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>302</v>
-      </c>
-      <c r="G7" s="1" t="s">
-        <v>303</v>
-      </c>
-      <c r="H7" s="1" t="s">
-        <v>304</v>
+        <v>169</v>
       </c>
     </row>
     <row r="8" ht="57">
       <c r="A8" s="1" t="s">
-        <v>305</v>
+        <v>178</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>285</v>
+        <v>179</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>306</v>
+        <v>180</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>307</v>
+        <v>181</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>308</v>
+        <v>159</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>309</v>
-      </c>
-      <c r="G8" s="1" t="s">
-        <v>310</v>
-      </c>
-      <c r="H8" s="1" t="s">
-        <v>311</v>
+        <v>155</v>
       </c>
     </row>
     <row r="9" ht="42.75">
       <c r="A9" s="1" t="s">
-        <v>312</v>
+        <v>182</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>313</v>
+        <v>179</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>314</v>
+        <v>183</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>315</v>
+        <v>184</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>42</v>
+        <v>159</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>316</v>
-      </c>
-      <c r="G9" s="1" t="s">
-        <v>317</v>
-      </c>
-      <c r="H9" s="1" t="s">
-        <v>318</v>
+        <v>169</v>
       </c>
     </row>
     <row r="10" ht="57">
       <c r="A10" s="1" t="s">
-        <v>319</v>
+        <v>185</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>313</v>
+        <v>186</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>320</v>
+        <v>187</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>321</v>
+        <v>188</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>322</v>
+        <v>164</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>323</v>
-      </c>
-      <c r="G10" s="1" t="s">
-        <v>234</v>
-      </c>
-    </row>
-    <row r="11" ht="42.75">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="11" ht="57">
       <c r="A11" s="1" t="s">
-        <v>324</v>
+        <v>189</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>313</v>
+        <v>186</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>325</v>
+        <v>190</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>326</v>
+        <v>191</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>327</v>
+        <v>164</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>328</v>
-      </c>
-      <c r="G11" s="1" t="s">
-        <v>311</v>
-      </c>
-      <c r="H11" s="1" t="s">
-        <v>329</v>
-      </c>
-    </row>
-    <row r="12" ht="42.75">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="12" ht="57">
       <c r="A12" s="1" t="s">
-        <v>330</v>
+        <v>193</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>331</v>
+        <v>194</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>332</v>
+        <v>195</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>333</v>
+        <v>196</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>238</v>
+        <v>159</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>334</v>
-      </c>
-      <c r="G12" s="1" t="s">
-        <v>335</v>
-      </c>
-      <c r="H12" s="1" t="s">
-        <v>336</v>
+        <v>197</v>
       </c>
     </row>
     <row r="13" ht="57">
       <c r="A13" s="1" t="s">
-        <v>337</v>
+        <v>198</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>331</v>
+        <v>194</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>338</v>
+        <v>199</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>339</v>
+        <v>200</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>340</v>
+        <v>159</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>341</v>
-      </c>
-      <c r="G13" s="1" t="s">
-        <v>342</v>
-      </c>
-      <c r="H13" s="1" t="s">
-        <v>343</v>
-      </c>
-    </row>
-    <row r="14" ht="42.75">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="14" ht="57">
       <c r="A14" s="1" t="s">
-        <v>344</v>
+        <v>201</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>345</v>
+        <v>202</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>346</v>
+        <v>203</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>347</v>
+        <v>204</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>348</v>
+        <v>159</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>349</v>
-      </c>
-      <c r="G14" s="1" t="s">
-        <v>94</v>
+        <v>169</v>
+      </c>
+    </row>
+    <row r="15" ht="42.75">
+      <c r="A15" s="1" t="s">
+        <v>205</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>202</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>206</v>
+      </c>
+      <c r="D15" s="1" t="s">
+        <v>207</v>
+      </c>
+      <c r="E15" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="F15" s="1" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="16" ht="57">
+      <c r="A16" s="1" t="s">
+        <v>208</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>209</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>210</v>
+      </c>
+      <c r="D16" s="1" t="s">
+        <v>211</v>
+      </c>
+      <c r="E16" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="F16" s="1" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="17" ht="57">
+      <c r="A17" s="1" t="s">
+        <v>212</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>209</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>213</v>
+      </c>
+      <c r="D17" s="1" t="s">
+        <v>214</v>
+      </c>
+      <c r="E17" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="F17" s="1" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="18" ht="71.25">
+      <c r="A18" s="1" t="s">
+        <v>215</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>216</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>217</v>
+      </c>
+      <c r="D18" s="1" t="s">
+        <v>218</v>
+      </c>
+      <c r="E18" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="F18" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="G18" s="2"/>
+    </row>
+    <row r="19" ht="42.75">
+      <c r="A19" s="1" t="s">
+        <v>219</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>216</v>
+      </c>
+      <c r="C19" s="1" t="s">
+        <v>220</v>
+      </c>
+      <c r="D19" s="1" t="s">
+        <v>221</v>
+      </c>
+      <c r="E19" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="F19" s="1" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="20" ht="57">
+      <c r="A20" s="1" t="s">
+        <v>222</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>223</v>
+      </c>
+      <c r="C20" s="1" t="s">
+        <v>224</v>
+      </c>
+      <c r="D20" s="1" t="s">
+        <v>225</v>
+      </c>
+      <c r="E20" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="F20" s="1" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="21" ht="57">
+      <c r="A21" s="1" t="s">
+        <v>226</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>227</v>
+      </c>
+      <c r="C21" s="1" t="s">
+        <v>228</v>
+      </c>
+      <c r="D21" s="1" t="s">
+        <v>229</v>
+      </c>
+      <c r="E21" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="F21" s="1" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="22" ht="71.25">
+      <c r="A22" s="1" t="s">
+        <v>230</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>231</v>
+      </c>
+      <c r="C22" s="1" t="s">
+        <v>232</v>
+      </c>
+      <c r="D22" s="1" t="s">
+        <v>233</v>
+      </c>
+      <c r="E22" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="F22" s="2" t="s">
+        <v>234</v>
+      </c>
+      <c r="G22" s="1" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="23" ht="57">
+      <c r="A23" s="1" t="s">
+        <v>236</v>
+      </c>
+      <c r="B23" s="1" t="s">
+        <v>231</v>
+      </c>
+      <c r="C23" s="1" t="s">
+        <v>237</v>
+      </c>
+      <c r="D23" s="1" t="s">
+        <v>238</v>
+      </c>
+      <c r="E23" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="F23" s="1" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="24" ht="57">
+      <c r="A24" s="1" t="s">
+        <v>239</v>
+      </c>
+      <c r="B24" s="1" t="s">
+        <v>240</v>
+      </c>
+      <c r="C24" s="1" t="s">
+        <v>241</v>
+      </c>
+      <c r="D24" s="1" t="s">
+        <v>242</v>
+      </c>
+      <c r="E24" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="F24" s="1" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="25" ht="42.75">
+      <c r="A25" s="1" t="s">
+        <v>243</v>
+      </c>
+      <c r="B25" s="1" t="s">
+        <v>240</v>
+      </c>
+      <c r="C25" s="1" t="s">
+        <v>244</v>
+      </c>
+      <c r="D25" s="1" t="s">
+        <v>245</v>
+      </c>
+      <c r="E25" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="F25" s="1" t="s">
+        <v>192</v>
+      </c>
+    </row>
+  </sheetData>
+  <printOptions headings="0" gridLines="0"/>
+  <pageMargins left="0.70078740157480324" right="0.70078740157480324" top="0.75196850393700787" bottom="0.75196850393700787" header="0.29999999999999999" footer="0.29999999999999999"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" cellComments="none" useFirstPageNumber="0" errors="displayed" horizontalDpi="600" verticalDpi="600" copies="1"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac">
+  <sheetPr>
+    <outlinePr applyStyles="0" summaryBelow="0" summaryRight="0" showOutlineSymbols="1"/>
+    <pageSetUpPr autoPageBreaks="1" fitToPage="0"/>
+  </sheetPr>
+  <sheetFormatPr defaultColWidth="12.630000000000001" defaultRowHeight="15.75" customHeight="1"/>
+  <cols>
+    <col customWidth="1" min="1" max="1" width="7.140625"/>
+    <col customWidth="1" min="3" max="3" width="6.8799999999999999"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="38.25">
+      <c r="A1" s="6" t="s">
+        <v>246</v>
+      </c>
+      <c r="B1" s="6" t="s">
+        <v>247</v>
+      </c>
+      <c r="C1" s="6" t="s">
+        <v>248</v>
+      </c>
+      <c r="D1" s="6" t="s">
+        <v>249</v>
+      </c>
+      <c r="E1" s="7" t="s">
+        <v>141</v>
+      </c>
+      <c r="F1" s="7"/>
+      <c r="G1" s="7"/>
+      <c r="H1" s="7"/>
+      <c r="I1" s="7"/>
+      <c r="J1" s="7"/>
+      <c r="K1" s="7"/>
+      <c r="L1" s="7"/>
+      <c r="M1" s="7"/>
+      <c r="N1" s="7"/>
+      <c r="O1" s="7"/>
+      <c r="P1" s="7"/>
+      <c r="Q1" s="7"/>
+      <c r="R1" s="7"/>
+      <c r="S1" s="7"/>
+      <c r="T1" s="7"/>
+      <c r="U1" s="7"/>
+      <c r="V1" s="7"/>
+      <c r="W1" s="7"/>
+      <c r="X1" s="7"/>
+      <c r="Y1" s="7"/>
+    </row>
+    <row r="2" ht="38.25">
+      <c r="A2" s="6" t="s">
+        <v>250</v>
+      </c>
+      <c r="B2" s="6" t="s">
+        <v>251</v>
+      </c>
+      <c r="C2" s="6" t="s">
+        <v>252</v>
+      </c>
+      <c r="D2" s="6" t="s">
+        <v>253</v>
+      </c>
+      <c r="E2" s="7" t="s">
+        <v>141</v>
+      </c>
+      <c r="F2" s="7"/>
+      <c r="G2" s="7"/>
+      <c r="H2" s="7"/>
+      <c r="I2" s="7"/>
+      <c r="J2" s="7"/>
+      <c r="K2" s="7"/>
+      <c r="L2" s="7"/>
+      <c r="M2" s="7"/>
+      <c r="N2" s="7"/>
+      <c r="O2" s="7"/>
+      <c r="P2" s="7"/>
+      <c r="Q2" s="7"/>
+      <c r="R2" s="7"/>
+      <c r="S2" s="7"/>
+      <c r="T2" s="7"/>
+      <c r="U2" s="7"/>
+      <c r="V2" s="7"/>
+      <c r="W2" s="7"/>
+      <c r="X2" s="7"/>
+      <c r="Y2" s="7"/>
+    </row>
+  </sheetData>
+  <printOptions headings="0" gridLines="0"/>
+  <pageMargins left="0.70078740157480324" right="0.70078740157480324" top="0.75196850393700787" bottom="0.75196850393700787" header="0.29999999999999999" footer="0.29999999999999999"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" cellComments="none" useFirstPageNumber="0" errors="displayed" horizontalDpi="600" verticalDpi="600" copies="1"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac">
+  <sheetPr>
+    <outlinePr applyStyles="0" summaryBelow="0" summaryRight="0" showOutlineSymbols="1"/>
+    <pageSetUpPr autoPageBreaks="1" fitToPage="0"/>
+  </sheetPr>
+  <sheetFormatPr defaultColWidth="12.630000000000001" defaultRowHeight="15.75" customHeight="1"/>
+  <cols>
+    <col customWidth="1" min="1" max="1" width="7.140625"/>
+    <col customWidth="1" min="3" max="3" width="6.8799999999999999"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="38.25">
+      <c r="A1" s="6" t="s">
+        <v>246</v>
+      </c>
+      <c r="B1" s="6" t="s">
+        <v>247</v>
+      </c>
+      <c r="C1" s="6" t="s">
+        <v>248</v>
+      </c>
+      <c r="D1" s="6" t="s">
+        <v>249</v>
+      </c>
+      <c r="E1" s="7" t="s">
+        <v>141</v>
+      </c>
+      <c r="F1" s="7"/>
+      <c r="G1" s="7"/>
+      <c r="H1" s="7"/>
+      <c r="I1" s="7"/>
+      <c r="J1" s="7"/>
+      <c r="K1" s="7"/>
+      <c r="L1" s="7"/>
+      <c r="M1" s="7"/>
+      <c r="N1" s="7"/>
+      <c r="O1" s="7"/>
+      <c r="P1" s="7"/>
+      <c r="Q1" s="7"/>
+      <c r="R1" s="7"/>
+      <c r="S1" s="7"/>
+      <c r="T1" s="7"/>
+      <c r="U1" s="7"/>
+      <c r="V1" s="7"/>
+      <c r="W1" s="7"/>
+      <c r="X1" s="7"/>
+      <c r="Y1" s="7"/>
+    </row>
+    <row r="2" ht="38.25">
+      <c r="A2" s="6" t="s">
+        <v>250</v>
+      </c>
+      <c r="B2" s="6" t="s">
+        <v>251</v>
+      </c>
+      <c r="C2" s="6" t="s">
+        <v>252</v>
+      </c>
+      <c r="D2" s="6" t="s">
+        <v>253</v>
+      </c>
+      <c r="E2" s="7" t="s">
+        <v>141</v>
+      </c>
+      <c r="F2" s="7"/>
+      <c r="G2" s="7"/>
+      <c r="H2" s="7"/>
+      <c r="I2" s="7"/>
+      <c r="J2" s="7"/>
+      <c r="K2" s="7"/>
+      <c r="L2" s="7"/>
+      <c r="M2" s="7"/>
+      <c r="N2" s="7"/>
+      <c r="O2" s="7"/>
+      <c r="P2" s="7"/>
+      <c r="Q2" s="7"/>
+      <c r="R2" s="7"/>
+      <c r="S2" s="7"/>
+      <c r="T2" s="7"/>
+      <c r="U2" s="7"/>
+      <c r="V2" s="7"/>
+      <c r="W2" s="7"/>
+      <c r="X2" s="7"/>
+      <c r="Y2" s="7"/>
+    </row>
+  </sheetData>
+  <printOptions headings="0" gridLines="0"/>
+  <pageMargins left="0.70078740157480324" right="0.70078740157480324" top="0.75196850393700787" bottom="0.75196850393700787" header="0.29999999999999999" footer="0.29999999999999999"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" cellComments="none" useFirstPageNumber="0" errors="displayed" horizontalDpi="600" verticalDpi="600" copies="1"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac">
+  <sheetPr>
+    <outlinePr applyStyles="0" summaryBelow="0" summaryRight="0" showOutlineSymbols="1"/>
+    <pageSetUpPr autoPageBreaks="1" fitToPage="0"/>
+  </sheetPr>
+  <sheetFormatPr defaultColWidth="12.630000000000001" defaultRowHeight="15.75" customHeight="1"/>
+  <cols>
+    <col customWidth="1" min="1" max="1" width="7.140625"/>
+    <col customWidth="1" min="3" max="3" width="6.8799999999999999"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="38.25">
+      <c r="A1" s="6" t="s">
+        <v>246</v>
+      </c>
+      <c r="B1" s="6" t="s">
+        <v>247</v>
+      </c>
+      <c r="C1" s="6" t="s">
+        <v>248</v>
+      </c>
+      <c r="D1" s="6" t="s">
+        <v>249</v>
+      </c>
+      <c r="E1" s="7" t="s">
+        <v>141</v>
+      </c>
+      <c r="F1" s="7"/>
+      <c r="G1" s="7"/>
+      <c r="H1" s="7"/>
+      <c r="I1" s="7"/>
+      <c r="J1" s="7"/>
+      <c r="K1" s="7"/>
+      <c r="L1" s="7"/>
+      <c r="M1" s="7"/>
+      <c r="N1" s="7"/>
+      <c r="O1" s="7"/>
+      <c r="P1" s="7"/>
+      <c r="Q1" s="7"/>
+      <c r="R1" s="7"/>
+      <c r="S1" s="7"/>
+      <c r="T1" s="7"/>
+      <c r="U1" s="7"/>
+      <c r="V1" s="7"/>
+      <c r="W1" s="7"/>
+      <c r="X1" s="7"/>
+      <c r="Y1" s="7"/>
+    </row>
+    <row r="2" ht="38.25">
+      <c r="A2" s="6" t="s">
+        <v>250</v>
+      </c>
+      <c r="B2" s="6" t="s">
+        <v>251</v>
+      </c>
+      <c r="C2" s="6" t="s">
+        <v>252</v>
+      </c>
+      <c r="D2" s="6" t="s">
+        <v>253</v>
+      </c>
+      <c r="E2" s="7" t="s">
+        <v>141</v>
+      </c>
+      <c r="F2" s="7"/>
+      <c r="G2" s="7"/>
+      <c r="H2" s="7"/>
+      <c r="I2" s="7"/>
+      <c r="J2" s="7"/>
+      <c r="K2" s="7"/>
+      <c r="L2" s="7"/>
+      <c r="M2" s="7"/>
+      <c r="N2" s="7"/>
+      <c r="O2" s="7"/>
+      <c r="P2" s="7"/>
+      <c r="Q2" s="7"/>
+      <c r="R2" s="7"/>
+      <c r="S2" s="7"/>
+      <c r="T2" s="7"/>
+      <c r="U2" s="7"/>
+      <c r="V2" s="7"/>
+      <c r="W2" s="7"/>
+      <c r="X2" s="7"/>
+      <c r="Y2" s="7"/>
+    </row>
+  </sheetData>
+  <printOptions headings="0" gridLines="0"/>
+  <pageMargins left="0.70078740157480324" right="0.70078740157480324" top="0.75196850393700787" bottom="0.75196850393700787" header="0.29999999999999999" footer="0.29999999999999999"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" cellComments="none" useFirstPageNumber="0" errors="displayed" horizontalDpi="600" verticalDpi="600" copies="1"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac">
+  <sheetPr>
+    <outlinePr applyStyles="0" summaryBelow="0" summaryRight="0" showOutlineSymbols="1"/>
+    <pageSetUpPr autoPageBreaks="1" fitToPage="0"/>
+  </sheetPr>
+  <sheetFormatPr defaultColWidth="12.630000000000001" defaultRowHeight="15.75" customHeight="1"/>
+  <cols>
+    <col customWidth="1" min="1" max="1" width="7.140625"/>
+    <col customWidth="1" min="3" max="3" width="6.8799999999999999"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="38.25">
+      <c r="A1" s="6" t="s">
+        <v>246</v>
+      </c>
+      <c r="B1" s="6" t="s">
+        <v>247</v>
+      </c>
+      <c r="C1" s="6" t="s">
+        <v>248</v>
+      </c>
+      <c r="D1" s="6" t="s">
+        <v>249</v>
+      </c>
+      <c r="E1" s="7" t="s">
+        <v>141</v>
+      </c>
+      <c r="F1" s="7"/>
+      <c r="G1" s="7"/>
+      <c r="H1" s="7"/>
+      <c r="I1" s="7"/>
+      <c r="J1" s="7"/>
+      <c r="K1" s="7"/>
+      <c r="L1" s="7"/>
+      <c r="M1" s="7"/>
+      <c r="N1" s="7"/>
+      <c r="O1" s="7"/>
+      <c r="P1" s="7"/>
+      <c r="Q1" s="7"/>
+      <c r="R1" s="7"/>
+      <c r="S1" s="7"/>
+      <c r="T1" s="7"/>
+      <c r="U1" s="7"/>
+      <c r="V1" s="7"/>
+      <c r="W1" s="7"/>
+      <c r="X1" s="7"/>
+      <c r="Y1" s="7"/>
+    </row>
+    <row r="2" ht="38.25">
+      <c r="A2" s="6" t="s">
+        <v>250</v>
+      </c>
+      <c r="B2" s="6" t="s">
+        <v>251</v>
+      </c>
+      <c r="C2" s="6" t="s">
+        <v>252</v>
+      </c>
+      <c r="D2" s="6" t="s">
+        <v>253</v>
+      </c>
+      <c r="E2" s="7" t="s">
+        <v>141</v>
+      </c>
+      <c r="F2" s="7"/>
+      <c r="G2" s="7"/>
+      <c r="H2" s="7"/>
+      <c r="I2" s="7"/>
+      <c r="J2" s="7"/>
+      <c r="K2" s="7"/>
+      <c r="L2" s="7"/>
+      <c r="M2" s="7"/>
+      <c r="N2" s="7"/>
+      <c r="O2" s="7"/>
+      <c r="P2" s="7"/>
+      <c r="Q2" s="7"/>
+      <c r="R2" s="7"/>
+      <c r="S2" s="7"/>
+      <c r="T2" s="7"/>
+      <c r="U2" s="7"/>
+      <c r="V2" s="7"/>
+      <c r="W2" s="7"/>
+      <c r="X2" s="7"/>
+      <c r="Y2" s="7"/>
+    </row>
+  </sheetData>
+  <printOptions headings="0" gridLines="0"/>
+  <pageMargins left="0.70078740157480324" right="0.70078740157480324" top="0.75196850393700787" bottom="0.75196850393700787" header="0.29999999999999999" footer="0.29999999999999999"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" cellComments="none" useFirstPageNumber="0" errors="displayed" horizontalDpi="600" verticalDpi="600" copies="1"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac">
+  <sheetFormatPr baseColWidth="9" defaultRowHeight="14.25"/>
+  <cols>
+    <col min="1" max="3" style="1" width="10.28125"/>
+    <col customWidth="1" min="4" max="4" style="1" width="16.421875"/>
+    <col min="5" max="16384" style="1" width="10.28125"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28.5">
+      <c r="B1" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>148</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="2" ht="57">
+      <c r="A2" s="1" t="s">
+        <v>150</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>151</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>152</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="3" ht="57">
+      <c r="A3" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>151</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="4" ht="57">
+      <c r="A4" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>163</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="G4" s="1" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="5" ht="57">
+      <c r="A5" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>168</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="F5" s="1" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="6" ht="71.25">
+      <c r="A6" s="1" t="s">
+        <v>170</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>171</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>172</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>173</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="G6" s="1" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="7" ht="57">
+      <c r="A7" s="1" t="s">
+        <v>175</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>171</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>176</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>177</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="F7" s="1" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="8" ht="57">
+      <c r="A8" s="1" t="s">
+        <v>178</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>179</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>180</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>181</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="F8" s="1" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="9" ht="42.75">
+      <c r="A9" s="1" t="s">
+        <v>182</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>179</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="E9" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="F9" s="1" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="10" ht="57">
+      <c r="A10" s="1" t="s">
+        <v>185</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>186</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>188</v>
+      </c>
+      <c r="E10" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="F10" s="1" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="11" ht="57">
+      <c r="A11" s="1" t="s">
+        <v>189</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>186</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>190</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>191</v>
+      </c>
+      <c r="E11" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="F11" s="1" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="12" ht="57">
+      <c r="A12" s="1" t="s">
+        <v>193</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>194</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>195</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>196</v>
+      </c>
+      <c r="E12" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="F12" s="1" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="13" ht="57">
+      <c r="A13" s="1" t="s">
+        <v>198</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>194</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>199</v>
+      </c>
+      <c r="D13" s="1" t="s">
+        <v>200</v>
+      </c>
+      <c r="E13" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="F13" s="1" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="14" ht="57">
+      <c r="A14" s="1" t="s">
+        <v>201</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>202</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>203</v>
+      </c>
+      <c r="D14" s="1" t="s">
+        <v>204</v>
+      </c>
+      <c r="E14" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="F14" s="1" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="15" ht="42.75">
+      <c r="A15" s="1" t="s">
+        <v>205</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>202</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>206</v>
+      </c>
+      <c r="D15" s="1" t="s">
+        <v>207</v>
+      </c>
+      <c r="E15" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="F15" s="1" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="16" ht="57">
+      <c r="A16" s="1" t="s">
+        <v>208</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>209</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>210</v>
+      </c>
+      <c r="D16" s="1" t="s">
+        <v>211</v>
+      </c>
+      <c r="E16" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="F16" s="1" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="17" ht="57">
+      <c r="A17" s="1" t="s">
+        <v>212</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>209</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>213</v>
+      </c>
+      <c r="D17" s="1" t="s">
+        <v>214</v>
+      </c>
+      <c r="E17" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="F17" s="1" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="18" ht="71.25">
+      <c r="A18" s="1" t="s">
+        <v>215</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>216</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>217</v>
+      </c>
+      <c r="D18" s="1" t="s">
+        <v>218</v>
+      </c>
+      <c r="E18" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="F18" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="G18" s="2"/>
+    </row>
+    <row r="19" ht="42.75">
+      <c r="A19" s="1" t="s">
+        <v>219</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>216</v>
+      </c>
+      <c r="C19" s="1" t="s">
+        <v>220</v>
+      </c>
+      <c r="D19" s="1" t="s">
+        <v>221</v>
+      </c>
+      <c r="E19" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="F19" s="1" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="20" ht="57">
+      <c r="A20" s="1" t="s">
+        <v>222</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>223</v>
+      </c>
+      <c r="C20" s="1" t="s">
+        <v>224</v>
+      </c>
+      <c r="D20" s="1" t="s">
+        <v>225</v>
+      </c>
+      <c r="E20" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="F20" s="1" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="21" ht="57">
+      <c r="A21" s="1" t="s">
+        <v>226</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>227</v>
+      </c>
+      <c r="C21" s="1" t="s">
+        <v>228</v>
+      </c>
+      <c r="D21" s="1" t="s">
+        <v>229</v>
+      </c>
+      <c r="E21" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="F21" s="1" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="22" ht="71.25">
+      <c r="A22" s="1" t="s">
+        <v>230</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>231</v>
+      </c>
+      <c r="C22" s="1" t="s">
+        <v>232</v>
+      </c>
+      <c r="D22" s="1" t="s">
+        <v>233</v>
+      </c>
+      <c r="E22" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="F22" s="2" t="s">
+        <v>234</v>
+      </c>
+      <c r="G22" s="1" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="23" ht="57">
+      <c r="A23" s="1" t="s">
+        <v>236</v>
+      </c>
+      <c r="B23" s="1" t="s">
+        <v>231</v>
+      </c>
+      <c r="C23" s="1" t="s">
+        <v>237</v>
+      </c>
+      <c r="D23" s="1" t="s">
+        <v>238</v>
+      </c>
+      <c r="E23" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="F23" s="1" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="24" ht="57">
+      <c r="A24" s="1" t="s">
+        <v>239</v>
+      </c>
+      <c r="B24" s="1" t="s">
+        <v>240</v>
+      </c>
+      <c r="C24" s="1" t="s">
+        <v>241</v>
+      </c>
+      <c r="D24" s="1" t="s">
+        <v>242</v>
+      </c>
+      <c r="E24" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="F24" s="1" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="25" ht="42.75">
+      <c r="A25" s="1" t="s">
+        <v>243</v>
+      </c>
+      <c r="B25" s="1" t="s">
+        <v>240</v>
+      </c>
+      <c r="C25" s="1" t="s">
+        <v>244</v>
+      </c>
+      <c r="D25" s="1" t="s">
+        <v>245</v>
+      </c>
+      <c r="E25" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="F25" s="1" t="s">
+        <v>192</v>
+      </c>
+    </row>
+  </sheetData>
+  <printOptions headings="0" gridLines="0"/>
+  <pageMargins left="0.70078740157480324" right="0.70078740157480324" top="0.75196850393700787" bottom="0.75196850393700787" header="0.29999999999999999" footer="0.29999999999999999"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" cellComments="none" useFirstPageNumber="0" errors="displayed" horizontalDpi="600" verticalDpi="600" copies="1"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac">
+  <sheetFormatPr baseColWidth="9" defaultRowHeight="14.25"/>
+  <cols>
+    <col min="1" max="3" style="1" width="10.28125"/>
+    <col customWidth="1" min="4" max="4" style="1" width="16.421875"/>
+    <col min="5" max="16384" style="1" width="10.28125"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28.5">
+      <c r="B1" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>148</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="2" ht="57">
+      <c r="A2" s="1" t="s">
+        <v>150</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>151</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>152</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="3" ht="57">
+      <c r="A3" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>151</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="4" ht="57">
+      <c r="A4" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>163</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="G4" s="1" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="5" ht="57">
+      <c r="A5" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>168</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="F5" s="1" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="6" ht="71.25">
+      <c r="A6" s="1" t="s">
+        <v>170</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>171</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>172</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>173</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="G6" s="1" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="7" ht="57">
+      <c r="A7" s="1" t="s">
+        <v>175</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>171</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>176</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>177</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="F7" s="1" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="8" ht="57">
+      <c r="A8" s="1" t="s">
+        <v>178</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>179</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>180</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>181</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="F8" s="1" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="9" ht="42.75">
+      <c r="A9" s="1" t="s">
+        <v>182</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>179</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="E9" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="F9" s="1" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="10" ht="57">
+      <c r="A10" s="1" t="s">
+        <v>185</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>186</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>188</v>
+      </c>
+      <c r="E10" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="F10" s="1" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="11" ht="57">
+      <c r="A11" s="1" t="s">
+        <v>189</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>186</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>190</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>191</v>
+      </c>
+      <c r="E11" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="F11" s="1" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="12" ht="57">
+      <c r="A12" s="1" t="s">
+        <v>193</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>194</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>195</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>196</v>
+      </c>
+      <c r="E12" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="F12" s="1" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="13" ht="57">
+      <c r="A13" s="1" t="s">
+        <v>198</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>194</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>199</v>
+      </c>
+      <c r="D13" s="1" t="s">
+        <v>200</v>
+      </c>
+      <c r="E13" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="F13" s="1" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="14" ht="57">
+      <c r="A14" s="1" t="s">
+        <v>201</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>202</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>203</v>
+      </c>
+      <c r="D14" s="1" t="s">
+        <v>204</v>
+      </c>
+      <c r="E14" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="F14" s="1" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="15" ht="42.75">
+      <c r="A15" s="1" t="s">
+        <v>205</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>202</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>206</v>
+      </c>
+      <c r="D15" s="1" t="s">
+        <v>207</v>
+      </c>
+      <c r="E15" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="F15" s="1" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="16" ht="57">
+      <c r="A16" s="1" t="s">
+        <v>208</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>209</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>210</v>
+      </c>
+      <c r="D16" s="1" t="s">
+        <v>211</v>
+      </c>
+      <c r="E16" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="F16" s="1" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="17" ht="57">
+      <c r="A17" s="1" t="s">
+        <v>212</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>209</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>213</v>
+      </c>
+      <c r="D17" s="1" t="s">
+        <v>214</v>
+      </c>
+      <c r="E17" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="F17" s="1" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="18" ht="71.25">
+      <c r="A18" s="1" t="s">
+        <v>215</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>216</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>217</v>
+      </c>
+      <c r="D18" s="1" t="s">
+        <v>218</v>
+      </c>
+      <c r="E18" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="F18" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="G18" s="2"/>
+    </row>
+    <row r="19" ht="42.75">
+      <c r="A19" s="1" t="s">
+        <v>219</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>216</v>
+      </c>
+      <c r="C19" s="1" t="s">
+        <v>220</v>
+      </c>
+      <c r="D19" s="1" t="s">
+        <v>221</v>
+      </c>
+      <c r="E19" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="F19" s="1" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="20" ht="57">
+      <c r="A20" s="1" t="s">
+        <v>222</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>223</v>
+      </c>
+      <c r="C20" s="1" t="s">
+        <v>224</v>
+      </c>
+      <c r="D20" s="1" t="s">
+        <v>225</v>
+      </c>
+      <c r="E20" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="F20" s="1" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="21" ht="57">
+      <c r="A21" s="1" t="s">
+        <v>226</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>227</v>
+      </c>
+      <c r="C21" s="1" t="s">
+        <v>228</v>
+      </c>
+      <c r="D21" s="1" t="s">
+        <v>229</v>
+      </c>
+      <c r="E21" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="F21" s="1" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="22" ht="71.25">
+      <c r="A22" s="1" t="s">
+        <v>230</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>231</v>
+      </c>
+      <c r="C22" s="1" t="s">
+        <v>232</v>
+      </c>
+      <c r="D22" s="1" t="s">
+        <v>233</v>
+      </c>
+      <c r="E22" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="F22" s="2" t="s">
+        <v>234</v>
+      </c>
+      <c r="G22" s="1" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="23" ht="57">
+      <c r="A23" s="1" t="s">
+        <v>236</v>
+      </c>
+      <c r="B23" s="1" t="s">
+        <v>231</v>
+      </c>
+      <c r="C23" s="1" t="s">
+        <v>237</v>
+      </c>
+      <c r="D23" s="1" t="s">
+        <v>238</v>
+      </c>
+      <c r="E23" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="F23" s="1" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="24" ht="57">
+      <c r="A24" s="1" t="s">
+        <v>239</v>
+      </c>
+      <c r="B24" s="1" t="s">
+        <v>240</v>
+      </c>
+      <c r="C24" s="1" t="s">
+        <v>241</v>
+      </c>
+      <c r="D24" s="1" t="s">
+        <v>242</v>
+      </c>
+      <c r="E24" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="F24" s="1" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="25" ht="42.75">
+      <c r="A25" s="1" t="s">
+        <v>243</v>
+      </c>
+      <c r="B25" s="1" t="s">
+        <v>240</v>
+      </c>
+      <c r="C25" s="1" t="s">
+        <v>244</v>
+      </c>
+      <c r="D25" s="1" t="s">
+        <v>245</v>
+      </c>
+      <c r="E25" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="F25" s="1" t="s">
+        <v>192</v>
       </c>
     </row>
   </sheetData>

--- a/tasklist/habitable.xlsx
+++ b/tasklist/habitable.xlsx
@@ -3,23 +3,17 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <workbookPr/>
   <bookViews>
-    <workbookView xWindow="360" yWindow="15" windowWidth="20955" windowHeight="9720" activeTab="11"/>
+    <workbookView xWindow="360" yWindow="15" windowWidth="20955" windowHeight="9720" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="水星探査" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="水星ダイソン環" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="ケンタ" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="WH第1章：時空開孔の安定化" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="WH第2章：系外インフラ自動構築" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="WH第3章：銀河蓄電池の運用" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="WHエピローグ：距離の消滅" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="ダイソン環" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="量子comp" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet name="HZ創出" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet name="PAI+DNA" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet name="Sheet1 (2)" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet name="Sheet1" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet name="人類消滅" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet name="HZ創出" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="PAI+DNA" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Sheet1 (2)" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Sheet1" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="人類消滅" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <calcPr/>
   <extLst>
@@ -29,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="827" uniqueCount="827">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="949" uniqueCount="949">
   <si>
     <t>課題ID</t>
   </si>
@@ -55,6 +49,399 @@
     <t>備考</t>
   </si>
   <si>
+    <t>DEV-01</t>
+  </si>
+  <si>
+    <t>技術開発</t>
+  </si>
+  <si>
+    <t>自己複製ロボット</t>
+  </si>
+  <si>
+    <t>ロボット複製倍率と所要時間の最適化</t>
+  </si>
+  <si>
+    <t xml:space="preserve">初期台数N_0 複製倍率R_double[倍/月] 目標台数N_target</t>
+  </si>
+  <si>
+    <t xml:space="preserve">N_0 R_double N_target</t>
+  </si>
+  <si>
+    <t xml:space="preserve">到達時間T_months 総消費エネルギーE_total[J]</t>
+  </si>
+  <si>
+    <t>金星ヘスペラスから電力を供給。複製倍率とコストのトレードオフ</t>
+  </si>
+  <si>
+    <t>DEV-02</t>
+  </si>
+  <si>
+    <t>ロボット1台あたりの製造エネルギー収支</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ロボット質量M_robot[kg] 材料E_mat[J/kg] 組立E_assem[J]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">M_robot E_mat E_assem</t>
+  </si>
+  <si>
+    <t xml:space="preserve">製造E_total[J/台] エネルギーコストC_energy[USD/台]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">自己複製のエネルギー収支。E_total &lt; 発電量が条件。金星電力を初期種として利用</t>
+  </si>
+  <si>
+    <t>DEV-03</t>
+  </si>
+  <si>
+    <t>金星大気対応ロボットの防食設計</t>
+  </si>
+  <si>
+    <t xml:space="preserve">硫酸濃度C_H2SO4[%] 温度T[℃] 耐食材料コストC_mat[USD/kg]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C_H2SO4 T C_mat</t>
+  </si>
+  <si>
+    <t xml:space="preserve">腐食速度R_corr[mm/年] ロボット寿命L_years[年]</t>
+  </si>
+  <si>
+    <t>金星大気は硫酸の雲。ヘスペラスはこの中で運用</t>
+  </si>
+  <si>
+    <t>DEV-04</t>
+  </si>
+  <si>
+    <t>金星ヘスペラス</t>
+  </si>
+  <si>
+    <t>ヘスペラス浮遊構造の設計</t>
+  </si>
+  <si>
+    <t xml:space="preserve">浮力ガス密度ρ_gas[kg/m³] 外気密度ρ_atm[kg/m³] ペイロードM_payload[kg]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ρ_gas ρ_atm M_payload</t>
+  </si>
+  <si>
+    <t xml:space="preserve">必要容積V_envelope[m³] 構造質量M_struct[kg]</t>
+  </si>
+  <si>
+    <t>金星大気はCO2主体で密度高い。ヘリウム浮力が有効</t>
+  </si>
+  <si>
+    <t>hesperusで計算済</t>
+  </si>
+  <si>
+    <t>DEV-05</t>
+  </si>
+  <si>
+    <t>ヘスペラスの大気中エネルギー生成</t>
+  </si>
+  <si>
+    <t xml:space="preserve">風力発電出力P_wind[W] 太陽光発電P_solar[W] LENR炉出力P_LENR[W]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">P_wind P_solar P_LENR</t>
+  </si>
+  <si>
+    <t xml:space="preserve">総発電量P_total[W] エネルギー自給率R_self[%]</t>
+  </si>
+  <si>
+    <t>金星大気は濃く風力が有効。夜間はLENR炉で補完</t>
+  </si>
+  <si>
+    <t>DEV-06</t>
+  </si>
+  <si>
+    <t>金星大気からの水素・炭素・窒素分離</t>
+  </si>
+  <si>
+    <t xml:space="preserve">大気組成（CO2 96% N2 3.5%） 分離効率η_sep 処理量M_atm[kg/日]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">組成 η_sep M_atm</t>
+  </si>
+  <si>
+    <t xml:space="preserve">水素製造量M_H2[kg/日] 炭素M_C[kg/日] 窒素M_N2[kg/日] 所要電力P_sep[W]</t>
+  </si>
+  <si>
+    <t>ヘスペラスの主要任務。水素は水星ダイソン環へ供給</t>
+  </si>
+  <si>
+    <t>26.07.09</t>
+  </si>
+  <si>
+    <t>DEV-07</t>
+  </si>
+  <si>
+    <t>ヘスペラス-水星間の資材輸送コスト</t>
+  </si>
+  <si>
+    <t xml:space="preserve">輸送距離d[AU] 輸送質量M_cargo[kg] 推進方式（化学/イオン）</t>
+  </si>
+  <si>
+    <t xml:space="preserve">d M_cargo 方式</t>
+  </si>
+  <si>
+    <t xml:space="preserve">所要燃料M_fuel[kg] 輸送コストC_trans[USD/ton]</t>
+  </si>
+  <si>
+    <t>金星と水星は接近時0.3AU。定期的なシャトル便</t>
+  </si>
+  <si>
+    <t>DEV-08</t>
+  </si>
+  <si>
+    <t>水星採掘</t>
+  </si>
+  <si>
+    <t>水星レゴリスからの鉄・シリコン分離効率</t>
+  </si>
+  <si>
+    <t xml:space="preserve">鉱石処理量M_ore[kg/日] 鉄含有率R_iron[%] 分離効率η_sep</t>
+  </si>
+  <si>
+    <t xml:space="preserve">M_ore R_iron η_sep</t>
+  </si>
+  <si>
+    <t xml:space="preserve">鉄生産量M_iron[kg/日] シリコンM_silicon[kg/日] 所要電力P_sep[W]</t>
+  </si>
+  <si>
+    <t>太陽熱溶解＋磁気分離。電力は初期はヘスペラスから</t>
+  </si>
+  <si>
+    <t>DEV-09</t>
+  </si>
+  <si>
+    <t>水星昼側+430℃対応の採掘機設計</t>
+  </si>
+  <si>
+    <t xml:space="preserve">動作温度T_op[℃] 冷却方式 冷却効率η_cool</t>
+  </si>
+  <si>
+    <t xml:space="preserve">T_op η_cool</t>
+  </si>
+  <si>
+    <t xml:space="preserve">必要冷却電力P_cool[W] 冷却器質量M_cooler[kg]</t>
+  </si>
+  <si>
+    <t>水星昼側は極高温。ヒートパイプ＋放射冷却で対応</t>
+  </si>
+  <si>
+    <t>DEV-10</t>
+  </si>
+  <si>
+    <t>水星パネル製造</t>
+  </si>
+  <si>
+    <t>シリコンインゴット製造効率</t>
+  </si>
+  <si>
+    <t xml:space="preserve">シリコン純度Purity[%] 成長速度R_grow[mm/hr] エネルギー消費E_grow[J/kg]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Purity R_grow E_grow</t>
+  </si>
+  <si>
+    <t xml:space="preserve">インゴット生産量M_ingot[kg/日] パネル変換効率η_panel[%]</t>
+  </si>
+  <si>
+    <t>無重力・真空での結晶成長。ヘスペラスから水素供給</t>
+  </si>
+  <si>
+    <t>DEV-11</t>
+  </si>
+  <si>
+    <t>ソーラーパネル製造ラインのスループット</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ライン速度R_line[m/hr] パネル幅W_panel[m] 歩留まりYield[%]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">R_line W_panel Yield</t>
+  </si>
+  <si>
+    <t xml:space="preserve">日産面積A_day[m²/日] 年産A_year[m²/年]</t>
+  </si>
+  <si>
+    <t>完全無人24時間生産。目標1日100km²</t>
+  </si>
+  <si>
+    <t>DEV-12</t>
+  </si>
+  <si>
+    <t>AI制御</t>
+  </si>
+  <si>
+    <t>ヘスペラス-水星間の通信遅延と自律制御</t>
+  </si>
+  <si>
+    <t xml:space="preserve">距離d[AU] 往復遅延T_delay[min] タスク応答要件T_req[sec]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">d T_delay T_req</t>
+  </si>
+  <si>
+    <t xml:space="preserve">必要自律制御率R_auto[%] 介入頻度F_int[回/日]</t>
+  </si>
+  <si>
+    <t>金星-水星間は0.3〜1.2AU。往復3〜12分の遅延</t>
+  </si>
+  <si>
+    <t>DEV-13</t>
+  </si>
+  <si>
+    <t>マルチロボット協調制御の通信帯域</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ロボット台数N_robot 1台あたりデータ量D_robot[bps] 制御周期T_cycle[sec]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">N_robot D_robot T_cycle</t>
+  </si>
+  <si>
+    <t xml:space="preserve">総通信帯域B_total[bps] 必要B_req[bps]</t>
+  </si>
+  <si>
+    <t>1万台のロボットを同時制御。ヘスペラスが中継</t>
+  </si>
+  <si>
+    <t>DEV-14</t>
+  </si>
+  <si>
+    <t>ヘスペラスと水星ロボット群の統合制御アーキテクチャ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ヘスペラスAI能力C_AI[FLOPS] 水星ロボット数N_robot 通信遅延T_delay</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C_AI N_robot T_delay</t>
+  </si>
+  <si>
+    <t xml:space="preserve">統合制御効率E_ctrl[%] 異常対応時間T_response[sec]</t>
+  </si>
+  <si>
+    <t>ヘスペラスが上位AI、水星ロボットが下位。階層型制御</t>
+  </si>
+  <si>
+    <t>DEV-15</t>
+  </si>
+  <si>
+    <t>統合試験</t>
+  </si>
+  <si>
+    <t>地球軌道上でのヘスペラス部分組み立て試験</t>
+  </si>
+  <si>
+    <t xml:space="preserve">試験項目数N_test 1項目あたり時間T_test[hr] 並行試験数N_parallel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">N_test T_test N_parallel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">総試験時間T_total[日] 試験コストC_test[USD]</t>
+  </si>
+  <si>
+    <t>ヘスペラスは巨大構造。軌道上でモジュール単位で試験</t>
+  </si>
+  <si>
+    <t>DEV-16</t>
+  </si>
+  <si>
+    <t>金星到着後のヘスペラス自動展開試験</t>
+  </si>
+  <si>
+    <t xml:space="preserve">展開モジュール数N_module 1モジュール展開時間T_deploy[hr] 自動化率R_auto[%]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">N_module T_deploy R_auto</t>
+  </si>
+  <si>
+    <t xml:space="preserve">総展開時間T_total[日] 失敗確率P_fail[%]</t>
+  </si>
+  <si>
+    <t>無人での自動展開。失敗時のバックアップ手順</t>
+  </si>
+  <si>
+    <t>DEV-17</t>
+  </si>
+  <si>
+    <t>開発スケジュール</t>
+  </si>
+  <si>
+    <t>並行開発のクリティカルパス分析</t>
+  </si>
+  <si>
+    <t xml:space="preserve">各技術の開発期間T_dev[月] 依存関係Dependency リソース制約R_constraint</t>
+  </si>
+  <si>
+    <t xml:space="preserve">T_dev Dependency R_constraint</t>
+  </si>
+  <si>
+    <t xml:space="preserve">総開発期間T_total[月] クリティカルパス</t>
+  </si>
+  <si>
+    <t>ヘスペラスと水星ロボットは独立して並行開発可能</t>
+  </si>
+  <si>
+    <t>DEV-18</t>
+  </si>
+  <si>
+    <t>ヘスペラス-水星間の資源融通スケジュール</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ヘスペラス水素生産開始時期T_H2[年] 水星ダイソン環着工時期T_dyson[年]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">T_H2 T_dyson</t>
+  </si>
+  <si>
+    <t xml:space="preserve">水素供給開始時期T_supply[年] ダイソン環完成時期T_complete[年]</t>
+  </si>
+  <si>
+    <t>ヘスペラスが先に稼働し、水素を水星に供給してからダイソン環本格着工</t>
+  </si>
+  <si>
+    <t>DEV-19</t>
+  </si>
+  <si>
+    <t>コスト</t>
+  </si>
+  <si>
+    <t>ヘスペラス＋水星ダイソン環の総開発コスト</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ヘスペラス開発C_hesperas 水星ロボットC_robot 水星基地C_base パネル工場C_factory AI開発C_AI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C_hesperas C_robot C_base C_factory C_AI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">総コストC_total[USD] 内訳比率R_breakdown[%]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10年で約6兆USD。内訳：ヘスペラス30% ロボット25% 基地15% 工場20% AI10%</t>
+  </si>
+  <si>
+    <t>DEV-20</t>
+  </si>
+  <si>
+    <t>ヘスペラス連携によるコスト削減効果</t>
+  </si>
+  <si>
+    <t xml:space="preserve">単独開発コストC_single 連携開発C_coop 資源融通効果S_synergy</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C_single C_coop S_synergy</t>
+  </si>
+  <si>
+    <t xml:space="preserve">コスト削減額ΔC[USD] 削減率R_reduce[%]</t>
+  </si>
+  <si>
+    <t>ヘスペラスから水素・炭素・窒素を調達することで地球からの輸送コストを80%削減</t>
+  </si>
+  <si>
     <t>MER-01</t>
   </si>
   <si>
@@ -172,7 +559,7 @@
     <t>太陽風由来の微量水素・炭素を回収。不足分は地球輸送</t>
   </si>
   <si>
-    <t>26.07.09</t>
+    <t>金星から供給</t>
   </si>
   <si>
     <t>MER-07</t>
@@ -214,6 +601,12 @@
     <t>ロボットがロボットを作る自己複製の要</t>
   </si>
   <si>
+    <t>26.07.12</t>
+  </si>
+  <si>
+    <t>母船？水星上？両方？</t>
+  </si>
+  <si>
     <t>MER-09</t>
   </si>
   <si>
@@ -274,6 +667,12 @@
     <t>水星0.38Gならエレベータ建設が現実的</t>
   </si>
   <si>
+    <t>26.07.10</t>
+  </si>
+  <si>
+    <t>精密機器用</t>
+  </si>
+  <si>
     <t>MER-12</t>
   </si>
   <si>
@@ -292,6 +691,9 @@
     <t>大気がない水星ではマスドライバーが効率的</t>
   </si>
   <si>
+    <t>バルク資材</t>
+  </si>
+  <si>
     <t>MER-13</t>
   </si>
   <si>
@@ -331,6 +733,9 @@
     <t>往復5〜22分の遅延。緊急時は自律制御が必須</t>
   </si>
   <si>
+    <t>金星母船ヘスペラスと通信</t>
+  </si>
+  <si>
     <t>MER-15</t>
   </si>
   <si>
@@ -409,9 +814,6 @@
     <t>MER-19</t>
   </si>
   <si>
-    <t>コスト</t>
-  </si>
-  <si>
     <t>水星地表基地の総建設コスト</t>
   </si>
   <si>
@@ -457,15 +859,6 @@
     <t>済</t>
   </si>
   <si>
-    <t>金星から供給</t>
-  </si>
-  <si>
-    <t>26.07.10</t>
-  </si>
-  <si>
-    <t>金星母船ヘスペラスと通信</t>
-  </si>
-  <si>
     <t>課題カテゴリ</t>
   </si>
   <si>
@@ -475,9 +868,6 @@
     <t xml:space="preserve"> 計算内容</t>
   </si>
   <si>
-    <t xml:space="preserve"> ツール</t>
-  </si>
-  <si>
     <t xml:space="preserve"> 優先度</t>
   </si>
   <si>
@@ -493,12 +883,12 @@
     <t xml:space="preserve"> NVセンター間の光結合効率を最大化する配置の最適化</t>
   </si>
   <si>
-    <t xml:space="preserve"> Python + Maxima</t>
-  </si>
-  <si>
     <t xml:space="preserve"> ◎ 最優先</t>
   </si>
   <si>
+    <t>26.07.11</t>
+  </si>
+  <si>
     <t>c202</t>
   </si>
   <si>
@@ -508,9 +898,6 @@
     <t xml:space="preserve"> ナノダイヤモンドから検出器までの光子伝搬損失を計算</t>
   </si>
   <si>
-    <t xml:space="preserve"> Python</t>
-  </si>
-  <si>
     <t>c203</t>
   </si>
   <si>
@@ -523,9 +910,6 @@
     <t xml:space="preserve"> NVセンターのスピン状態に依存したゲートエラー率の理論計算</t>
   </si>
   <si>
-    <t xml:space="preserve"> Maxima</t>
-  </si>
-  <si>
     <t>26.06.23</t>
   </si>
   <si>
@@ -767,30 +1151,6 @@
   </si>
   <si>
     <t xml:space="preserve"> 量子ビット数に対する計算能力の理論曲線</t>
-  </si>
-  <si>
-    <t>#4001</t>
-  </si>
-  <si>
-    <t>多元宇宙穿孔（マルチ・パンクチャー）</t>
-  </si>
-  <si>
-    <t>Maxima</t>
-  </si>
-  <si>
-    <t>4.2光年以上の長距離穿孔への拡張数式</t>
-  </si>
-  <si>
-    <t>#903</t>
-  </si>
-  <si>
-    <t>銀河スケール・カルダシェフ査定</t>
-  </si>
-  <si>
-    <t>Python</t>
-  </si>
-  <si>
-    <t>タイプII文明（）への完全移行証明</t>
   </si>
   <si>
     <t>HZC-01</t>
@@ -1909,7 +2269,7 @@
     <t>軌道</t>
   </si>
   <si>
-    <t>プロキシマb→グリーゼ581の最適軌道</t>
+    <t>プロキシマb→くじら座タウ星の最適軌道</t>
   </si>
   <si>
     <t>出発位置r1=4.24ly</t>
@@ -2552,15 +2912,15 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="7">
+  <fonts count="6">
     <font>
       <sz val="11.000000"/>
       <name val="Calibri"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <strike/>
       <sz val="11.000000"/>
-      <color indexed="2"/>
       <name val="Calibri"/>
       <scheme val="minor"/>
     </font>
@@ -2576,14 +2936,9 @@
       <name val="IPAGothic"/>
     </font>
     <font>
-      <strike/>
       <sz val="11.000000"/>
+      <color indexed="2"/>
       <name val="Calibri"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <color theme="1"/>
-      <name val="Arial"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -2612,7 +2967,7 @@
   <cellStyleXfs count="1">
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="8">
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0"/>
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
@@ -2631,16 +2986,10 @@
     <xf fontId="4" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf fontId="5" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment readingOrder="0" vertical="top" wrapText="1"/>
+    <xf fontId="4" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top"/>
     </xf>
     <xf fontId="5" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf fontId="1" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf fontId="6" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -3132,7 +3481,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" ht="128.25">
+    <row r="2" ht="114">
       <c r="A2" s="1" t="s">
         <v>8</v>
       </c>
@@ -3158,7 +3507,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="3" ht="99.75">
+    <row r="3" ht="128.25">
       <c r="A3" s="1" t="s">
         <v>16</v>
       </c>
@@ -3184,7 +3533,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="4" ht="128.25">
+    <row r="4" ht="114">
       <c r="A4" s="1" t="s">
         <v>22</v>
       </c>
@@ -3235,11 +3584,13 @@
       <c r="H5" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="I5" s="1"/>
-    </row>
-    <row r="6" ht="142.5">
+      <c r="I5" s="1" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="6" ht="128.25">
       <c r="A6" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>9</v>
@@ -3248,24 +3599,24 @@
         <v>29</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="H6" s="1" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="7" ht="128.25">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="7" ht="142.5">
       <c r="A7" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B7" s="1" t="s">
         <v>9</v>
@@ -3274,33 +3625,33 @@
         <v>29</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="H7" s="1" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="I7" s="1" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="8" ht="114">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="8" ht="99.75">
       <c r="A8" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B8" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>49</v>
+        <v>29</v>
       </c>
       <c r="D8" s="1" t="s">
         <v>50</v>
@@ -3318,7 +3669,7 @@
         <v>54</v>
       </c>
       <c r="I8" s="1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="9" ht="114">
@@ -3329,33 +3680,33 @@
         <v>9</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>49</v>
+        <v>56</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="H9" s="1" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="10" ht="114">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="10" ht="99.75">
       <c r="A10" s="1" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B10" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="D10" s="1" t="s">
         <v>63</v>
@@ -3373,7 +3724,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="11" ht="114">
+    <row r="11" ht="142.5">
       <c r="A11" s="1" t="s">
         <v>68</v>
       </c>
@@ -3381,34 +3732,33 @@
         <v>9</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>62</v>
+        <v>69</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="H11" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="I11" s="2"/>
+        <v>74</v>
+      </c>
     </row>
     <row r="12" ht="114">
       <c r="A12" s="1" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="B12" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>75</v>
+        <v>69</v>
       </c>
       <c r="D12" s="1" t="s">
         <v>76</v>
@@ -3425,10 +3775,8 @@
       <c r="H12" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="I12" s="2"/>
-      <c r="J12" s="1"/>
-    </row>
-    <row r="13" ht="128.25">
+    </row>
+    <row r="13" ht="85.5">
       <c r="A13" s="1" t="s">
         <v>81</v>
       </c>
@@ -3436,33 +3784,33 @@
         <v>9</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="G13" s="1" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="H13" s="1" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="14" ht="99.75">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="14" ht="142.5">
       <c r="A14" s="1" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B14" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="D14" s="1" t="s">
         <v>89</v>
@@ -3480,7 +3828,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="15" ht="71.25">
+    <row r="15" ht="114">
       <c r="A15" s="1" t="s">
         <v>94</v>
       </c>
@@ -3488,7 +3836,7 @@
         <v>9</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="D15" s="1" t="s">
         <v>95</v>
@@ -3506,7 +3854,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="16" ht="142.5">
+    <row r="16" ht="114">
       <c r="A16" s="1" t="s">
         <v>100</v>
       </c>
@@ -3514,2548 +3862,152 @@
         <v>9</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>88</v>
+        <v>101</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="G16" s="1" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="H16" s="1" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="17" ht="99.75">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="17" ht="142.5">
       <c r="A17" s="1" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="B17" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>88</v>
+        <v>101</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="G17" s="1" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="H17" s="1" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="18" ht="142.5">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="18" ht="128.25">
       <c r="A18" s="1" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="B18" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="G18" s="1" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="H18" s="1" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="19" ht="142.5">
       <c r="A19" s="1" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="B19" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="G19" s="1" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="H19" s="1" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
     </row>
     <row r="20" ht="171">
       <c r="A20" s="1" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="B20" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="G20" s="1" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="H20" s="1" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="21" ht="156.75">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="21" ht="142.5">
       <c r="A21" s="1" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="B21" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="G21" s="1" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="H21" s="1" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="22" ht="51">
-      <c r="A22" s="3" t="s">
         <v>138</v>
-      </c>
-      <c r="B22" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="C22" s="4" t="s">
-        <v>139</v>
-      </c>
-      <c r="D22" s="4" t="s">
-        <v>140</v>
-      </c>
-      <c r="E22" s="4" t="s">
-        <v>141</v>
-      </c>
-    </row>
-  </sheetData>
-  <printOptions headings="0" gridLines="0"/>
-  <pageMargins left="0.70078740157480324" right="0.70078740157480324" top="0.75196850393700787" bottom="0.75196850393700787" header="0.29999999999999999" footer="0.29999999999999999"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" cellComments="none" useFirstPageNumber="0" errors="displayed" horizontalDpi="600" verticalDpi="600" copies="1"/>
-  <headerFooter/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac">
-  <sheetFormatPr baseColWidth="9" defaultRowHeight="14.25"/>
-  <cols>
-    <col min="1" max="16384" style="1" width="10.28125"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="28.5">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="2" ht="71.25">
-      <c r="A2" s="1" t="s">
-        <v>254</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>255</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>256</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>257</v>
-      </c>
-      <c r="E2" s="1" t="s">
-        <v>258</v>
-      </c>
-      <c r="F2" s="1" t="s">
-        <v>259</v>
-      </c>
-      <c r="G2" s="1" t="s">
-        <v>260</v>
-      </c>
-      <c r="H2" s="1" t="s">
-        <v>261</v>
-      </c>
-      <c r="I2" s="1" t="s">
-        <v>262</v>
-      </c>
-    </row>
-    <row r="3" ht="85.5">
-      <c r="A3" s="1" t="s">
-        <v>263</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>255</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>256</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>264</v>
-      </c>
-      <c r="E3" s="1" t="s">
-        <v>265</v>
-      </c>
-      <c r="F3" s="1" t="s">
-        <v>266</v>
-      </c>
-      <c r="G3" s="1" t="s">
-        <v>267</v>
-      </c>
-      <c r="H3" s="1" t="s">
-        <v>268</v>
-      </c>
-    </row>
-    <row r="4" ht="99.75">
-      <c r="A4" s="1" t="s">
-        <v>269</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>255</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>270</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>271</v>
-      </c>
-      <c r="E4" s="1" t="s">
-        <v>272</v>
-      </c>
-      <c r="F4" s="1" t="s">
-        <v>273</v>
-      </c>
-      <c r="G4" s="1" t="s">
-        <v>274</v>
-      </c>
-      <c r="H4" s="1" t="s">
-        <v>275</v>
-      </c>
-    </row>
-    <row r="5" ht="99.75">
-      <c r="A5" s="1" t="s">
-        <v>276</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>255</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>270</v>
-      </c>
-      <c r="D5" s="1" t="s">
-        <v>277</v>
-      </c>
-      <c r="E5" s="1" t="s">
-        <v>278</v>
-      </c>
-      <c r="F5" s="1" t="s">
-        <v>279</v>
-      </c>
-      <c r="G5" s="1" t="s">
-        <v>280</v>
-      </c>
-      <c r="H5" s="1" t="s">
-        <v>281</v>
-      </c>
-    </row>
-    <row r="6" ht="85.5">
-      <c r="A6" s="1" t="s">
-        <v>282</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>255</v>
-      </c>
-      <c r="C6" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="D6" s="1" t="s">
-        <v>283</v>
-      </c>
-      <c r="E6" s="1" t="s">
-        <v>284</v>
-      </c>
-      <c r="F6" s="1" t="s">
-        <v>285</v>
-      </c>
-      <c r="G6" s="1" t="s">
-        <v>286</v>
-      </c>
-      <c r="H6" s="1" t="s">
-        <v>287</v>
-      </c>
-    </row>
-    <row r="7" ht="71.25">
-      <c r="A7" s="1" t="s">
-        <v>288</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>255</v>
-      </c>
-      <c r="C7" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="D7" s="1" t="s">
-        <v>289</v>
-      </c>
-      <c r="E7" s="1" t="s">
-        <v>290</v>
-      </c>
-      <c r="F7" s="1" t="s">
-        <v>291</v>
-      </c>
-      <c r="G7" s="1" t="s">
-        <v>292</v>
-      </c>
-      <c r="H7" s="1" t="s">
-        <v>293</v>
-      </c>
-    </row>
-    <row r="8" ht="71.25">
-      <c r="A8" s="1" t="s">
-        <v>294</v>
-      </c>
-      <c r="B8" s="1" t="s">
-        <v>255</v>
-      </c>
-      <c r="C8" s="1" t="s">
-        <v>295</v>
-      </c>
-      <c r="D8" s="1" t="s">
-        <v>296</v>
-      </c>
-      <c r="E8" s="1" t="s">
-        <v>297</v>
-      </c>
-      <c r="F8" s="1" t="s">
-        <v>298</v>
-      </c>
-      <c r="G8" s="1" t="s">
-        <v>299</v>
-      </c>
-      <c r="H8" s="1" t="s">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="9" ht="99.75">
-      <c r="A9" s="1" t="s">
-        <v>301</v>
-      </c>
-      <c r="B9" s="1" t="s">
-        <v>255</v>
-      </c>
-      <c r="C9" s="1" t="s">
-        <v>295</v>
-      </c>
-      <c r="D9" s="1" t="s">
-        <v>302</v>
-      </c>
-      <c r="E9" s="1" t="s">
-        <v>303</v>
-      </c>
-      <c r="F9" s="1" t="s">
-        <v>304</v>
-      </c>
-      <c r="G9" s="1" t="s">
-        <v>305</v>
-      </c>
-      <c r="H9" s="1" t="s">
-        <v>306</v>
-      </c>
-    </row>
-    <row r="10" ht="99.75">
-      <c r="A10" s="1" t="s">
-        <v>307</v>
-      </c>
-      <c r="B10" s="1" t="s">
-        <v>255</v>
-      </c>
-      <c r="C10" s="1" t="s">
-        <v>308</v>
-      </c>
-      <c r="D10" s="1" t="s">
-        <v>309</v>
-      </c>
-      <c r="E10" s="1" t="s">
-        <v>310</v>
-      </c>
-      <c r="F10" s="1" t="s">
-        <v>311</v>
-      </c>
-      <c r="G10" s="1" t="s">
-        <v>312</v>
-      </c>
-      <c r="H10" s="1" t="s">
-        <v>313</v>
-      </c>
-    </row>
-    <row r="11" ht="85.5">
-      <c r="A11" s="1" t="s">
-        <v>314</v>
-      </c>
-      <c r="B11" s="1" t="s">
-        <v>255</v>
-      </c>
-      <c r="C11" s="1" t="s">
-        <v>308</v>
-      </c>
-      <c r="D11" s="1" t="s">
-        <v>315</v>
-      </c>
-      <c r="E11" s="1" t="s">
-        <v>316</v>
-      </c>
-      <c r="F11" s="1" t="s">
-        <v>317</v>
-      </c>
-      <c r="G11" s="1" t="s">
-        <v>318</v>
-      </c>
-      <c r="H11" s="1" t="s">
-        <v>319</v>
-      </c>
-    </row>
-    <row r="12" ht="85.5">
-      <c r="A12" s="1" t="s">
-        <v>320</v>
-      </c>
-      <c r="B12" s="1" t="s">
-        <v>255</v>
-      </c>
-      <c r="C12" s="1" t="s">
-        <v>321</v>
-      </c>
-      <c r="D12" s="1" t="s">
-        <v>322</v>
-      </c>
-      <c r="E12" s="1" t="s">
-        <v>323</v>
-      </c>
-      <c r="F12" s="1" t="s">
-        <v>324</v>
-      </c>
-      <c r="G12" s="1" t="s">
-        <v>325</v>
-      </c>
-      <c r="H12" s="1" t="s">
-        <v>326</v>
-      </c>
-    </row>
-    <row r="13" ht="71.25">
-      <c r="A13" s="1" t="s">
-        <v>327</v>
-      </c>
-      <c r="B13" s="1" t="s">
-        <v>255</v>
-      </c>
-      <c r="C13" s="1" t="s">
-        <v>321</v>
-      </c>
-      <c r="D13" s="1" t="s">
-        <v>328</v>
-      </c>
-      <c r="E13" s="1" t="s">
-        <v>329</v>
-      </c>
-      <c r="F13" s="1" t="s">
-        <v>330</v>
-      </c>
-      <c r="G13" s="1" t="s">
-        <v>331</v>
-      </c>
-      <c r="H13" s="1" t="s">
-        <v>332</v>
-      </c>
-    </row>
-    <row r="14" ht="71.25">
-      <c r="A14" s="1" t="s">
-        <v>333</v>
-      </c>
-      <c r="B14" s="1" t="s">
-        <v>255</v>
-      </c>
-      <c r="C14" s="1" t="s">
-        <v>334</v>
-      </c>
-      <c r="D14" s="1" t="s">
-        <v>335</v>
-      </c>
-      <c r="E14" s="1" t="s">
-        <v>336</v>
-      </c>
-      <c r="F14" s="1" t="s">
-        <v>337</v>
-      </c>
-      <c r="G14" s="1" t="s">
-        <v>338</v>
-      </c>
-      <c r="H14" s="1" t="s">
-        <v>339</v>
-      </c>
-    </row>
-    <row r="15" ht="71.25">
-      <c r="A15" s="1" t="s">
-        <v>340</v>
-      </c>
-      <c r="B15" s="1" t="s">
-        <v>255</v>
-      </c>
-      <c r="C15" s="1" t="s">
-        <v>334</v>
-      </c>
-      <c r="D15" s="1" t="s">
-        <v>341</v>
-      </c>
-      <c r="E15" s="1" t="s">
-        <v>342</v>
-      </c>
-      <c r="F15" s="1" t="s">
-        <v>343</v>
-      </c>
-      <c r="G15" s="1" t="s">
-        <v>344</v>
-      </c>
-      <c r="H15" s="1" t="s">
-        <v>345</v>
-      </c>
-    </row>
-    <row r="16" ht="85.5">
-      <c r="A16" s="1" t="s">
-        <v>346</v>
-      </c>
-      <c r="B16" s="1" t="s">
-        <v>255</v>
-      </c>
-      <c r="C16" s="1" t="s">
-        <v>347</v>
-      </c>
-      <c r="D16" s="1" t="s">
-        <v>348</v>
-      </c>
-      <c r="E16" s="1" t="s">
-        <v>349</v>
-      </c>
-      <c r="F16" s="1" t="s">
-        <v>350</v>
-      </c>
-      <c r="G16" s="1" t="s">
-        <v>351</v>
-      </c>
-      <c r="H16" s="1" t="s">
-        <v>352</v>
-      </c>
-    </row>
-    <row r="17" ht="85.5">
-      <c r="A17" s="1" t="s">
-        <v>353</v>
-      </c>
-      <c r="B17" s="1" t="s">
-        <v>255</v>
-      </c>
-      <c r="C17" s="1" t="s">
-        <v>347</v>
-      </c>
-      <c r="D17" s="1" t="s">
-        <v>354</v>
-      </c>
-      <c r="E17" s="1" t="s">
-        <v>355</v>
-      </c>
-      <c r="F17" s="1" t="s">
-        <v>356</v>
-      </c>
-      <c r="G17" s="1" t="s">
-        <v>357</v>
-      </c>
-      <c r="H17" s="1" t="s">
-        <v>358</v>
-      </c>
-    </row>
-    <row r="18" ht="85.5">
-      <c r="A18" s="1" t="s">
-        <v>359</v>
-      </c>
-      <c r="B18" s="1" t="s">
-        <v>255</v>
-      </c>
-      <c r="C18" s="1" t="s">
-        <v>360</v>
-      </c>
-      <c r="D18" s="1" t="s">
-        <v>361</v>
-      </c>
-      <c r="E18" s="1" t="s">
-        <v>362</v>
-      </c>
-      <c r="F18" s="1" t="s">
-        <v>363</v>
-      </c>
-      <c r="G18" s="1" t="s">
-        <v>364</v>
-      </c>
-      <c r="H18" s="1" t="s">
-        <v>365</v>
-      </c>
-    </row>
-    <row r="19" ht="99.75">
-      <c r="A19" s="1" t="s">
-        <v>366</v>
-      </c>
-      <c r="B19" s="1" t="s">
-        <v>255</v>
-      </c>
-      <c r="C19" s="1" t="s">
-        <v>360</v>
-      </c>
-      <c r="D19" s="1" t="s">
-        <v>367</v>
-      </c>
-      <c r="E19" s="1" t="s">
-        <v>368</v>
-      </c>
-      <c r="F19" s="1" t="s">
-        <v>369</v>
-      </c>
-      <c r="G19" s="1" t="s">
-        <v>370</v>
-      </c>
-      <c r="H19" s="1" t="s">
-        <v>371</v>
-      </c>
-    </row>
-    <row r="20" ht="99.75">
-      <c r="A20" s="1" t="s">
-        <v>372</v>
-      </c>
-      <c r="B20" s="1" t="s">
-        <v>255</v>
-      </c>
-      <c r="C20" s="1" t="s">
-        <v>126</v>
-      </c>
-      <c r="D20" s="1" t="s">
-        <v>373</v>
-      </c>
-      <c r="E20" s="1" t="s">
-        <v>374</v>
-      </c>
-      <c r="F20" s="1" t="s">
-        <v>375</v>
-      </c>
-      <c r="G20" s="1" t="s">
-        <v>376</v>
-      </c>
-      <c r="H20" s="1" t="s">
-        <v>377</v>
-      </c>
-    </row>
-    <row r="21" ht="114">
-      <c r="A21" s="1" t="s">
-        <v>378</v>
-      </c>
-      <c r="B21" s="1" t="s">
-        <v>255</v>
-      </c>
-      <c r="C21" s="1" t="s">
-        <v>126</v>
-      </c>
-      <c r="D21" s="1" t="s">
-        <v>379</v>
-      </c>
-      <c r="E21" s="1" t="s">
-        <v>380</v>
-      </c>
-      <c r="F21" s="1" t="s">
-        <v>381</v>
-      </c>
-      <c r="G21" s="1" t="s">
-        <v>382</v>
-      </c>
-      <c r="H21" s="1" t="s">
-        <v>383</v>
-      </c>
-    </row>
-    <row r="22" ht="51">
-      <c r="A22" s="3" t="s">
-        <v>384</v>
-      </c>
-      <c r="B22" s="4" t="s">
-        <v>385</v>
-      </c>
-      <c r="C22" s="3" t="s">
-        <v>386</v>
-      </c>
-      <c r="D22" s="4" t="s">
-        <v>387</v>
-      </c>
-      <c r="E22" s="4" t="s">
-        <v>388</v>
-      </c>
-      <c r="F22" s="4" t="s">
-        <v>141</v>
-      </c>
-      <c r="G22" s="4" t="s">
-        <v>389</v>
-      </c>
-    </row>
-    <row r="23" ht="14.25">
-      <c r="A23" s="1"/>
-      <c r="B23" s="1"/>
-      <c r="C23" s="1"/>
-      <c r="D23" s="1"/>
-      <c r="E23" s="1"/>
-      <c r="F23" s="1"/>
-      <c r="G23" s="1"/>
-    </row>
-  </sheetData>
-  <printOptions headings="0" gridLines="0"/>
-  <pageMargins left="0.70078740157480324" right="0.70078740157480324" top="0.75196850393700787" bottom="0.75196850393700787" header="0.29999999999999999" footer="0.29999999999999999"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" cellComments="none" useFirstPageNumber="0" errors="displayed" horizontalDpi="600" verticalDpi="600" copies="1"/>
-  <headerFooter/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac">
-  <sheetFormatPr baseColWidth="9" defaultRowHeight="14.25"/>
-  <cols>
-    <col min="1" max="7" style="1" width="10.28125"/>
-    <col customWidth="1" min="8" max="8" style="1" width="16.57421875"/>
-    <col customWidth="1" min="9" max="9" style="1" width="19.421875"/>
-    <col customWidth="1" min="10" max="10" style="1" width="15.57421875"/>
-    <col customWidth="1" min="11" max="11" style="1" width="13.8515625"/>
-    <col min="12" max="16384" style="1" width="10.28125"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="28.5">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="2" ht="57">
-      <c r="A2" s="1" t="s">
-        <v>390</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>391</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>392</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>393</v>
-      </c>
-      <c r="E2" s="1" t="s">
-        <v>394</v>
-      </c>
-      <c r="F2" s="1" t="s">
-        <v>395</v>
-      </c>
-      <c r="G2" s="1" t="s">
-        <v>396</v>
-      </c>
-      <c r="H2" s="1" t="s">
-        <v>397</v>
-      </c>
-      <c r="I2" s="1" t="s">
-        <v>398</v>
-      </c>
-      <c r="J2" s="1"/>
-    </row>
-    <row r="3" ht="57">
-      <c r="A3" s="1" t="s">
-        <v>399</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>391</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>400</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>401</v>
-      </c>
-      <c r="E3" s="1" t="s">
-        <v>402</v>
-      </c>
-      <c r="F3" s="1" t="s">
-        <v>403</v>
-      </c>
-      <c r="G3" s="1" t="s">
-        <v>404</v>
-      </c>
-      <c r="H3" s="1" t="s">
-        <v>405</v>
-      </c>
-    </row>
-    <row r="4" ht="71.25">
-      <c r="A4" s="1" t="s">
-        <v>406</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>407</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>408</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>409</v>
-      </c>
-      <c r="E4" s="1" t="s">
-        <v>410</v>
-      </c>
-      <c r="F4" s="1" t="s">
-        <v>411</v>
-      </c>
-      <c r="G4" s="1" t="s">
-        <v>412</v>
-      </c>
-      <c r="H4" s="1" t="s">
-        <v>413</v>
-      </c>
-    </row>
-    <row r="5" ht="71.25">
-      <c r="A5" s="1" t="s">
-        <v>414</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>407</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>415</v>
-      </c>
-      <c r="D5" s="1" t="s">
-        <v>416</v>
-      </c>
-      <c r="E5" s="1" t="s">
-        <v>417</v>
-      </c>
-      <c r="F5" s="1" t="s">
-        <v>418</v>
-      </c>
-      <c r="G5" s="1" t="s">
-        <v>419</v>
-      </c>
-      <c r="H5" s="1" t="s">
-        <v>420</v>
-      </c>
-    </row>
-    <row r="6" ht="71.25">
-      <c r="A6" s="1" t="s">
-        <v>421</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>422</v>
-      </c>
-      <c r="C6" s="1" t="s">
-        <v>423</v>
-      </c>
-      <c r="D6" s="1" t="s">
-        <v>424</v>
-      </c>
-      <c r="E6" s="1" t="s">
-        <v>425</v>
-      </c>
-      <c r="F6" s="1" t="s">
-        <v>426</v>
-      </c>
-      <c r="G6" s="1" t="s">
-        <v>427</v>
-      </c>
-      <c r="H6" s="1" t="s">
-        <v>428</v>
-      </c>
-      <c r="I6" s="1" t="s">
-        <v>429</v>
-      </c>
-      <c r="J6" s="1" t="s">
-        <v>430</v>
-      </c>
-      <c r="K6" s="1"/>
-    </row>
-    <row r="7" ht="57">
-      <c r="A7" s="1" t="s">
-        <v>431</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>422</v>
-      </c>
-      <c r="C7" s="1" t="s">
-        <v>432</v>
-      </c>
-      <c r="D7" s="1" t="s">
-        <v>433</v>
-      </c>
-      <c r="E7" s="1" t="s">
-        <v>434</v>
-      </c>
-      <c r="F7" s="1" t="s">
-        <v>435</v>
-      </c>
-      <c r="G7" s="1" t="s">
-        <v>436</v>
-      </c>
-      <c r="H7" s="1" t="s">
-        <v>437</v>
-      </c>
-    </row>
-    <row r="8" ht="71.25">
-      <c r="A8" s="1" t="s">
-        <v>438</v>
-      </c>
-      <c r="B8" s="1" t="s">
-        <v>439</v>
-      </c>
-      <c r="C8" s="1" t="s">
-        <v>440</v>
-      </c>
-      <c r="D8" s="1" t="s">
-        <v>441</v>
-      </c>
-      <c r="E8" s="1" t="s">
-        <v>442</v>
-      </c>
-      <c r="F8" s="1" t="s">
-        <v>443</v>
-      </c>
-      <c r="G8" s="1" t="s">
-        <v>444</v>
-      </c>
-      <c r="H8" s="1" t="s">
-        <v>445</v>
-      </c>
-    </row>
-    <row r="9" ht="57">
-      <c r="A9" s="1" t="s">
-        <v>446</v>
-      </c>
-      <c r="B9" s="1" t="s">
-        <v>439</v>
-      </c>
-      <c r="C9" s="1" t="s">
-        <v>447</v>
-      </c>
-      <c r="D9" s="1" t="s">
-        <v>448</v>
-      </c>
-      <c r="E9" s="1" t="s">
-        <v>449</v>
-      </c>
-      <c r="F9" s="1" t="s">
-        <v>450</v>
-      </c>
-      <c r="G9" s="1" t="s">
-        <v>451</v>
-      </c>
-      <c r="H9" s="1" t="s">
-        <v>452</v>
-      </c>
-    </row>
-    <row r="10" ht="57">
-      <c r="A10" s="1" t="s">
-        <v>453</v>
-      </c>
-      <c r="B10" s="1" t="s">
-        <v>439</v>
-      </c>
-      <c r="C10" s="1" t="s">
-        <v>454</v>
-      </c>
-      <c r="D10" s="1" t="s">
-        <v>455</v>
-      </c>
-      <c r="E10" s="1" t="s">
-        <v>456</v>
-      </c>
-      <c r="F10" s="1" t="s">
-        <v>457</v>
-      </c>
-      <c r="G10" s="1" t="s">
-        <v>458</v>
-      </c>
-      <c r="H10" s="1" t="s">
-        <v>459</v>
-      </c>
-    </row>
-    <row r="11" ht="42.75">
-      <c r="A11" s="1" t="s">
-        <v>460</v>
-      </c>
-      <c r="B11" s="1" t="s">
-        <v>461</v>
-      </c>
-      <c r="C11" s="1" t="s">
-        <v>462</v>
-      </c>
-      <c r="D11" s="1" t="s">
-        <v>463</v>
-      </c>
-      <c r="E11" s="1" t="s">
-        <v>464</v>
-      </c>
-      <c r="F11" s="1" t="s">
-        <v>465</v>
-      </c>
-      <c r="G11" s="1" t="s">
-        <v>466</v>
-      </c>
-      <c r="H11" s="1" t="s">
-        <v>467</v>
-      </c>
-    </row>
-    <row r="12" ht="71.25">
-      <c r="A12" s="1" t="s">
-        <v>468</v>
-      </c>
-      <c r="B12" s="1" t="s">
-        <v>461</v>
-      </c>
-      <c r="C12" s="1" t="s">
-        <v>113</v>
-      </c>
-      <c r="D12" s="1" t="s">
-        <v>469</v>
-      </c>
-      <c r="E12" s="1" t="s">
-        <v>470</v>
-      </c>
-      <c r="F12" s="1" t="s">
-        <v>471</v>
-      </c>
-      <c r="G12" s="1" t="s">
-        <v>472</v>
-      </c>
-      <c r="H12" s="1" t="s">
-        <v>473</v>
-      </c>
-    </row>
-    <row r="13" ht="71.25">
-      <c r="A13" s="1" t="s">
-        <v>474</v>
-      </c>
-      <c r="B13" s="1" t="s">
-        <v>461</v>
-      </c>
-      <c r="C13" s="1" t="s">
-        <v>475</v>
-      </c>
-      <c r="D13" s="1" t="s">
-        <v>476</v>
-      </c>
-      <c r="E13" s="1" t="s">
-        <v>477</v>
-      </c>
-      <c r="F13" s="1" t="s">
-        <v>478</v>
-      </c>
-      <c r="G13" s="1" t="s">
-        <v>479</v>
-      </c>
-      <c r="H13" s="1" t="s">
-        <v>480</v>
-      </c>
-    </row>
-  </sheetData>
-  <printOptions headings="0" gridLines="0"/>
-  <pageMargins left="0.70078740157480324" right="0.70078740157480324" top="0.75196850393700787" bottom="0.75196850393700787" header="0.29999999999999999" footer="0.29999999999999999"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" cellComments="none" useFirstPageNumber="0" errors="displayed" horizontalDpi="600" verticalDpi="600" copies="1"/>
-  <headerFooter/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac">
-  <sheetFormatPr baseColWidth="9" defaultRowHeight="14.25"/>
-  <cols>
-    <col min="1" max="4" style="1" width="10.28125"/>
-    <col customWidth="1" min="5" max="5" style="1" width="14.421875"/>
-    <col min="6" max="16384" style="1" width="10.28125"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="14.25">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="2" ht="99.75">
-      <c r="A2" s="1" t="s">
-        <v>481</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>422</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>482</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>483</v>
-      </c>
-      <c r="E2" s="1" t="s">
-        <v>484</v>
-      </c>
-      <c r="F2" s="1" t="s">
-        <v>485</v>
-      </c>
-      <c r="G2" s="1" t="s">
-        <v>486</v>
-      </c>
-    </row>
-    <row r="3" ht="71.25">
-      <c r="A3" s="1" t="s">
-        <v>487</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>422</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>488</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>489</v>
-      </c>
-      <c r="E3" s="1" t="s">
-        <v>490</v>
-      </c>
-      <c r="F3" s="1" t="s">
-        <v>484</v>
-      </c>
-      <c r="G3" s="1" t="s">
-        <v>491</v>
-      </c>
-      <c r="H3" s="1" t="s">
-        <v>492</v>
-      </c>
-    </row>
-    <row r="4" ht="57">
-      <c r="A4" s="1" t="s">
-        <v>493</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>422</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>494</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>495</v>
-      </c>
-      <c r="E4" s="1" t="s">
-        <v>496</v>
-      </c>
-      <c r="F4" s="1" t="s">
-        <v>497</v>
-      </c>
-      <c r="G4" s="1" t="s">
-        <v>498</v>
-      </c>
-      <c r="H4" s="1" t="s">
-        <v>499</v>
-      </c>
-    </row>
-    <row r="5" ht="42.75">
-      <c r="A5" s="1" t="s">
-        <v>500</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>501</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>502</v>
-      </c>
-      <c r="D5" s="1" t="s">
-        <v>503</v>
-      </c>
-      <c r="E5" s="1" t="s">
-        <v>504</v>
-      </c>
-      <c r="F5" s="1" t="s">
-        <v>505</v>
-      </c>
-      <c r="G5" s="1" t="s">
-        <v>506</v>
-      </c>
-      <c r="H5" s="1" t="s">
-        <v>507</v>
-      </c>
-      <c r="I5" s="1" t="s">
-        <v>508</v>
-      </c>
-    </row>
-    <row r="6" ht="71.25">
-      <c r="A6" s="1" t="s">
-        <v>509</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>501</v>
-      </c>
-      <c r="C6" s="1" t="s">
-        <v>510</v>
-      </c>
-      <c r="D6" s="1" t="s">
-        <v>511</v>
-      </c>
-      <c r="E6" s="1" t="s">
-        <v>512</v>
-      </c>
-      <c r="F6" s="1" t="s">
-        <v>513</v>
-      </c>
-      <c r="G6" s="1" t="s">
-        <v>514</v>
-      </c>
-    </row>
-    <row r="7" ht="57">
-      <c r="A7" s="1" t="s">
-        <v>515</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>501</v>
-      </c>
-      <c r="C7" s="1" t="s">
-        <v>516</v>
-      </c>
-      <c r="D7" s="1" t="s">
-        <v>517</v>
-      </c>
-      <c r="E7" s="1" t="s">
-        <v>518</v>
-      </c>
-      <c r="F7" s="1" t="s">
-        <v>519</v>
-      </c>
-      <c r="G7" s="1" t="s">
-        <v>520</v>
-      </c>
-      <c r="H7" s="1" t="s">
-        <v>521</v>
-      </c>
-    </row>
-    <row r="8" ht="57">
-      <c r="A8" s="1" t="s">
-        <v>522</v>
-      </c>
-      <c r="B8" s="1" t="s">
-        <v>501</v>
-      </c>
-      <c r="C8" s="1" t="s">
-        <v>523</v>
-      </c>
-      <c r="D8" s="1" t="s">
-        <v>524</v>
-      </c>
-      <c r="E8" s="1" t="s">
-        <v>525</v>
-      </c>
-      <c r="F8" s="1" t="s">
-        <v>526</v>
-      </c>
-      <c r="G8" s="1" t="s">
-        <v>527</v>
-      </c>
-      <c r="H8" s="1" t="s">
-        <v>528</v>
-      </c>
-    </row>
-    <row r="9" ht="114">
-      <c r="A9" s="1" t="s">
-        <v>529</v>
-      </c>
-      <c r="B9" s="1" t="s">
-        <v>530</v>
-      </c>
-      <c r="C9" s="1" t="s">
-        <v>531</v>
-      </c>
-      <c r="D9" s="1" t="s">
-        <v>532</v>
-      </c>
-      <c r="E9" s="1" t="s">
-        <v>533</v>
-      </c>
-      <c r="F9" s="1" t="s">
-        <v>534</v>
-      </c>
-      <c r="G9" s="1" t="s">
-        <v>535</v>
-      </c>
-      <c r="H9" s="1" t="s">
-        <v>536</v>
-      </c>
-      <c r="I9" s="1" t="s">
-        <v>537</v>
-      </c>
-    </row>
-    <row r="10" ht="99.75">
-      <c r="A10" s="1" t="s">
-        <v>538</v>
-      </c>
-      <c r="B10" s="1" t="s">
-        <v>530</v>
-      </c>
-      <c r="C10" s="1" t="s">
-        <v>539</v>
-      </c>
-      <c r="D10" s="1" t="s">
-        <v>540</v>
-      </c>
-      <c r="E10" s="1" t="s">
-        <v>541</v>
-      </c>
-      <c r="F10" s="1" t="s">
-        <v>542</v>
-      </c>
-      <c r="G10" s="1" t="s">
-        <v>543</v>
-      </c>
-      <c r="H10" s="1" t="s">
-        <v>544</v>
-      </c>
-    </row>
-    <row r="11" s="5" customFormat="1" ht="99.75">
-      <c r="A11" s="5" t="s">
-        <v>545</v>
-      </c>
-      <c r="B11" s="5" t="s">
-        <v>530</v>
-      </c>
-      <c r="C11" s="5" t="s">
-        <v>546</v>
-      </c>
-      <c r="D11" s="5" t="s">
-        <v>547</v>
-      </c>
-      <c r="E11" s="5" t="s">
-        <v>548</v>
-      </c>
-      <c r="F11" s="5" t="s">
-        <v>549</v>
-      </c>
-      <c r="G11" s="5" t="s">
-        <v>550</v>
-      </c>
-      <c r="H11" s="5" t="s">
-        <v>551</v>
-      </c>
-    </row>
-    <row r="12" ht="85.5">
-      <c r="A12" s="1" t="s">
-        <v>552</v>
-      </c>
-      <c r="B12" s="1" t="s">
-        <v>530</v>
-      </c>
-      <c r="C12" s="1" t="s">
-        <v>553</v>
-      </c>
-      <c r="D12" s="1" t="s">
-        <v>554</v>
-      </c>
-      <c r="E12" s="1" t="s">
-        <v>555</v>
-      </c>
-      <c r="F12" s="1" t="s">
-        <v>556</v>
-      </c>
-      <c r="G12" s="1" t="s">
-        <v>557</v>
-      </c>
-      <c r="H12" s="1" t="s">
-        <v>558</v>
-      </c>
-    </row>
-    <row r="13" ht="85.5">
-      <c r="A13" s="1" t="s">
-        <v>559</v>
-      </c>
-      <c r="B13" s="1" t="s">
-        <v>530</v>
-      </c>
-      <c r="C13" s="1" t="s">
-        <v>560</v>
-      </c>
-      <c r="D13" s="1" t="s">
-        <v>561</v>
-      </c>
-      <c r="E13" s="1" t="s">
-        <v>562</v>
-      </c>
-      <c r="F13" s="1" t="s">
-        <v>563</v>
-      </c>
-      <c r="G13" s="1" t="s">
-        <v>564</v>
-      </c>
-      <c r="H13" s="1" t="s">
-        <v>565</v>
-      </c>
-    </row>
-    <row r="14" s="2" customFormat="1" ht="42.75">
-      <c r="A14" s="2" t="s">
-        <v>566</v>
-      </c>
-      <c r="B14" s="2" t="s">
-        <v>567</v>
-      </c>
-      <c r="C14" s="2" t="s">
-        <v>568</v>
-      </c>
-      <c r="D14" s="2" t="s">
-        <v>569</v>
-      </c>
-      <c r="E14" s="2" t="s">
-        <v>570</v>
-      </c>
-      <c r="F14" s="2" t="s">
-        <v>571</v>
-      </c>
-      <c r="G14" s="2" t="s">
-        <v>572</v>
-      </c>
-      <c r="I14" s="2" t="s">
-        <v>573</v>
-      </c>
-      <c r="J14" s="8" t="s">
-        <v>574</v>
-      </c>
-    </row>
-  </sheetData>
-  <printOptions headings="0" gridLines="0"/>
-  <pageMargins left="0.70078740157480324" right="0.70078740157480324" top="0.75196850393700787" bottom="0.75196850393700787" header="0.29999999999999999" footer="0.29999999999999999"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" cellComments="none" useFirstPageNumber="0" errors="displayed" horizontalDpi="600" verticalDpi="600" copies="1"/>
-  <headerFooter/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac">
-  <sheetFormatPr baseColWidth="9" defaultRowHeight="14.25"/>
-  <cols>
-    <col min="1" max="16384" style="1" width="10.28125"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>575</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="2" ht="57">
-      <c r="A2" s="1" t="s">
-        <v>576</v>
-      </c>
-      <c r="B2" s="1">
-        <v>0</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>577</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>578</v>
-      </c>
-      <c r="E2" s="1" t="s">
-        <v>579</v>
-      </c>
-      <c r="F2" s="1" t="s">
-        <v>580</v>
-      </c>
-      <c r="G2" s="1" t="s">
-        <v>581</v>
-      </c>
-      <c r="H2" s="1" t="s">
-        <v>582</v>
-      </c>
-      <c r="I2" s="1" t="s">
-        <v>583</v>
-      </c>
-      <c r="J2" s="1" t="s">
-        <v>584</v>
-      </c>
-    </row>
-    <row r="3" ht="71.25">
-      <c r="A3" s="1" t="s">
-        <v>585</v>
-      </c>
-      <c r="B3" s="1">
-        <v>0</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>586</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>587</v>
-      </c>
-      <c r="E3" s="1" t="s">
-        <v>588</v>
-      </c>
-      <c r="F3" s="1" t="s">
-        <v>589</v>
-      </c>
-      <c r="G3" s="1" t="s">
-        <v>590</v>
-      </c>
-      <c r="H3" s="1" t="s">
-        <v>591</v>
-      </c>
-    </row>
-    <row r="4" ht="57">
-      <c r="A4" s="1" t="s">
-        <v>592</v>
-      </c>
-      <c r="B4" s="1">
-        <v>1</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>593</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>594</v>
-      </c>
-      <c r="E4" s="1" t="s">
-        <v>595</v>
-      </c>
-      <c r="F4" s="1" t="s">
-        <v>596</v>
-      </c>
-      <c r="G4" s="1" t="s">
-        <v>597</v>
-      </c>
-      <c r="H4" s="1" t="s">
-        <v>598</v>
-      </c>
-    </row>
-    <row r="5" ht="42.75">
-      <c r="A5" s="1" t="s">
-        <v>599</v>
-      </c>
-      <c r="B5" s="1">
-        <v>1</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="D5" s="1" t="s">
-        <v>600</v>
-      </c>
-      <c r="E5" s="1" t="s">
-        <v>601</v>
-      </c>
-      <c r="F5" s="1" t="s">
-        <v>602</v>
-      </c>
-      <c r="G5" s="1" t="s">
-        <v>603</v>
-      </c>
-      <c r="H5" s="1" t="s">
-        <v>604</v>
-      </c>
-    </row>
-    <row r="6" ht="71.25">
-      <c r="A6" s="1" t="s">
-        <v>605</v>
-      </c>
-      <c r="B6" s="1">
-        <v>2</v>
-      </c>
-      <c r="C6" s="1" t="s">
-        <v>606</v>
-      </c>
-      <c r="D6" s="1" t="s">
-        <v>607</v>
-      </c>
-      <c r="E6" s="1" t="s">
-        <v>608</v>
-      </c>
-      <c r="F6" s="1" t="s">
-        <v>609</v>
-      </c>
-      <c r="G6" s="1" t="s">
-        <v>610</v>
-      </c>
-      <c r="H6" s="1" t="s">
-        <v>611</v>
-      </c>
-    </row>
-    <row r="7" ht="57">
-      <c r="A7" s="1" t="s">
-        <v>612</v>
-      </c>
-      <c r="B7" s="1">
-        <v>2</v>
-      </c>
-      <c r="C7" s="1" t="s">
-        <v>613</v>
-      </c>
-      <c r="D7" s="1" t="s">
-        <v>614</v>
-      </c>
-      <c r="E7" s="1" t="s">
-        <v>615</v>
-      </c>
-      <c r="F7" s="1" t="s">
-        <v>616</v>
-      </c>
-      <c r="G7" s="1" t="s">
-        <v>617</v>
-      </c>
-      <c r="H7" s="1" t="s">
-        <v>618</v>
-      </c>
-    </row>
-    <row r="8" ht="42.75">
-      <c r="A8" s="1" t="s">
-        <v>619</v>
-      </c>
-      <c r="B8" s="1">
-        <v>3</v>
-      </c>
-      <c r="C8" s="1" t="s">
-        <v>620</v>
-      </c>
-      <c r="D8" s="1" t="s">
-        <v>621</v>
-      </c>
-      <c r="E8" s="1" t="s">
-        <v>622</v>
-      </c>
-      <c r="F8" s="1" t="s">
-        <v>623</v>
-      </c>
-      <c r="G8" s="1" t="s">
-        <v>624</v>
-      </c>
-      <c r="H8" s="1" t="s">
-        <v>625</v>
-      </c>
-    </row>
-    <row r="9" ht="42.75">
-      <c r="A9" s="1" t="s">
-        <v>626</v>
-      </c>
-      <c r="B9" s="1">
-        <v>3</v>
-      </c>
-      <c r="C9" s="1" t="s">
-        <v>627</v>
-      </c>
-      <c r="D9" s="1" t="s">
-        <v>628</v>
-      </c>
-      <c r="E9" s="1" t="s">
-        <v>629</v>
-      </c>
-      <c r="F9" s="1" t="s">
-        <v>630</v>
-      </c>
-      <c r="G9" s="1" t="s">
-        <v>631</v>
-      </c>
-      <c r="H9" s="1" t="s">
-        <v>632</v>
-      </c>
-      <c r="I9" s="1" t="s">
-        <v>633</v>
-      </c>
-    </row>
-    <row r="10" ht="57">
-      <c r="A10" s="1" t="s">
-        <v>634</v>
-      </c>
-      <c r="B10" s="1">
-        <v>4</v>
-      </c>
-      <c r="C10" s="1" t="s">
-        <v>635</v>
-      </c>
-      <c r="D10" s="1" t="s">
-        <v>636</v>
-      </c>
-      <c r="E10" s="1" t="s">
-        <v>637</v>
-      </c>
-      <c r="F10" s="1" t="s">
-        <v>638</v>
-      </c>
-      <c r="G10" s="1" t="s">
-        <v>639</v>
-      </c>
-      <c r="H10" s="1" t="s">
-        <v>640</v>
-      </c>
-    </row>
-    <row r="11" ht="57">
-      <c r="A11" s="1" t="s">
-        <v>641</v>
-      </c>
-      <c r="B11" s="1">
-        <v>4</v>
-      </c>
-      <c r="C11" s="1" t="s">
-        <v>642</v>
-      </c>
-      <c r="D11" s="1" t="s">
-        <v>643</v>
-      </c>
-      <c r="E11" s="1" t="s">
-        <v>644</v>
-      </c>
-      <c r="F11" s="1" t="s">
-        <v>645</v>
-      </c>
-      <c r="G11" s="1" t="s">
-        <v>646</v>
-      </c>
-      <c r="H11" s="1" t="s">
-        <v>647</v>
-      </c>
-      <c r="I11" s="1" t="s">
-        <v>648</v>
-      </c>
-    </row>
-  </sheetData>
-  <printOptions headings="0" gridLines="0"/>
-  <pageMargins left="0.70078740157480324" right="0.70078740157480324" top="0.75196850393700787" bottom="0.75196850393700787" header="0.29999999999999999" footer="0.29999999999999999"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" cellComments="none" useFirstPageNumber="0" errors="displayed" horizontalDpi="600" verticalDpi="600" copies="1"/>
-  <headerFooter/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac">
-  <sheetFormatPr baseColWidth="9" defaultRowHeight="14.25"/>
-  <cols>
-    <col min="1" max="8" style="1" width="10.28125"/>
-    <col customWidth="1" min="9" max="9" style="1" width="13.7109375"/>
-    <col min="10" max="16384" style="1" width="10.28125"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="28.5">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="2" ht="57">
-      <c r="A2" s="1" t="s">
-        <v>649</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>650</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>651</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>652</v>
-      </c>
-      <c r="E2" s="1" t="s">
-        <v>653</v>
-      </c>
-      <c r="F2" s="1" t="s">
-        <v>654</v>
-      </c>
-      <c r="G2" s="1" t="s">
-        <v>655</v>
-      </c>
-      <c r="H2" s="1" t="s">
-        <v>656</v>
-      </c>
-      <c r="I2" s="2" t="s">
-        <v>657</v>
-      </c>
-    </row>
-    <row r="3" ht="57">
-      <c r="A3" s="1" t="s">
-        <v>658</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>650</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>659</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>660</v>
-      </c>
-      <c r="E3" s="1" t="s">
-        <v>661</v>
-      </c>
-      <c r="F3" s="1" t="s">
-        <v>662</v>
-      </c>
-      <c r="G3" s="1" t="s">
-        <v>663</v>
-      </c>
-      <c r="H3" s="1" t="s">
-        <v>664</v>
-      </c>
-    </row>
-    <row r="4" ht="57">
-      <c r="A4" s="1" t="s">
-        <v>665</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>650</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>666</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>667</v>
-      </c>
-      <c r="E4" s="1" t="s">
-        <v>668</v>
-      </c>
-      <c r="F4" s="1" t="s">
-        <v>669</v>
-      </c>
-      <c r="G4" s="1" t="s">
-        <v>670</v>
-      </c>
-      <c r="H4" s="1" t="s">
-        <v>671</v>
-      </c>
-    </row>
-    <row r="5" ht="57">
-      <c r="A5" s="1" t="s">
-        <v>672</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>650</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>627</v>
-      </c>
-      <c r="D5" s="1" t="s">
-        <v>673</v>
-      </c>
-      <c r="E5" s="1" t="s">
-        <v>674</v>
-      </c>
-      <c r="F5" s="1" t="s">
-        <v>675</v>
-      </c>
-      <c r="G5" s="1" t="s">
-        <v>676</v>
-      </c>
-      <c r="H5" s="1" t="s">
-        <v>677</v>
-      </c>
-    </row>
-    <row r="6" ht="42.75">
-      <c r="A6" s="1" t="s">
-        <v>678</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>650</v>
-      </c>
-      <c r="C6" s="1" t="s">
-        <v>454</v>
-      </c>
-      <c r="D6" s="1" t="s">
-        <v>679</v>
-      </c>
-      <c r="E6" s="1" t="s">
-        <v>680</v>
-      </c>
-      <c r="F6" s="1" t="s">
-        <v>681</v>
-      </c>
-      <c r="G6" s="1" t="s">
-        <v>682</v>
-      </c>
-      <c r="H6" s="1" t="s">
-        <v>683</v>
-      </c>
-      <c r="I6" s="1" t="s">
-        <v>684</v>
-      </c>
-    </row>
-    <row r="7" ht="57">
-      <c r="A7" s="1" t="s">
-        <v>685</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>650</v>
-      </c>
-      <c r="C7" s="1" t="s">
-        <v>686</v>
-      </c>
-      <c r="D7" s="1" t="s">
-        <v>687</v>
-      </c>
-      <c r="E7" s="1" t="s">
-        <v>688</v>
-      </c>
-      <c r="F7" s="1" t="s">
-        <v>689</v>
-      </c>
-      <c r="G7" s="1" t="s">
-        <v>690</v>
-      </c>
-      <c r="H7" s="1" t="s">
-        <v>691</v>
-      </c>
-    </row>
-    <row r="8" ht="42.75">
-      <c r="A8" s="1" t="s">
-        <v>692</v>
-      </c>
-      <c r="B8" s="1" t="s">
-        <v>693</v>
-      </c>
-      <c r="C8" s="1" t="s">
-        <v>627</v>
-      </c>
-      <c r="D8" s="1" t="s">
-        <v>694</v>
-      </c>
-      <c r="E8" s="1" t="s">
-        <v>695</v>
-      </c>
-      <c r="F8" s="1" t="s">
-        <v>696</v>
-      </c>
-      <c r="G8" s="1" t="s">
-        <v>697</v>
-      </c>
-      <c r="H8" s="1" t="s">
-        <v>698</v>
-      </c>
-    </row>
-    <row r="9" ht="57">
-      <c r="A9" s="1" t="s">
-        <v>699</v>
-      </c>
-      <c r="B9" s="1" t="s">
-        <v>693</v>
-      </c>
-      <c r="C9" s="1" t="s">
-        <v>700</v>
-      </c>
-      <c r="D9" s="1" t="s">
-        <v>701</v>
-      </c>
-      <c r="E9" s="1" t="s">
-        <v>702</v>
-      </c>
-      <c r="F9" s="1" t="s">
-        <v>703</v>
-      </c>
-      <c r="G9" s="1" t="s">
-        <v>704</v>
-      </c>
-      <c r="H9" s="1" t="s">
-        <v>705</v>
-      </c>
-    </row>
-    <row r="10" ht="42.75">
-      <c r="A10" s="1" t="s">
-        <v>706</v>
-      </c>
-      <c r="B10" s="1" t="s">
-        <v>693</v>
-      </c>
-      <c r="C10" s="1" t="s">
-        <v>707</v>
-      </c>
-      <c r="D10" s="1" t="s">
-        <v>708</v>
-      </c>
-      <c r="E10" s="1" t="s">
-        <v>709</v>
-      </c>
-      <c r="F10" s="1" t="s">
-        <v>710</v>
-      </c>
-      <c r="G10" s="1" t="s">
-        <v>711</v>
-      </c>
-      <c r="H10" s="1" t="s">
-        <v>712</v>
-      </c>
-    </row>
-    <row r="11" ht="57">
-      <c r="A11" s="1" t="s">
-        <v>713</v>
-      </c>
-      <c r="B11" s="1" t="s">
-        <v>693</v>
-      </c>
-      <c r="C11" s="1" t="s">
-        <v>714</v>
-      </c>
-      <c r="D11" s="1" t="s">
-        <v>715</v>
-      </c>
-      <c r="E11" s="1" t="s">
-        <v>716</v>
-      </c>
-      <c r="F11" s="1" t="s">
-        <v>717</v>
-      </c>
-      <c r="G11" s="1" t="s">
-        <v>718</v>
-      </c>
-      <c r="H11" s="1" t="s">
-        <v>719</v>
-      </c>
-    </row>
-    <row r="12" ht="57">
-      <c r="A12" s="1" t="s">
-        <v>720</v>
-      </c>
-      <c r="B12" s="1" t="s">
-        <v>693</v>
-      </c>
-      <c r="C12" s="1" t="s">
-        <v>721</v>
-      </c>
-      <c r="D12" s="1" t="s">
-        <v>722</v>
-      </c>
-      <c r="E12" s="1" t="s">
-        <v>723</v>
-      </c>
-      <c r="F12" s="1" t="s">
-        <v>724</v>
-      </c>
-      <c r="G12" s="1" t="s">
-        <v>725</v>
-      </c>
-      <c r="H12" s="1" t="s">
-        <v>726</v>
-      </c>
-    </row>
-    <row r="13" ht="57">
-      <c r="A13" s="1" t="s">
-        <v>727</v>
-      </c>
-      <c r="B13" s="1" t="s">
-        <v>693</v>
-      </c>
-      <c r="C13" s="1" t="s">
-        <v>728</v>
-      </c>
-      <c r="D13" s="1" t="s">
-        <v>729</v>
-      </c>
-      <c r="E13" s="1" t="s">
-        <v>730</v>
-      </c>
-      <c r="F13" s="1" t="s">
-        <v>731</v>
-      </c>
-      <c r="G13" s="1" t="s">
-        <v>732</v>
-      </c>
-      <c r="H13" s="1" t="s">
-        <v>572</v>
-      </c>
-    </row>
-    <row r="14" ht="60">
-      <c r="A14" s="1" t="s">
-        <v>733</v>
-      </c>
-      <c r="B14" s="1" t="s">
-        <v>734</v>
-      </c>
-      <c r="C14" s="1" t="s">
-        <v>735</v>
-      </c>
-      <c r="D14" s="1" t="s">
-        <v>736</v>
-      </c>
-      <c r="E14" s="1" t="s">
-        <v>737</v>
-      </c>
-      <c r="F14" s="1" t="s">
-        <v>738</v>
-      </c>
-      <c r="G14" s="1" t="s">
-        <v>739</v>
-      </c>
-      <c r="H14" s="1" t="s">
-        <v>740</v>
-      </c>
-      <c r="I14" s="9" t="s">
-        <v>741</v>
-      </c>
-    </row>
-    <row r="15" ht="60">
-      <c r="A15" s="1" t="s">
-        <v>742</v>
-      </c>
-      <c r="B15" s="1" t="s">
-        <v>734</v>
-      </c>
-      <c r="C15" s="1" t="s">
-        <v>743</v>
-      </c>
-      <c r="D15" s="1" t="s">
-        <v>744</v>
-      </c>
-      <c r="E15" s="1" t="s">
-        <v>745</v>
-      </c>
-      <c r="F15" s="1" t="s">
-        <v>746</v>
-      </c>
-      <c r="G15" s="1" t="s">
-        <v>747</v>
-      </c>
-      <c r="H15" s="1" t="s">
-        <v>748</v>
-      </c>
-      <c r="I15" s="9" t="s">
-        <v>741</v>
-      </c>
-    </row>
-    <row r="16" ht="60">
-      <c r="A16" s="1" t="s">
-        <v>749</v>
-      </c>
-      <c r="B16" s="1" t="s">
-        <v>734</v>
-      </c>
-      <c r="C16" s="1" t="s">
-        <v>750</v>
-      </c>
-      <c r="D16" s="1" t="s">
-        <v>751</v>
-      </c>
-      <c r="E16" s="1" t="s">
-        <v>752</v>
-      </c>
-      <c r="F16" s="1" t="s">
-        <v>753</v>
-      </c>
-      <c r="G16" s="1" t="s">
-        <v>754</v>
-      </c>
-      <c r="H16" s="1" t="s">
-        <v>755</v>
-      </c>
-      <c r="I16" s="9" t="s">
-        <v>741</v>
-      </c>
-    </row>
-    <row r="17" ht="60">
-      <c r="A17" s="1" t="s">
-        <v>756</v>
-      </c>
-      <c r="B17" s="1" t="s">
-        <v>734</v>
-      </c>
-      <c r="C17" s="1" t="s">
-        <v>757</v>
-      </c>
-      <c r="D17" s="1" t="s">
-        <v>758</v>
-      </c>
-      <c r="E17" s="1" t="s">
-        <v>759</v>
-      </c>
-      <c r="F17" s="1" t="s">
-        <v>760</v>
-      </c>
-      <c r="G17" s="1" t="s">
-        <v>761</v>
-      </c>
-      <c r="H17" s="1" t="s">
-        <v>762</v>
-      </c>
-      <c r="I17" s="9" t="s">
-        <v>741</v>
-      </c>
-    </row>
-    <row r="18" ht="71.25">
-      <c r="A18" s="1" t="s">
-        <v>763</v>
-      </c>
-      <c r="B18" s="1" t="s">
-        <v>734</v>
-      </c>
-      <c r="C18" s="1" t="s">
-        <v>764</v>
-      </c>
-      <c r="D18" s="1" t="s">
-        <v>765</v>
-      </c>
-      <c r="E18" s="1" t="s">
-        <v>766</v>
-      </c>
-      <c r="F18" s="1" t="s">
-        <v>767</v>
-      </c>
-      <c r="G18" s="1" t="s">
-        <v>768</v>
-      </c>
-      <c r="H18" s="1" t="s">
-        <v>769</v>
-      </c>
-    </row>
-    <row r="19" ht="71.25">
-      <c r="A19" s="1" t="s">
-        <v>770</v>
-      </c>
-      <c r="B19" s="1" t="s">
-        <v>734</v>
-      </c>
-      <c r="C19" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="D19" s="1" t="s">
-        <v>771</v>
-      </c>
-      <c r="E19" s="1" t="s">
-        <v>772</v>
-      </c>
-      <c r="F19" s="1" t="s">
-        <v>773</v>
-      </c>
-      <c r="G19" s="1" t="s">
-        <v>774</v>
-      </c>
-      <c r="H19" s="1" t="s">
-        <v>775</v>
-      </c>
-    </row>
-    <row r="20" ht="60">
-      <c r="A20" s="1" t="s">
-        <v>776</v>
-      </c>
-      <c r="B20" s="1" t="s">
-        <v>734</v>
-      </c>
-      <c r="C20" s="1" t="s">
-        <v>777</v>
-      </c>
-      <c r="D20" s="1" t="s">
-        <v>778</v>
-      </c>
-      <c r="E20" s="1" t="s">
-        <v>779</v>
-      </c>
-      <c r="F20" s="1" t="s">
-        <v>780</v>
-      </c>
-      <c r="G20" s="1" t="s">
-        <v>781</v>
-      </c>
-      <c r="H20" s="1" t="s">
-        <v>782</v>
-      </c>
-      <c r="I20" s="9" t="s">
-        <v>741</v>
-      </c>
-    </row>
-    <row r="21" ht="60">
-      <c r="A21" s="1" t="s">
-        <v>783</v>
-      </c>
-      <c r="B21" s="1" t="s">
-        <v>734</v>
-      </c>
-      <c r="C21" s="1" t="s">
-        <v>784</v>
-      </c>
-      <c r="D21" s="1" t="s">
-        <v>785</v>
-      </c>
-      <c r="E21" s="1" t="s">
-        <v>786</v>
-      </c>
-      <c r="F21" s="1" t="s">
-        <v>787</v>
-      </c>
-      <c r="G21" s="1" t="s">
-        <v>788</v>
-      </c>
-      <c r="H21" s="1" t="s">
-        <v>789</v>
-      </c>
-      <c r="I21" s="9" t="s">
-        <v>741</v>
-      </c>
-    </row>
-    <row r="22" ht="57">
-      <c r="A22" s="1" t="s">
-        <v>790</v>
-      </c>
-      <c r="B22" s="1" t="s">
-        <v>461</v>
-      </c>
-      <c r="C22" s="1" t="s">
-        <v>791</v>
-      </c>
-      <c r="D22" s="1" t="s">
-        <v>792</v>
-      </c>
-      <c r="E22" s="1" t="s">
-        <v>793</v>
-      </c>
-      <c r="F22" s="1" t="s">
-        <v>794</v>
-      </c>
-      <c r="G22" s="1" t="s">
-        <v>795</v>
-      </c>
-      <c r="H22" s="1" t="s">
-        <v>796</v>
-      </c>
-      <c r="I22" s="1" t="s">
-        <v>797</v>
-      </c>
-    </row>
-    <row r="23" ht="42.75">
-      <c r="A23" s="1" t="s">
-        <v>798</v>
-      </c>
-      <c r="B23" s="1" t="s">
-        <v>461</v>
-      </c>
-      <c r="C23" s="1" t="s">
-        <v>799</v>
-      </c>
-      <c r="D23" s="1" t="s">
-        <v>800</v>
-      </c>
-      <c r="E23" s="1" t="s">
-        <v>801</v>
-      </c>
-      <c r="F23" s="1" t="s">
-        <v>802</v>
-      </c>
-      <c r="G23" s="1" t="s">
-        <v>803</v>
-      </c>
-      <c r="H23" s="1" t="s">
-        <v>804</v>
-      </c>
-    </row>
-    <row r="24" ht="57">
-      <c r="A24" s="1" t="s">
-        <v>805</v>
-      </c>
-      <c r="B24" s="1" t="s">
-        <v>461</v>
-      </c>
-      <c r="C24" s="1" t="s">
-        <v>806</v>
-      </c>
-      <c r="D24" s="1" t="s">
-        <v>807</v>
-      </c>
-      <c r="E24" s="1" t="s">
-        <v>808</v>
-      </c>
-      <c r="F24" s="1" t="s">
-        <v>809</v>
-      </c>
-      <c r="G24" s="1" t="s">
-        <v>810</v>
-      </c>
-      <c r="H24" s="1" t="s">
-        <v>811</v>
-      </c>
-      <c r="I24" s="1" t="s">
-        <v>812</v>
-      </c>
-    </row>
-    <row r="25" ht="57">
-      <c r="A25" s="1" t="s">
-        <v>813</v>
-      </c>
-      <c r="B25" s="1" t="s">
-        <v>461</v>
-      </c>
-      <c r="C25" s="1" t="s">
-        <v>814</v>
-      </c>
-      <c r="D25" s="1" t="s">
-        <v>815</v>
-      </c>
-      <c r="E25" s="1" t="s">
-        <v>816</v>
-      </c>
-      <c r="F25" s="1" t="s">
-        <v>817</v>
-      </c>
-      <c r="G25" s="1" t="s">
-        <v>818</v>
-      </c>
-      <c r="H25" s="1" t="s">
-        <v>819</v>
-      </c>
-    </row>
-    <row r="26" ht="57">
-      <c r="A26" s="1" t="s">
-        <v>820</v>
-      </c>
-      <c r="B26" s="1" t="s">
-        <v>461</v>
-      </c>
-      <c r="C26" s="1" t="s">
-        <v>821</v>
-      </c>
-      <c r="D26" s="1" t="s">
-        <v>822</v>
-      </c>
-      <c r="E26" s="1" t="s">
-        <v>823</v>
-      </c>
-      <c r="F26" s="1" t="s">
-        <v>824</v>
-      </c>
-      <c r="G26" s="1" t="s">
-        <v>825</v>
-      </c>
-      <c r="H26" s="1" t="s">
-        <v>826</v>
       </c>
     </row>
   </sheetData>
@@ -6101,554 +4053,566 @@
     </row>
     <row r="2" ht="128.25">
       <c r="A2" s="1" t="s">
-        <v>8</v>
+        <v>139</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>9</v>
+        <v>140</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>10</v>
+        <v>141</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>11</v>
+        <v>142</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>12</v>
+        <v>143</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>13</v>
+        <v>144</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>14</v>
+        <v>145</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>15</v>
+        <v>146</v>
       </c>
     </row>
     <row r="3" ht="99.75">
       <c r="A3" s="1" t="s">
-        <v>16</v>
+        <v>147</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>9</v>
+        <v>140</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>10</v>
+        <v>141</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>17</v>
+        <v>148</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>18</v>
+        <v>149</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>19</v>
+        <v>150</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>20</v>
+        <v>151</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>21</v>
+        <v>152</v>
       </c>
     </row>
     <row r="4" ht="128.25">
       <c r="A4" s="1" t="s">
-        <v>22</v>
+        <v>153</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>9</v>
+        <v>140</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>10</v>
+        <v>141</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>23</v>
+        <v>154</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>24</v>
+        <v>155</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>25</v>
+        <v>156</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>26</v>
+        <v>157</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>27</v>
+        <v>158</v>
       </c>
     </row>
     <row r="5" ht="142.5">
       <c r="A5" s="1" t="s">
-        <v>28</v>
+        <v>159</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>9</v>
+        <v>140</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>29</v>
+        <v>160</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>30</v>
+        <v>161</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>31</v>
+        <v>162</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>32</v>
+        <v>163</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>33</v>
+        <v>164</v>
       </c>
       <c r="H5" s="1" t="s">
-        <v>34</v>
+        <v>165</v>
       </c>
     </row>
     <row r="6" ht="142.5">
       <c r="A6" s="1" t="s">
-        <v>35</v>
+        <v>166</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>9</v>
+        <v>140</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>29</v>
+        <v>160</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>36</v>
+        <v>167</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>37</v>
+        <v>168</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>38</v>
+        <v>169</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>39</v>
+        <v>170</v>
       </c>
       <c r="H6" s="1" t="s">
-        <v>40</v>
+        <v>171</v>
       </c>
     </row>
     <row r="7" ht="128.25">
       <c r="A7" s="1" t="s">
-        <v>41</v>
+        <v>172</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>9</v>
+        <v>140</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>29</v>
+        <v>160</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>42</v>
+        <v>173</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>43</v>
+        <v>174</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>44</v>
+        <v>175</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>45</v>
+        <v>176</v>
       </c>
       <c r="H7" s="1" t="s">
-        <v>46</v>
+        <v>177</v>
       </c>
       <c r="I7" s="1" t="s">
-        <v>142</v>
+        <v>178</v>
       </c>
     </row>
     <row r="8" ht="114">
       <c r="A8" s="1" t="s">
-        <v>48</v>
+        <v>179</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>9</v>
+        <v>140</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>49</v>
+        <v>180</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>50</v>
+        <v>181</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>51</v>
+        <v>182</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>52</v>
+        <v>183</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>53</v>
+        <v>184</v>
       </c>
       <c r="H8" s="1" t="s">
-        <v>54</v>
+        <v>185</v>
       </c>
     </row>
     <row r="9" ht="114">
       <c r="A9" s="1" t="s">
-        <v>55</v>
+        <v>186</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>9</v>
+        <v>140</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>49</v>
+        <v>180</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>56</v>
+        <v>187</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>57</v>
+        <v>188</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>58</v>
+        <v>189</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>59</v>
+        <v>190</v>
       </c>
       <c r="H9" s="1" t="s">
-        <v>60</v>
+        <v>191</v>
+      </c>
+      <c r="I9" s="1" t="s">
+        <v>192</v>
+      </c>
+      <c r="J9" s="1" t="s">
+        <v>193</v>
       </c>
     </row>
     <row r="10" ht="114">
       <c r="A10" s="1" t="s">
-        <v>61</v>
+        <v>194</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>9</v>
+        <v>140</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>62</v>
+        <v>195</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>63</v>
+        <v>196</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>64</v>
+        <v>197</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>65</v>
+        <v>198</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>66</v>
+        <v>199</v>
       </c>
       <c r="H10" s="1" t="s">
-        <v>67</v>
+        <v>200</v>
       </c>
       <c r="I10" s="1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="11" ht="114">
       <c r="A11" s="1" t="s">
-        <v>68</v>
+        <v>201</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>9</v>
+        <v>140</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>62</v>
+        <v>195</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>69</v>
+        <v>202</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>70</v>
+        <v>203</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>71</v>
+        <v>204</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>72</v>
+        <v>205</v>
       </c>
       <c r="H11" s="1" t="s">
-        <v>73</v>
+        <v>206</v>
       </c>
     </row>
     <row r="12" ht="114">
       <c r="A12" s="1" t="s">
-        <v>74</v>
+        <v>207</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>9</v>
+        <v>140</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>75</v>
+        <v>208</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>76</v>
+        <v>209</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>77</v>
+        <v>210</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>78</v>
+        <v>211</v>
       </c>
       <c r="G12" s="1" t="s">
-        <v>79</v>
+        <v>212</v>
       </c>
       <c r="H12" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="I12" s="2" t="s">
-        <v>143</v>
+        <v>213</v>
+      </c>
+      <c r="I12" s="1" t="s">
+        <v>214</v>
+      </c>
+      <c r="J12" s="1" t="s">
+        <v>215</v>
       </c>
     </row>
     <row r="13" ht="128.25">
       <c r="A13" s="1" t="s">
-        <v>81</v>
+        <v>216</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>9</v>
+        <v>140</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>75</v>
+        <v>208</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>82</v>
+        <v>217</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>83</v>
+        <v>218</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>84</v>
+        <v>219</v>
       </c>
       <c r="G13" s="1" t="s">
-        <v>85</v>
+        <v>220</v>
       </c>
       <c r="H13" s="1" t="s">
-        <v>86</v>
-      </c>
-      <c r="I13" s="2" t="s">
-        <v>143</v>
+        <v>221</v>
+      </c>
+      <c r="I13" s="1" t="s">
+        <v>214</v>
+      </c>
+      <c r="J13" s="1" t="s">
+        <v>222</v>
       </c>
     </row>
     <row r="14" ht="99.75">
       <c r="A14" s="1" t="s">
-        <v>87</v>
+        <v>223</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>9</v>
+        <v>140</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>88</v>
+        <v>224</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>89</v>
+        <v>225</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>90</v>
+        <v>226</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>91</v>
+        <v>227</v>
       </c>
       <c r="G14" s="1" t="s">
-        <v>92</v>
+        <v>228</v>
       </c>
       <c r="H14" s="1" t="s">
-        <v>93</v>
+        <v>229</v>
       </c>
     </row>
     <row r="15" ht="71.25">
       <c r="A15" s="1" t="s">
-        <v>94</v>
+        <v>230</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>9</v>
+        <v>140</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>88</v>
+        <v>224</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>95</v>
+        <v>231</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>96</v>
+        <v>232</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>97</v>
+        <v>233</v>
       </c>
       <c r="G15" s="1" t="s">
-        <v>98</v>
+        <v>234</v>
       </c>
       <c r="H15" s="1" t="s">
-        <v>99</v>
+        <v>235</v>
       </c>
       <c r="I15" s="1" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="16" s="5" customFormat="1" ht="142.5">
-      <c r="A16" s="5" t="s">
-        <v>100</v>
-      </c>
-      <c r="B16" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C16" s="5" t="s">
-        <v>88</v>
-      </c>
-      <c r="D16" s="5" t="s">
-        <v>101</v>
-      </c>
-      <c r="E16" s="5" t="s">
-        <v>102</v>
-      </c>
-      <c r="F16" s="5" t="s">
-        <v>103</v>
-      </c>
-      <c r="G16" s="5" t="s">
-        <v>104</v>
-      </c>
-      <c r="H16" s="5" t="s">
-        <v>105</v>
+        <v>236</v>
+      </c>
+    </row>
+    <row r="16" s="2" customFormat="1" ht="142.5">
+      <c r="A16" s="2" t="s">
+        <v>237</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>224</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>238</v>
+      </c>
+      <c r="E16" s="2" t="s">
+        <v>239</v>
+      </c>
+      <c r="F16" s="2" t="s">
+        <v>240</v>
+      </c>
+      <c r="G16" s="2" t="s">
+        <v>241</v>
+      </c>
+      <c r="H16" s="2" t="s">
+        <v>242</v>
       </c>
     </row>
     <row r="17" ht="99.75">
       <c r="A17" s="1" t="s">
-        <v>106</v>
+        <v>243</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>9</v>
+        <v>140</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>88</v>
+        <v>224</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>107</v>
+        <v>244</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>108</v>
+        <v>245</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>109</v>
+        <v>246</v>
       </c>
       <c r="G17" s="1" t="s">
-        <v>110</v>
+        <v>247</v>
       </c>
       <c r="H17" s="1" t="s">
-        <v>111</v>
+        <v>248</v>
       </c>
     </row>
     <row r="18" ht="142.5">
       <c r="A18" s="1" t="s">
-        <v>112</v>
+        <v>249</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>9</v>
+        <v>140</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>113</v>
+        <v>250</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>114</v>
+        <v>251</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>115</v>
+        <v>252</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>116</v>
+        <v>253</v>
       </c>
       <c r="G18" s="1" t="s">
-        <v>117</v>
+        <v>254</v>
       </c>
       <c r="H18" s="1" t="s">
-        <v>118</v>
+        <v>255</v>
       </c>
     </row>
     <row r="19" ht="142.5">
       <c r="A19" s="1" t="s">
-        <v>119</v>
+        <v>256</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>9</v>
+        <v>140</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>113</v>
+        <v>250</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>120</v>
+        <v>257</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>121</v>
+        <v>258</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>122</v>
+        <v>259</v>
       </c>
       <c r="G19" s="1" t="s">
-        <v>123</v>
+        <v>260</v>
       </c>
       <c r="H19" s="1" t="s">
-        <v>124</v>
+        <v>261</v>
       </c>
     </row>
     <row r="20" ht="171">
       <c r="A20" s="1" t="s">
-        <v>125</v>
+        <v>262</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>9</v>
+        <v>140</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>127</v>
+        <v>263</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>128</v>
+        <v>264</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>129</v>
+        <v>265</v>
       </c>
       <c r="G20" s="1" t="s">
-        <v>130</v>
+        <v>266</v>
       </c>
       <c r="H20" s="1" t="s">
-        <v>131</v>
+        <v>267</v>
       </c>
     </row>
     <row r="21" ht="156.75">
       <c r="A21" s="1" t="s">
-        <v>132</v>
+        <v>268</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>9</v>
+        <v>140</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>133</v>
+        <v>269</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>134</v>
+        <v>270</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>135</v>
+        <v>271</v>
       </c>
       <c r="G21" s="1" t="s">
-        <v>136</v>
+        <v>272</v>
       </c>
       <c r="H21" s="1" t="s">
-        <v>137</v>
+        <v>273</v>
       </c>
     </row>
     <row r="22" ht="51">
       <c r="A22" s="3" t="s">
-        <v>138</v>
+        <v>274</v>
       </c>
       <c r="B22" s="4" t="s">
-        <v>9</v>
+        <v>140</v>
       </c>
       <c r="C22" s="4" t="s">
-        <v>139</v>
+        <v>275</v>
       </c>
       <c r="D22" s="4" t="s">
-        <v>140</v>
+        <v>276</v>
       </c>
       <c r="E22" s="4" t="s">
-        <v>141</v>
+        <v>277</v>
       </c>
     </row>
   </sheetData>
@@ -6670,509 +4634,438 @@
   <sheetData>
     <row r="1" ht="28.5">
       <c r="B1" s="1" t="s">
-        <v>145</v>
+        <v>278</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>146</v>
+        <v>279</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>147</v>
+        <v>280</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>148</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>149</v>
+        <v>281</v>
       </c>
     </row>
     <row r="2" ht="57">
       <c r="A2" s="1" t="s">
-        <v>150</v>
+        <v>282</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>151</v>
+        <v>283</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>152</v>
+        <v>284</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>153</v>
+        <v>285</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>154</v>
+        <v>286</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>155</v>
-      </c>
+        <v>287</v>
+      </c>
+      <c r="G2" s="1"/>
     </row>
     <row r="3" ht="57">
       <c r="A3" s="1" t="s">
-        <v>156</v>
+        <v>288</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>151</v>
+        <v>283</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>157</v>
+        <v>289</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>158</v>
+        <v>290</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>159</v>
-      </c>
-      <c r="F3" s="1" t="s">
-        <v>155</v>
+        <v>286</v>
       </c>
     </row>
     <row r="4" ht="57">
       <c r="A4" s="1" t="s">
-        <v>160</v>
+        <v>291</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>161</v>
+        <v>292</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>162</v>
+        <v>293</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>163</v>
-      </c>
-      <c r="E4" s="1" t="s">
-        <v>164</v>
-      </c>
-      <c r="F4" s="2" t="s">
-        <v>155</v>
-      </c>
-      <c r="G4" s="1" t="s">
-        <v>165</v>
+        <v>294</v>
+      </c>
+      <c r="E4" s="5" t="s">
+        <v>286</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>295</v>
       </c>
     </row>
     <row r="5" ht="57">
       <c r="A5" s="1" t="s">
-        <v>166</v>
+        <v>296</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>161</v>
+        <v>292</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>167</v>
+        <v>297</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>168</v>
+        <v>298</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>159</v>
-      </c>
-      <c r="F5" s="1" t="s">
-        <v>169</v>
+        <v>299</v>
       </c>
     </row>
     <row r="6" ht="71.25">
       <c r="A6" s="1" t="s">
-        <v>170</v>
+        <v>300</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>171</v>
+        <v>301</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>172</v>
+        <v>302</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>173</v>
-      </c>
-      <c r="E6" s="1" t="s">
-        <v>164</v>
-      </c>
-      <c r="F6" s="2" t="s">
-        <v>155</v>
-      </c>
-      <c r="G6" s="1" t="s">
-        <v>174</v>
+        <v>303</v>
+      </c>
+      <c r="E6" s="5" t="s">
+        <v>286</v>
+      </c>
+      <c r="F6" s="1" t="s">
+        <v>304</v>
       </c>
     </row>
     <row r="7" ht="57">
       <c r="A7" s="1" t="s">
-        <v>175</v>
+        <v>305</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>171</v>
+        <v>301</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>176</v>
+        <v>306</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>177</v>
+        <v>307</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>164</v>
-      </c>
-      <c r="F7" s="1" t="s">
-        <v>169</v>
+        <v>299</v>
       </c>
     </row>
     <row r="8" ht="57">
       <c r="A8" s="1" t="s">
-        <v>178</v>
+        <v>308</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>179</v>
+        <v>309</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>180</v>
+        <v>310</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>181</v>
+        <v>311</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>159</v>
-      </c>
-      <c r="F8" s="1" t="s">
-        <v>155</v>
+        <v>286</v>
       </c>
     </row>
     <row r="9" ht="42.75">
       <c r="A9" s="1" t="s">
-        <v>182</v>
+        <v>312</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>179</v>
+        <v>309</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>183</v>
+        <v>313</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>184</v>
+        <v>314</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>159</v>
-      </c>
-      <c r="F9" s="1" t="s">
-        <v>169</v>
+        <v>299</v>
       </c>
     </row>
     <row r="10" ht="57">
       <c r="A10" s="1" t="s">
-        <v>185</v>
+        <v>315</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>186</v>
+        <v>316</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>187</v>
+        <v>317</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>188</v>
+        <v>318</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>164</v>
-      </c>
-      <c r="F10" s="1" t="s">
-        <v>169</v>
+        <v>299</v>
       </c>
     </row>
     <row r="11" ht="57">
       <c r="A11" s="1" t="s">
-        <v>189</v>
+        <v>319</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>186</v>
+        <v>316</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>190</v>
+        <v>320</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>191</v>
+        <v>321</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>164</v>
-      </c>
-      <c r="F11" s="1" t="s">
-        <v>192</v>
+        <v>322</v>
       </c>
     </row>
     <row r="12" ht="57">
       <c r="A12" s="1" t="s">
-        <v>193</v>
+        <v>323</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>194</v>
+        <v>324</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>195</v>
+        <v>325</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>196</v>
+        <v>326</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>159</v>
-      </c>
-      <c r="F12" s="1" t="s">
-        <v>197</v>
+        <v>327</v>
       </c>
     </row>
     <row r="13" ht="57">
       <c r="A13" s="1" t="s">
-        <v>198</v>
+        <v>328</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>194</v>
+        <v>324</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>199</v>
+        <v>329</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>200</v>
+        <v>330</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>159</v>
-      </c>
-      <c r="F13" s="1" t="s">
-        <v>197</v>
+        <v>327</v>
       </c>
     </row>
     <row r="14" ht="57">
       <c r="A14" s="1" t="s">
-        <v>201</v>
+        <v>331</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>202</v>
+        <v>332</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>203</v>
+        <v>333</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>204</v>
+        <v>334</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>159</v>
-      </c>
-      <c r="F14" s="1" t="s">
-        <v>169</v>
+        <v>299</v>
       </c>
     </row>
     <row r="15" ht="42.75">
       <c r="A15" s="1" t="s">
-        <v>205</v>
+        <v>335</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>202</v>
+        <v>332</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>206</v>
+        <v>336</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>207</v>
+        <v>337</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>159</v>
-      </c>
-      <c r="F15" s="1" t="s">
-        <v>169</v>
+        <v>299</v>
       </c>
     </row>
     <row r="16" ht="57">
       <c r="A16" s="1" t="s">
-        <v>208</v>
+        <v>338</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>209</v>
+        <v>339</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>210</v>
+        <v>340</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>211</v>
+        <v>341</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>164</v>
-      </c>
-      <c r="F16" s="1" t="s">
-        <v>169</v>
+        <v>299</v>
       </c>
     </row>
     <row r="17" ht="57">
       <c r="A17" s="1" t="s">
-        <v>212</v>
+        <v>342</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>209</v>
+        <v>339</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>213</v>
+        <v>343</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>214</v>
+        <v>344</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>159</v>
-      </c>
-      <c r="F17" s="1" t="s">
-        <v>192</v>
+        <v>322</v>
       </c>
     </row>
     <row r="18" ht="71.25">
       <c r="A18" s="1" t="s">
-        <v>215</v>
+        <v>345</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>216</v>
+        <v>346</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>217</v>
+        <v>347</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>218</v>
-      </c>
-      <c r="E18" s="1" t="s">
-        <v>159</v>
-      </c>
-      <c r="F18" s="2" t="s">
-        <v>155</v>
-      </c>
-      <c r="G18" s="2"/>
+        <v>348</v>
+      </c>
+      <c r="E18" s="5" t="s">
+        <v>286</v>
+      </c>
+      <c r="F18" s="5"/>
     </row>
     <row r="19" ht="42.75">
       <c r="A19" s="1" t="s">
-        <v>219</v>
+        <v>349</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>216</v>
+        <v>346</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>220</v>
+        <v>350</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>221</v>
+        <v>351</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>164</v>
-      </c>
-      <c r="F19" s="1" t="s">
-        <v>169</v>
+        <v>299</v>
       </c>
     </row>
     <row r="20" ht="57">
       <c r="A20" s="1" t="s">
-        <v>222</v>
+        <v>352</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>223</v>
+        <v>353</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>224</v>
+        <v>354</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>225</v>
+        <v>355</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>159</v>
-      </c>
-      <c r="F20" s="1" t="s">
-        <v>169</v>
+        <v>299</v>
       </c>
     </row>
     <row r="21" ht="57">
       <c r="A21" s="1" t="s">
-        <v>226</v>
+        <v>356</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>227</v>
+        <v>357</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>228</v>
+        <v>358</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>229</v>
+        <v>359</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>159</v>
-      </c>
-      <c r="F21" s="1" t="s">
-        <v>192</v>
+        <v>322</v>
       </c>
     </row>
     <row r="22" ht="71.25">
       <c r="A22" s="1" t="s">
-        <v>230</v>
+        <v>360</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>231</v>
+        <v>361</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>232</v>
+        <v>362</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>233</v>
-      </c>
-      <c r="E22" s="1" t="s">
-        <v>164</v>
-      </c>
-      <c r="F22" s="2" t="s">
-        <v>234</v>
-      </c>
-      <c r="G22" s="1" t="s">
-        <v>235</v>
+        <v>363</v>
+      </c>
+      <c r="E22" s="5" t="s">
+        <v>364</v>
+      </c>
+      <c r="F22" s="1" t="s">
+        <v>365</v>
       </c>
     </row>
     <row r="23" ht="57">
       <c r="A23" s="1" t="s">
-        <v>236</v>
+        <v>366</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>231</v>
+        <v>361</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>237</v>
+        <v>367</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>238</v>
+        <v>368</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>159</v>
-      </c>
-      <c r="F23" s="1" t="s">
-        <v>169</v>
+        <v>299</v>
       </c>
     </row>
     <row r="24" ht="57">
       <c r="A24" s="1" t="s">
-        <v>239</v>
+        <v>369</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>240</v>
+        <v>370</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>241</v>
+        <v>371</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>242</v>
+        <v>372</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>159</v>
-      </c>
-      <c r="F24" s="1" t="s">
-        <v>169</v>
+        <v>299</v>
       </c>
     </row>
     <row r="25" ht="42.75">
       <c r="A25" s="1" t="s">
-        <v>243</v>
+        <v>373</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>240</v>
+        <v>370</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>244</v>
+        <v>374</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>245</v>
+        <v>375</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>164</v>
-      </c>
-      <c r="F25" s="1" t="s">
-        <v>192</v>
+        <v>322</v>
       </c>
     </row>
   </sheetData>
@@ -7185,89 +5078,591 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac">
-  <sheetPr>
-    <outlinePr applyStyles="0" summaryBelow="0" summaryRight="0" showOutlineSymbols="1"/>
-    <pageSetUpPr autoPageBreaks="1" fitToPage="0"/>
-  </sheetPr>
-  <sheetFormatPr defaultColWidth="12.630000000000001" defaultRowHeight="15.75" customHeight="1"/>
+  <sheetFormatPr baseColWidth="9" defaultRowHeight="14.25"/>
   <cols>
-    <col customWidth="1" min="1" max="1" width="7.140625"/>
-    <col customWidth="1" min="3" max="3" width="6.8799999999999999"/>
+    <col min="1" max="16384" style="1" width="10.28125"/>
   </cols>
   <sheetData>
-    <row r="1" ht="38.25">
-      <c r="A1" s="6" t="s">
-        <v>246</v>
-      </c>
-      <c r="B1" s="6" t="s">
-        <v>247</v>
-      </c>
-      <c r="C1" s="6" t="s">
-        <v>248</v>
-      </c>
-      <c r="D1" s="6" t="s">
-        <v>249</v>
-      </c>
-      <c r="E1" s="7" t="s">
-        <v>141</v>
-      </c>
-      <c r="F1" s="7"/>
-      <c r="G1" s="7"/>
-      <c r="H1" s="7"/>
-      <c r="I1" s="7"/>
-      <c r="J1" s="7"/>
-      <c r="K1" s="7"/>
-      <c r="L1" s="7"/>
-      <c r="M1" s="7"/>
-      <c r="N1" s="7"/>
-      <c r="O1" s="7"/>
-      <c r="P1" s="7"/>
-      <c r="Q1" s="7"/>
-      <c r="R1" s="7"/>
-      <c r="S1" s="7"/>
-      <c r="T1" s="7"/>
-      <c r="U1" s="7"/>
-      <c r="V1" s="7"/>
-      <c r="W1" s="7"/>
-      <c r="X1" s="7"/>
-      <c r="Y1" s="7"/>
-    </row>
-    <row r="2" ht="38.25">
-      <c r="A2" s="6" t="s">
-        <v>250</v>
-      </c>
-      <c r="B2" s="6" t="s">
-        <v>251</v>
-      </c>
-      <c r="C2" s="6" t="s">
-        <v>252</v>
-      </c>
-      <c r="D2" s="6" t="s">
-        <v>253</v>
-      </c>
-      <c r="E2" s="7" t="s">
-        <v>141</v>
-      </c>
-      <c r="F2" s="7"/>
-      <c r="G2" s="7"/>
-      <c r="H2" s="7"/>
-      <c r="I2" s="7"/>
-      <c r="J2" s="7"/>
-      <c r="K2" s="7"/>
-      <c r="L2" s="7"/>
-      <c r="M2" s="7"/>
-      <c r="N2" s="7"/>
-      <c r="O2" s="7"/>
-      <c r="P2" s="7"/>
-      <c r="Q2" s="7"/>
-      <c r="R2" s="7"/>
-      <c r="S2" s="7"/>
-      <c r="T2" s="7"/>
-      <c r="U2" s="7"/>
-      <c r="V2" s="7"/>
-      <c r="W2" s="7"/>
-      <c r="X2" s="7"/>
-      <c r="Y2" s="7"/>
+    <row r="1" ht="28.5">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2" ht="71.25">
+      <c r="A2" s="1" t="s">
+        <v>376</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>377</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>378</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>379</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>380</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>381</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>382</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>383</v>
+      </c>
+      <c r="I2" s="1" t="s">
+        <v>384</v>
+      </c>
+    </row>
+    <row r="3" ht="85.5">
+      <c r="A3" s="1" t="s">
+        <v>385</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>377</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>378</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>386</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>387</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>388</v>
+      </c>
+      <c r="G3" s="1" t="s">
+        <v>389</v>
+      </c>
+      <c r="H3" s="1" t="s">
+        <v>390</v>
+      </c>
+    </row>
+    <row r="4" ht="99.75">
+      <c r="A4" s="1" t="s">
+        <v>391</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>377</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>392</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>393</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>394</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>395</v>
+      </c>
+      <c r="G4" s="1" t="s">
+        <v>396</v>
+      </c>
+      <c r="H4" s="1" t="s">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="5" ht="99.75">
+      <c r="A5" s="1" t="s">
+        <v>398</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>377</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>392</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>399</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>400</v>
+      </c>
+      <c r="F5" s="1" t="s">
+        <v>401</v>
+      </c>
+      <c r="G5" s="1" t="s">
+        <v>402</v>
+      </c>
+      <c r="H5" s="1" t="s">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="6" ht="85.5">
+      <c r="A6" s="1" t="s">
+        <v>404</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>377</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>195</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>405</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>406</v>
+      </c>
+      <c r="F6" s="1" t="s">
+        <v>407</v>
+      </c>
+      <c r="G6" s="1" t="s">
+        <v>408</v>
+      </c>
+      <c r="H6" s="1" t="s">
+        <v>409</v>
+      </c>
+    </row>
+    <row r="7" ht="71.25">
+      <c r="A7" s="1" t="s">
+        <v>410</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>377</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>195</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>411</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>412</v>
+      </c>
+      <c r="F7" s="1" t="s">
+        <v>413</v>
+      </c>
+      <c r="G7" s="1" t="s">
+        <v>414</v>
+      </c>
+      <c r="H7" s="1" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="8" ht="71.25">
+      <c r="A8" s="1" t="s">
+        <v>416</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>377</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>417</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>418</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>419</v>
+      </c>
+      <c r="F8" s="1" t="s">
+        <v>420</v>
+      </c>
+      <c r="G8" s="1" t="s">
+        <v>421</v>
+      </c>
+      <c r="H8" s="1" t="s">
+        <v>422</v>
+      </c>
+    </row>
+    <row r="9" ht="99.75">
+      <c r="A9" s="1" t="s">
+        <v>423</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>377</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>417</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>424</v>
+      </c>
+      <c r="E9" s="1" t="s">
+        <v>425</v>
+      </c>
+      <c r="F9" s="1" t="s">
+        <v>426</v>
+      </c>
+      <c r="G9" s="1" t="s">
+        <v>427</v>
+      </c>
+      <c r="H9" s="1" t="s">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="10" ht="99.75">
+      <c r="A10" s="1" t="s">
+        <v>429</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>377</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>430</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>431</v>
+      </c>
+      <c r="E10" s="1" t="s">
+        <v>432</v>
+      </c>
+      <c r="F10" s="1" t="s">
+        <v>433</v>
+      </c>
+      <c r="G10" s="1" t="s">
+        <v>434</v>
+      </c>
+      <c r="H10" s="1" t="s">
+        <v>435</v>
+      </c>
+    </row>
+    <row r="11" ht="85.5">
+      <c r="A11" s="1" t="s">
+        <v>436</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>377</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>430</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>437</v>
+      </c>
+      <c r="E11" s="1" t="s">
+        <v>438</v>
+      </c>
+      <c r="F11" s="1" t="s">
+        <v>439</v>
+      </c>
+      <c r="G11" s="1" t="s">
+        <v>440</v>
+      </c>
+      <c r="H11" s="1" t="s">
+        <v>441</v>
+      </c>
+    </row>
+    <row r="12" ht="85.5">
+      <c r="A12" s="1" t="s">
+        <v>442</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>377</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>443</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>444</v>
+      </c>
+      <c r="E12" s="1" t="s">
+        <v>445</v>
+      </c>
+      <c r="F12" s="1" t="s">
+        <v>446</v>
+      </c>
+      <c r="G12" s="1" t="s">
+        <v>447</v>
+      </c>
+      <c r="H12" s="1" t="s">
+        <v>448</v>
+      </c>
+    </row>
+    <row r="13" ht="71.25">
+      <c r="A13" s="1" t="s">
+        <v>449</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>377</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>443</v>
+      </c>
+      <c r="D13" s="1" t="s">
+        <v>450</v>
+      </c>
+      <c r="E13" s="1" t="s">
+        <v>451</v>
+      </c>
+      <c r="F13" s="1" t="s">
+        <v>452</v>
+      </c>
+      <c r="G13" s="1" t="s">
+        <v>453</v>
+      </c>
+      <c r="H13" s="1" t="s">
+        <v>454</v>
+      </c>
+    </row>
+    <row r="14" ht="71.25">
+      <c r="A14" s="1" t="s">
+        <v>455</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>377</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>456</v>
+      </c>
+      <c r="D14" s="1" t="s">
+        <v>457</v>
+      </c>
+      <c r="E14" s="1" t="s">
+        <v>458</v>
+      </c>
+      <c r="F14" s="1" t="s">
+        <v>459</v>
+      </c>
+      <c r="G14" s="1" t="s">
+        <v>460</v>
+      </c>
+      <c r="H14" s="1" t="s">
+        <v>461</v>
+      </c>
+    </row>
+    <row r="15" ht="71.25">
+      <c r="A15" s="1" t="s">
+        <v>462</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>377</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>456</v>
+      </c>
+      <c r="D15" s="1" t="s">
+        <v>463</v>
+      </c>
+      <c r="E15" s="1" t="s">
+        <v>464</v>
+      </c>
+      <c r="F15" s="1" t="s">
+        <v>465</v>
+      </c>
+      <c r="G15" s="1" t="s">
+        <v>466</v>
+      </c>
+      <c r="H15" s="1" t="s">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="16" ht="85.5">
+      <c r="A16" s="1" t="s">
+        <v>468</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>377</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>469</v>
+      </c>
+      <c r="D16" s="1" t="s">
+        <v>470</v>
+      </c>
+      <c r="E16" s="1" t="s">
+        <v>471</v>
+      </c>
+      <c r="F16" s="1" t="s">
+        <v>472</v>
+      </c>
+      <c r="G16" s="1" t="s">
+        <v>473</v>
+      </c>
+      <c r="H16" s="1" t="s">
+        <v>474</v>
+      </c>
+    </row>
+    <row r="17" ht="85.5">
+      <c r="A17" s="1" t="s">
+        <v>475</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>377</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>469</v>
+      </c>
+      <c r="D17" s="1" t="s">
+        <v>476</v>
+      </c>
+      <c r="E17" s="1" t="s">
+        <v>477</v>
+      </c>
+      <c r="F17" s="1" t="s">
+        <v>478</v>
+      </c>
+      <c r="G17" s="1" t="s">
+        <v>479</v>
+      </c>
+      <c r="H17" s="1" t="s">
+        <v>480</v>
+      </c>
+    </row>
+    <row r="18" ht="85.5">
+      <c r="A18" s="1" t="s">
+        <v>481</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>377</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>482</v>
+      </c>
+      <c r="D18" s="1" t="s">
+        <v>483</v>
+      </c>
+      <c r="E18" s="1" t="s">
+        <v>484</v>
+      </c>
+      <c r="F18" s="1" t="s">
+        <v>485</v>
+      </c>
+      <c r="G18" s="1" t="s">
+        <v>486</v>
+      </c>
+      <c r="H18" s="1" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="19" ht="99.75">
+      <c r="A19" s="1" t="s">
+        <v>488</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>377</v>
+      </c>
+      <c r="C19" s="1" t="s">
+        <v>482</v>
+      </c>
+      <c r="D19" s="1" t="s">
+        <v>489</v>
+      </c>
+      <c r="E19" s="1" t="s">
+        <v>490</v>
+      </c>
+      <c r="F19" s="1" t="s">
+        <v>491</v>
+      </c>
+      <c r="G19" s="1" t="s">
+        <v>492</v>
+      </c>
+      <c r="H19" s="1" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="20" ht="99.75">
+      <c r="A20" s="1" t="s">
+        <v>494</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>377</v>
+      </c>
+      <c r="C20" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="D20" s="1" t="s">
+        <v>495</v>
+      </c>
+      <c r="E20" s="1" t="s">
+        <v>496</v>
+      </c>
+      <c r="F20" s="1" t="s">
+        <v>497</v>
+      </c>
+      <c r="G20" s="1" t="s">
+        <v>498</v>
+      </c>
+      <c r="H20" s="1" t="s">
+        <v>499</v>
+      </c>
+    </row>
+    <row r="21" ht="114">
+      <c r="A21" s="1" t="s">
+        <v>500</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>377</v>
+      </c>
+      <c r="C21" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="D21" s="1" t="s">
+        <v>501</v>
+      </c>
+      <c r="E21" s="1" t="s">
+        <v>502</v>
+      </c>
+      <c r="F21" s="1" t="s">
+        <v>503</v>
+      </c>
+      <c r="G21" s="1" t="s">
+        <v>504</v>
+      </c>
+      <c r="H21" s="1" t="s">
+        <v>505</v>
+      </c>
+    </row>
+    <row r="22" ht="51">
+      <c r="A22" s="3" t="s">
+        <v>506</v>
+      </c>
+      <c r="B22" s="4" t="s">
+        <v>507</v>
+      </c>
+      <c r="C22" s="3" t="s">
+        <v>508</v>
+      </c>
+      <c r="D22" s="4" t="s">
+        <v>509</v>
+      </c>
+      <c r="E22" s="4" t="s">
+        <v>510</v>
+      </c>
+      <c r="F22" s="4" t="s">
+        <v>277</v>
+      </c>
+      <c r="G22" s="4" t="s">
+        <v>511</v>
+      </c>
+    </row>
+    <row r="23" ht="14.25">
+      <c r="A23" s="1"/>
+      <c r="B23" s="1"/>
+      <c r="C23" s="1"/>
+      <c r="D23" s="1"/>
+      <c r="E23" s="1"/>
+      <c r="F23" s="1"/>
+      <c r="G23" s="1"/>
     </row>
   </sheetData>
   <printOptions headings="0" gridLines="0"/>
@@ -7279,89 +5674,364 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac">
-  <sheetPr>
-    <outlinePr applyStyles="0" summaryBelow="0" summaryRight="0" showOutlineSymbols="1"/>
-    <pageSetUpPr autoPageBreaks="1" fitToPage="0"/>
-  </sheetPr>
-  <sheetFormatPr defaultColWidth="12.630000000000001" defaultRowHeight="15.75" customHeight="1"/>
+  <sheetFormatPr baseColWidth="9" defaultRowHeight="14.25"/>
   <cols>
-    <col customWidth="1" min="1" max="1" width="7.140625"/>
-    <col customWidth="1" min="3" max="3" width="6.8799999999999999"/>
+    <col min="1" max="7" style="1" width="10.28125"/>
+    <col customWidth="1" min="8" max="8" style="1" width="16.57421875"/>
+    <col customWidth="1" min="9" max="9" style="1" width="19.421875"/>
+    <col customWidth="1" min="10" max="10" style="1" width="15.57421875"/>
+    <col customWidth="1" min="11" max="11" style="1" width="13.8515625"/>
+    <col min="12" max="16384" style="1" width="10.28125"/>
   </cols>
   <sheetData>
-    <row r="1" ht="38.25">
-      <c r="A1" s="6" t="s">
-        <v>246</v>
-      </c>
-      <c r="B1" s="6" t="s">
-        <v>247</v>
-      </c>
-      <c r="C1" s="6" t="s">
-        <v>248</v>
-      </c>
-      <c r="D1" s="6" t="s">
-        <v>249</v>
-      </c>
-      <c r="E1" s="7" t="s">
-        <v>141</v>
-      </c>
-      <c r="F1" s="7"/>
-      <c r="G1" s="7"/>
-      <c r="H1" s="7"/>
-      <c r="I1" s="7"/>
-      <c r="J1" s="7"/>
-      <c r="K1" s="7"/>
-      <c r="L1" s="7"/>
-      <c r="M1" s="7"/>
-      <c r="N1" s="7"/>
-      <c r="O1" s="7"/>
-      <c r="P1" s="7"/>
-      <c r="Q1" s="7"/>
-      <c r="R1" s="7"/>
-      <c r="S1" s="7"/>
-      <c r="T1" s="7"/>
-      <c r="U1" s="7"/>
-      <c r="V1" s="7"/>
-      <c r="W1" s="7"/>
-      <c r="X1" s="7"/>
-      <c r="Y1" s="7"/>
-    </row>
-    <row r="2" ht="38.25">
-      <c r="A2" s="6" t="s">
+    <row r="1" ht="28.5">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2" ht="57">
+      <c r="A2" s="1" t="s">
+        <v>512</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>513</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>514</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>515</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>516</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>517</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>518</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>519</v>
+      </c>
+      <c r="I2" s="1" t="s">
+        <v>520</v>
+      </c>
+      <c r="J2" s="1"/>
+    </row>
+    <row r="3" ht="57">
+      <c r="A3" s="1" t="s">
+        <v>521</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>513</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>522</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>523</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>524</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>525</v>
+      </c>
+      <c r="G3" s="1" t="s">
+        <v>526</v>
+      </c>
+      <c r="H3" s="1" t="s">
+        <v>527</v>
+      </c>
+    </row>
+    <row r="4" ht="71.25">
+      <c r="A4" s="1" t="s">
+        <v>528</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>529</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>530</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>531</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>532</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>533</v>
+      </c>
+      <c r="G4" s="1" t="s">
+        <v>534</v>
+      </c>
+      <c r="H4" s="1" t="s">
+        <v>535</v>
+      </c>
+    </row>
+    <row r="5" ht="71.25">
+      <c r="A5" s="1" t="s">
+        <v>536</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>529</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>537</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>538</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>539</v>
+      </c>
+      <c r="F5" s="1" t="s">
+        <v>540</v>
+      </c>
+      <c r="G5" s="1" t="s">
+        <v>541</v>
+      </c>
+      <c r="H5" s="1" t="s">
+        <v>542</v>
+      </c>
+    </row>
+    <row r="6" ht="71.25">
+      <c r="A6" s="1" t="s">
+        <v>543</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>544</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>545</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>546</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>547</v>
+      </c>
+      <c r="F6" s="1" t="s">
+        <v>548</v>
+      </c>
+      <c r="G6" s="1" t="s">
+        <v>549</v>
+      </c>
+      <c r="H6" s="1" t="s">
+        <v>550</v>
+      </c>
+      <c r="I6" s="1" t="s">
+        <v>551</v>
+      </c>
+      <c r="J6" s="1" t="s">
+        <v>552</v>
+      </c>
+      <c r="K6" s="1"/>
+    </row>
+    <row r="7" ht="57">
+      <c r="A7" s="1" t="s">
+        <v>553</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>544</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>554</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>555</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>556</v>
+      </c>
+      <c r="F7" s="1" t="s">
+        <v>557</v>
+      </c>
+      <c r="G7" s="1" t="s">
+        <v>558</v>
+      </c>
+      <c r="H7" s="1" t="s">
+        <v>559</v>
+      </c>
+    </row>
+    <row r="8" ht="71.25">
+      <c r="A8" s="1" t="s">
+        <v>560</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>561</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>562</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>563</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>564</v>
+      </c>
+      <c r="F8" s="1" t="s">
+        <v>565</v>
+      </c>
+      <c r="G8" s="1" t="s">
+        <v>566</v>
+      </c>
+      <c r="H8" s="1" t="s">
+        <v>567</v>
+      </c>
+    </row>
+    <row r="9" ht="57">
+      <c r="A9" s="1" t="s">
+        <v>568</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>561</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>569</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>570</v>
+      </c>
+      <c r="E9" s="1" t="s">
+        <v>571</v>
+      </c>
+      <c r="F9" s="1" t="s">
+        <v>572</v>
+      </c>
+      <c r="G9" s="1" t="s">
+        <v>573</v>
+      </c>
+      <c r="H9" s="1" t="s">
+        <v>574</v>
+      </c>
+    </row>
+    <row r="10" ht="57">
+      <c r="A10" s="1" t="s">
+        <v>575</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>561</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>576</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>577</v>
+      </c>
+      <c r="E10" s="1" t="s">
+        <v>578</v>
+      </c>
+      <c r="F10" s="1" t="s">
+        <v>579</v>
+      </c>
+      <c r="G10" s="1" t="s">
+        <v>580</v>
+      </c>
+      <c r="H10" s="1" t="s">
+        <v>581</v>
+      </c>
+    </row>
+    <row r="11" ht="42.75">
+      <c r="A11" s="1" t="s">
+        <v>582</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>583</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>584</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>585</v>
+      </c>
+      <c r="E11" s="1" t="s">
+        <v>586</v>
+      </c>
+      <c r="F11" s="1" t="s">
+        <v>587</v>
+      </c>
+      <c r="G11" s="1" t="s">
+        <v>588</v>
+      </c>
+      <c r="H11" s="1" t="s">
+        <v>589</v>
+      </c>
+    </row>
+    <row r="12" ht="71.25">
+      <c r="A12" s="1" t="s">
+        <v>590</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>583</v>
+      </c>
+      <c r="C12" s="1" t="s">
         <v>250</v>
       </c>
-      <c r="B2" s="6" t="s">
-        <v>251</v>
-      </c>
-      <c r="C2" s="6" t="s">
-        <v>252</v>
-      </c>
-      <c r="D2" s="6" t="s">
-        <v>253</v>
-      </c>
-      <c r="E2" s="7" t="s">
-        <v>141</v>
-      </c>
-      <c r="F2" s="7"/>
-      <c r="G2" s="7"/>
-      <c r="H2" s="7"/>
-      <c r="I2" s="7"/>
-      <c r="J2" s="7"/>
-      <c r="K2" s="7"/>
-      <c r="L2" s="7"/>
-      <c r="M2" s="7"/>
-      <c r="N2" s="7"/>
-      <c r="O2" s="7"/>
-      <c r="P2" s="7"/>
-      <c r="Q2" s="7"/>
-      <c r="R2" s="7"/>
-      <c r="S2" s="7"/>
-      <c r="T2" s="7"/>
-      <c r="U2" s="7"/>
-      <c r="V2" s="7"/>
-      <c r="W2" s="7"/>
-      <c r="X2" s="7"/>
-      <c r="Y2" s="7"/>
+      <c r="D12" s="1" t="s">
+        <v>591</v>
+      </c>
+      <c r="E12" s="1" t="s">
+        <v>592</v>
+      </c>
+      <c r="F12" s="1" t="s">
+        <v>593</v>
+      </c>
+      <c r="G12" s="1" t="s">
+        <v>594</v>
+      </c>
+      <c r="H12" s="1" t="s">
+        <v>595</v>
+      </c>
+    </row>
+    <row r="13" ht="71.25">
+      <c r="A13" s="1" t="s">
+        <v>596</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>583</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>597</v>
+      </c>
+      <c r="D13" s="1" t="s">
+        <v>598</v>
+      </c>
+      <c r="E13" s="1" t="s">
+        <v>599</v>
+      </c>
+      <c r="F13" s="1" t="s">
+        <v>600</v>
+      </c>
+      <c r="G13" s="1" t="s">
+        <v>601</v>
+      </c>
+      <c r="H13" s="1" t="s">
+        <v>602</v>
+      </c>
     </row>
   </sheetData>
   <printOptions headings="0" gridLines="0"/>
@@ -7373,89 +6043,376 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac">
-  <sheetPr>
-    <outlinePr applyStyles="0" summaryBelow="0" summaryRight="0" showOutlineSymbols="1"/>
-    <pageSetUpPr autoPageBreaks="1" fitToPage="0"/>
-  </sheetPr>
-  <sheetFormatPr defaultColWidth="12.630000000000001" defaultRowHeight="15.75" customHeight="1"/>
+  <sheetFormatPr baseColWidth="9" defaultRowHeight="14.25"/>
   <cols>
-    <col customWidth="1" min="1" max="1" width="7.140625"/>
-    <col customWidth="1" min="3" max="3" width="6.8799999999999999"/>
+    <col min="1" max="4" style="1" width="10.28125"/>
+    <col customWidth="1" min="5" max="5" style="1" width="14.421875"/>
+    <col min="6" max="16384" style="1" width="10.28125"/>
   </cols>
   <sheetData>
-    <row r="1" ht="38.25">
-      <c r="A1" s="6" t="s">
-        <v>246</v>
-      </c>
-      <c r="B1" s="6" t="s">
-        <v>247</v>
-      </c>
-      <c r="C1" s="6" t="s">
-        <v>248</v>
-      </c>
-      <c r="D1" s="6" t="s">
-        <v>249</v>
-      </c>
-      <c r="E1" s="7" t="s">
-        <v>141</v>
-      </c>
-      <c r="F1" s="7"/>
-      <c r="G1" s="7"/>
-      <c r="H1" s="7"/>
-      <c r="I1" s="7"/>
-      <c r="J1" s="7"/>
-      <c r="K1" s="7"/>
-      <c r="L1" s="7"/>
-      <c r="M1" s="7"/>
-      <c r="N1" s="7"/>
-      <c r="O1" s="7"/>
-      <c r="P1" s="7"/>
-      <c r="Q1" s="7"/>
-      <c r="R1" s="7"/>
-      <c r="S1" s="7"/>
-      <c r="T1" s="7"/>
-      <c r="U1" s="7"/>
-      <c r="V1" s="7"/>
-      <c r="W1" s="7"/>
-      <c r="X1" s="7"/>
-      <c r="Y1" s="7"/>
-    </row>
-    <row r="2" ht="38.25">
-      <c r="A2" s="6" t="s">
-        <v>250</v>
-      </c>
-      <c r="B2" s="6" t="s">
-        <v>251</v>
-      </c>
-      <c r="C2" s="6" t="s">
-        <v>252</v>
-      </c>
-      <c r="D2" s="6" t="s">
-        <v>253</v>
-      </c>
-      <c r="E2" s="7" t="s">
-        <v>141</v>
-      </c>
-      <c r="F2" s="7"/>
-      <c r="G2" s="7"/>
-      <c r="H2" s="7"/>
-      <c r="I2" s="7"/>
-      <c r="J2" s="7"/>
-      <c r="K2" s="7"/>
-      <c r="L2" s="7"/>
-      <c r="M2" s="7"/>
-      <c r="N2" s="7"/>
-      <c r="O2" s="7"/>
-      <c r="P2" s="7"/>
-      <c r="Q2" s="7"/>
-      <c r="R2" s="7"/>
-      <c r="S2" s="7"/>
-      <c r="T2" s="7"/>
-      <c r="U2" s="7"/>
-      <c r="V2" s="7"/>
-      <c r="W2" s="7"/>
-      <c r="X2" s="7"/>
-      <c r="Y2" s="7"/>
+    <row r="1" ht="14.25">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2" ht="99.75">
+      <c r="A2" s="1" t="s">
+        <v>603</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>544</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>604</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>605</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>606</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>607</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>608</v>
+      </c>
+    </row>
+    <row r="3" ht="71.25">
+      <c r="A3" s="1" t="s">
+        <v>609</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>544</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>610</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>611</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>612</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>606</v>
+      </c>
+      <c r="G3" s="1" t="s">
+        <v>613</v>
+      </c>
+      <c r="H3" s="1" t="s">
+        <v>614</v>
+      </c>
+    </row>
+    <row r="4" ht="57">
+      <c r="A4" s="1" t="s">
+        <v>615</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>544</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>616</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>617</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>618</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>619</v>
+      </c>
+      <c r="G4" s="1" t="s">
+        <v>620</v>
+      </c>
+      <c r="H4" s="1" t="s">
+        <v>621</v>
+      </c>
+    </row>
+    <row r="5" ht="42.75">
+      <c r="A5" s="1" t="s">
+        <v>622</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>623</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>624</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>625</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>626</v>
+      </c>
+      <c r="F5" s="1" t="s">
+        <v>627</v>
+      </c>
+      <c r="G5" s="1" t="s">
+        <v>628</v>
+      </c>
+      <c r="H5" s="1" t="s">
+        <v>629</v>
+      </c>
+      <c r="I5" s="1" t="s">
+        <v>630</v>
+      </c>
+    </row>
+    <row r="6" ht="71.25">
+      <c r="A6" s="1" t="s">
+        <v>631</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>623</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>632</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>633</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>634</v>
+      </c>
+      <c r="F6" s="1" t="s">
+        <v>635</v>
+      </c>
+      <c r="G6" s="1" t="s">
+        <v>636</v>
+      </c>
+    </row>
+    <row r="7" ht="57">
+      <c r="A7" s="1" t="s">
+        <v>637</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>623</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>638</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>639</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>640</v>
+      </c>
+      <c r="F7" s="1" t="s">
+        <v>641</v>
+      </c>
+      <c r="G7" s="1" t="s">
+        <v>642</v>
+      </c>
+      <c r="H7" s="1" t="s">
+        <v>643</v>
+      </c>
+    </row>
+    <row r="8" ht="57">
+      <c r="A8" s="1" t="s">
+        <v>644</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>623</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>645</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>646</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>647</v>
+      </c>
+      <c r="F8" s="1" t="s">
+        <v>648</v>
+      </c>
+      <c r="G8" s="1" t="s">
+        <v>649</v>
+      </c>
+      <c r="H8" s="1" t="s">
+        <v>650</v>
+      </c>
+    </row>
+    <row r="9" ht="114">
+      <c r="A9" s="1" t="s">
+        <v>651</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>652</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>653</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>654</v>
+      </c>
+      <c r="E9" s="1" t="s">
+        <v>655</v>
+      </c>
+      <c r="F9" s="1" t="s">
+        <v>656</v>
+      </c>
+      <c r="G9" s="1" t="s">
+        <v>657</v>
+      </c>
+      <c r="H9" s="1" t="s">
+        <v>658</v>
+      </c>
+      <c r="I9" s="1" t="s">
+        <v>659</v>
+      </c>
+    </row>
+    <row r="10" ht="99.75">
+      <c r="A10" s="1" t="s">
+        <v>660</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>652</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>661</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>662</v>
+      </c>
+      <c r="E10" s="1" t="s">
+        <v>663</v>
+      </c>
+      <c r="F10" s="1" t="s">
+        <v>664</v>
+      </c>
+      <c r="G10" s="1" t="s">
+        <v>665</v>
+      </c>
+      <c r="H10" s="1" t="s">
+        <v>666</v>
+      </c>
+    </row>
+    <row r="11" s="2" customFormat="1" ht="99.75">
+      <c r="A11" s="2" t="s">
+        <v>667</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>652</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>668</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>669</v>
+      </c>
+      <c r="E11" s="2" t="s">
+        <v>670</v>
+      </c>
+      <c r="F11" s="2" t="s">
+        <v>671</v>
+      </c>
+      <c r="G11" s="2" t="s">
+        <v>672</v>
+      </c>
+      <c r="H11" s="2" t="s">
+        <v>673</v>
+      </c>
+    </row>
+    <row r="12" ht="85.5">
+      <c r="A12" s="1" t="s">
+        <v>674</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>652</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>675</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>676</v>
+      </c>
+      <c r="E12" s="1" t="s">
+        <v>677</v>
+      </c>
+      <c r="F12" s="1" t="s">
+        <v>678</v>
+      </c>
+      <c r="G12" s="1" t="s">
+        <v>679</v>
+      </c>
+      <c r="H12" s="1" t="s">
+        <v>680</v>
+      </c>
+    </row>
+    <row r="13" ht="85.5">
+      <c r="A13" s="1" t="s">
+        <v>681</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>652</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>682</v>
+      </c>
+      <c r="D13" s="1" t="s">
+        <v>683</v>
+      </c>
+      <c r="E13" s="1" t="s">
+        <v>684</v>
+      </c>
+      <c r="F13" s="1" t="s">
+        <v>685</v>
+      </c>
+      <c r="G13" s="1" t="s">
+        <v>686</v>
+      </c>
+      <c r="H13" s="1" t="s">
+        <v>687</v>
+      </c>
+    </row>
+    <row r="14" s="5" customFormat="1" ht="42.75">
+      <c r="A14" s="5" t="s">
+        <v>688</v>
+      </c>
+      <c r="B14" s="5" t="s">
+        <v>689</v>
+      </c>
+      <c r="C14" s="5" t="s">
+        <v>690</v>
+      </c>
+      <c r="D14" s="5" t="s">
+        <v>691</v>
+      </c>
+      <c r="E14" s="5" t="s">
+        <v>692</v>
+      </c>
+      <c r="F14" s="5" t="s">
+        <v>693</v>
+      </c>
+      <c r="G14" s="5" t="s">
+        <v>694</v>
+      </c>
+      <c r="I14" s="5" t="s">
+        <v>695</v>
+      </c>
+      <c r="J14" s="6" t="s">
+        <v>696</v>
+      </c>
     </row>
   </sheetData>
   <printOptions headings="0" gridLines="0"/>
@@ -7467,89 +6424,305 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac">
-  <sheetPr>
-    <outlinePr applyStyles="0" summaryBelow="0" summaryRight="0" showOutlineSymbols="1"/>
-    <pageSetUpPr autoPageBreaks="1" fitToPage="0"/>
-  </sheetPr>
-  <sheetFormatPr defaultColWidth="12.630000000000001" defaultRowHeight="15.75" customHeight="1"/>
+  <sheetFormatPr baseColWidth="9" defaultRowHeight="14.25"/>
   <cols>
-    <col customWidth="1" min="1" max="1" width="7.140625"/>
-    <col customWidth="1" min="3" max="3" width="6.8799999999999999"/>
+    <col min="1" max="16384" style="1" width="10.28125"/>
   </cols>
   <sheetData>
-    <row r="1" ht="38.25">
-      <c r="A1" s="6" t="s">
-        <v>246</v>
-      </c>
-      <c r="B1" s="6" t="s">
-        <v>247</v>
-      </c>
-      <c r="C1" s="6" t="s">
-        <v>248</v>
-      </c>
-      <c r="D1" s="6" t="s">
-        <v>249</v>
-      </c>
-      <c r="E1" s="7" t="s">
-        <v>141</v>
-      </c>
-      <c r="F1" s="7"/>
-      <c r="G1" s="7"/>
-      <c r="H1" s="7"/>
-      <c r="I1" s="7"/>
-      <c r="J1" s="7"/>
-      <c r="K1" s="7"/>
-      <c r="L1" s="7"/>
-      <c r="M1" s="7"/>
-      <c r="N1" s="7"/>
-      <c r="O1" s="7"/>
-      <c r="P1" s="7"/>
-      <c r="Q1" s="7"/>
-      <c r="R1" s="7"/>
-      <c r="S1" s="7"/>
-      <c r="T1" s="7"/>
-      <c r="U1" s="7"/>
-      <c r="V1" s="7"/>
-      <c r="W1" s="7"/>
-      <c r="X1" s="7"/>
-      <c r="Y1" s="7"/>
-    </row>
-    <row r="2" ht="38.25">
-      <c r="A2" s="6" t="s">
-        <v>250</v>
-      </c>
-      <c r="B2" s="6" t="s">
-        <v>251</v>
-      </c>
-      <c r="C2" s="6" t="s">
-        <v>252</v>
-      </c>
-      <c r="D2" s="6" t="s">
-        <v>253</v>
-      </c>
-      <c r="E2" s="7" t="s">
-        <v>141</v>
-      </c>
-      <c r="F2" s="7"/>
-      <c r="G2" s="7"/>
-      <c r="H2" s="7"/>
-      <c r="I2" s="7"/>
-      <c r="J2" s="7"/>
-      <c r="K2" s="7"/>
-      <c r="L2" s="7"/>
-      <c r="M2" s="7"/>
-      <c r="N2" s="7"/>
-      <c r="O2" s="7"/>
-      <c r="P2" s="7"/>
-      <c r="Q2" s="7"/>
-      <c r="R2" s="7"/>
-      <c r="S2" s="7"/>
-      <c r="T2" s="7"/>
-      <c r="U2" s="7"/>
-      <c r="V2" s="7"/>
-      <c r="W2" s="7"/>
-      <c r="X2" s="7"/>
-      <c r="Y2" s="7"/>
+    <row r="1">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>697</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2" ht="57">
+      <c r="A2" s="1" t="s">
+        <v>698</v>
+      </c>
+      <c r="B2" s="1">
+        <v>0</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>699</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>700</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>701</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>702</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>703</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>704</v>
+      </c>
+      <c r="I2" s="1" t="s">
+        <v>705</v>
+      </c>
+      <c r="J2" s="1" t="s">
+        <v>706</v>
+      </c>
+    </row>
+    <row r="3" ht="71.25">
+      <c r="A3" s="1" t="s">
+        <v>707</v>
+      </c>
+      <c r="B3" s="1">
+        <v>0</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>708</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>709</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>710</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>711</v>
+      </c>
+      <c r="G3" s="1" t="s">
+        <v>712</v>
+      </c>
+      <c r="H3" s="1" t="s">
+        <v>713</v>
+      </c>
+    </row>
+    <row r="4" ht="57">
+      <c r="A4" s="1" t="s">
+        <v>714</v>
+      </c>
+      <c r="B4" s="1">
+        <v>1</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>715</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>716</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>717</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>718</v>
+      </c>
+      <c r="G4" s="1" t="s">
+        <v>719</v>
+      </c>
+      <c r="H4" s="1" t="s">
+        <v>720</v>
+      </c>
+    </row>
+    <row r="5" ht="42.75">
+      <c r="A5" s="1" t="s">
+        <v>721</v>
+      </c>
+      <c r="B5" s="1">
+        <v>1</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>195</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>722</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>723</v>
+      </c>
+      <c r="F5" s="1" t="s">
+        <v>724</v>
+      </c>
+      <c r="G5" s="1" t="s">
+        <v>725</v>
+      </c>
+      <c r="H5" s="1" t="s">
+        <v>726</v>
+      </c>
+    </row>
+    <row r="6" ht="71.25">
+      <c r="A6" s="1" t="s">
+        <v>727</v>
+      </c>
+      <c r="B6" s="1">
+        <v>2</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>728</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>729</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>730</v>
+      </c>
+      <c r="F6" s="1" t="s">
+        <v>731</v>
+      </c>
+      <c r="G6" s="1" t="s">
+        <v>732</v>
+      </c>
+      <c r="H6" s="1" t="s">
+        <v>733</v>
+      </c>
+    </row>
+    <row r="7" ht="57">
+      <c r="A7" s="1" t="s">
+        <v>734</v>
+      </c>
+      <c r="B7" s="1">
+        <v>2</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>735</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>736</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>737</v>
+      </c>
+      <c r="F7" s="1" t="s">
+        <v>738</v>
+      </c>
+      <c r="G7" s="1" t="s">
+        <v>739</v>
+      </c>
+      <c r="H7" s="1" t="s">
+        <v>740</v>
+      </c>
+    </row>
+    <row r="8" ht="42.75">
+      <c r="A8" s="1" t="s">
+        <v>741</v>
+      </c>
+      <c r="B8" s="1">
+        <v>3</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>742</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>743</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>744</v>
+      </c>
+      <c r="F8" s="1" t="s">
+        <v>745</v>
+      </c>
+      <c r="G8" s="1" t="s">
+        <v>746</v>
+      </c>
+      <c r="H8" s="1" t="s">
+        <v>747</v>
+      </c>
+    </row>
+    <row r="9" ht="42.75">
+      <c r="A9" s="1" t="s">
+        <v>748</v>
+      </c>
+      <c r="B9" s="1">
+        <v>3</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>749</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>750</v>
+      </c>
+      <c r="E9" s="1" t="s">
+        <v>751</v>
+      </c>
+      <c r="F9" s="1" t="s">
+        <v>752</v>
+      </c>
+      <c r="G9" s="1" t="s">
+        <v>753</v>
+      </c>
+      <c r="H9" s="1" t="s">
+        <v>754</v>
+      </c>
+      <c r="I9" s="1" t="s">
+        <v>755</v>
+      </c>
+    </row>
+    <row r="10" ht="57">
+      <c r="A10" s="1" t="s">
+        <v>756</v>
+      </c>
+      <c r="B10" s="1">
+        <v>4</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>757</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>758</v>
+      </c>
+      <c r="E10" s="1" t="s">
+        <v>759</v>
+      </c>
+      <c r="F10" s="1" t="s">
+        <v>760</v>
+      </c>
+      <c r="G10" s="1" t="s">
+        <v>761</v>
+      </c>
+      <c r="H10" s="1" t="s">
+        <v>762</v>
+      </c>
+    </row>
+    <row r="11" ht="57">
+      <c r="A11" s="1" t="s">
+        <v>763</v>
+      </c>
+      <c r="B11" s="1">
+        <v>4</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>764</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>765</v>
+      </c>
+      <c r="E11" s="1" t="s">
+        <v>766</v>
+      </c>
+      <c r="F11" s="1" t="s">
+        <v>767</v>
+      </c>
+      <c r="G11" s="1" t="s">
+        <v>768</v>
+      </c>
+      <c r="H11" s="1" t="s">
+        <v>769</v>
+      </c>
+      <c r="I11" s="1" t="s">
+        <v>770</v>
+      </c>
     </row>
   </sheetData>
   <printOptions headings="0" gridLines="0"/>
@@ -7563,1040 +6736,715 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac">
   <sheetFormatPr baseColWidth="9" defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="3" style="1" width="10.28125"/>
-    <col customWidth="1" min="4" max="4" style="1" width="16.421875"/>
-    <col min="5" max="16384" style="1" width="10.28125"/>
+    <col min="1" max="8" style="1" width="10.28125"/>
+    <col customWidth="1" min="9" max="9" style="1" width="13.7109375"/>
+    <col min="10" max="16384" style="1" width="10.28125"/>
   </cols>
   <sheetData>
     <row r="1" ht="28.5">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
       <c r="B1" s="1" t="s">
-        <v>145</v>
+        <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>146</v>
+        <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>147</v>
+        <v>3</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>148</v>
+        <v>4</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>149</v>
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="2" ht="57">
       <c r="A2" s="1" t="s">
-        <v>150</v>
+        <v>771</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>151</v>
+        <v>772</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>152</v>
+        <v>773</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>153</v>
+        <v>774</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>154</v>
+        <v>775</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>155</v>
+        <v>776</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>777</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>778</v>
+      </c>
+      <c r="I2" s="5" t="s">
+        <v>779</v>
       </c>
     </row>
     <row r="3" ht="57">
       <c r="A3" s="1" t="s">
-        <v>156</v>
+        <v>780</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>151</v>
+        <v>772</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>157</v>
+        <v>781</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>158</v>
+        <v>782</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>159</v>
+        <v>783</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>155</v>
+        <v>784</v>
+      </c>
+      <c r="G3" s="1" t="s">
+        <v>785</v>
+      </c>
+      <c r="H3" s="1" t="s">
+        <v>786</v>
       </c>
     </row>
     <row r="4" ht="57">
       <c r="A4" s="1" t="s">
-        <v>160</v>
+        <v>787</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>161</v>
+        <v>772</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>162</v>
+        <v>788</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>163</v>
+        <v>789</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>164</v>
-      </c>
-      <c r="F4" s="2" t="s">
-        <v>155</v>
+        <v>790</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>791</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>165</v>
+        <v>792</v>
+      </c>
+      <c r="H4" s="1" t="s">
+        <v>793</v>
       </c>
     </row>
     <row r="5" ht="57">
       <c r="A5" s="1" t="s">
-        <v>166</v>
+        <v>794</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>161</v>
+        <v>772</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>167</v>
+        <v>749</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>168</v>
+        <v>795</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>159</v>
+        <v>796</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="6" ht="71.25">
+        <v>797</v>
+      </c>
+      <c r="G5" s="1" t="s">
+        <v>798</v>
+      </c>
+      <c r="H5" s="1" t="s">
+        <v>799</v>
+      </c>
+    </row>
+    <row r="6" ht="42.75">
       <c r="A6" s="1" t="s">
-        <v>170</v>
+        <v>800</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>171</v>
+        <v>772</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>172</v>
+        <v>576</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>173</v>
+        <v>801</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>164</v>
-      </c>
-      <c r="F6" s="2" t="s">
-        <v>155</v>
+        <v>802</v>
+      </c>
+      <c r="F6" s="1" t="s">
+        <v>803</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>174</v>
+        <v>804</v>
+      </c>
+      <c r="H6" s="1" t="s">
+        <v>805</v>
+      </c>
+      <c r="I6" s="1" t="s">
+        <v>806</v>
       </c>
     </row>
     <row r="7" ht="57">
       <c r="A7" s="1" t="s">
-        <v>175</v>
+        <v>807</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>171</v>
+        <v>772</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>176</v>
+        <v>808</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>177</v>
+        <v>809</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>164</v>
+        <v>810</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="8" ht="57">
+        <v>811</v>
+      </c>
+      <c r="G7" s="1" t="s">
+        <v>812</v>
+      </c>
+      <c r="H7" s="1" t="s">
+        <v>813</v>
+      </c>
+    </row>
+    <row r="8" ht="42.75">
       <c r="A8" s="1" t="s">
-        <v>178</v>
+        <v>814</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>179</v>
+        <v>815</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>180</v>
+        <v>749</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>181</v>
+        <v>816</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>159</v>
+        <v>817</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>155</v>
-      </c>
-    </row>
-    <row r="9" ht="42.75">
+        <v>818</v>
+      </c>
+      <c r="G8" s="1" t="s">
+        <v>819</v>
+      </c>
+      <c r="H8" s="1" t="s">
+        <v>820</v>
+      </c>
+    </row>
+    <row r="9" ht="57">
       <c r="A9" s="1" t="s">
-        <v>182</v>
+        <v>821</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>179</v>
+        <v>815</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>183</v>
+        <v>822</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>184</v>
+        <v>823</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>159</v>
+        <v>824</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="10" ht="57">
+        <v>825</v>
+      </c>
+      <c r="G9" s="1" t="s">
+        <v>826</v>
+      </c>
+      <c r="H9" s="1" t="s">
+        <v>827</v>
+      </c>
+    </row>
+    <row r="10" ht="42.75">
       <c r="A10" s="1" t="s">
-        <v>185</v>
+        <v>828</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>186</v>
+        <v>815</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>187</v>
+        <v>829</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>188</v>
+        <v>830</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>164</v>
+        <v>831</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>169</v>
+        <v>832</v>
+      </c>
+      <c r="G10" s="1" t="s">
+        <v>833</v>
+      </c>
+      <c r="H10" s="1" t="s">
+        <v>834</v>
       </c>
     </row>
     <row r="11" ht="57">
       <c r="A11" s="1" t="s">
-        <v>189</v>
+        <v>835</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>186</v>
+        <v>815</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>190</v>
+        <v>836</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>191</v>
+        <v>837</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>164</v>
+        <v>838</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>192</v>
+        <v>839</v>
+      </c>
+      <c r="G11" s="1" t="s">
+        <v>840</v>
+      </c>
+      <c r="H11" s="1" t="s">
+        <v>841</v>
       </c>
     </row>
     <row r="12" ht="57">
       <c r="A12" s="1" t="s">
-        <v>193</v>
+        <v>842</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>194</v>
+        <v>815</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>195</v>
+        <v>843</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>196</v>
+        <v>844</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>159</v>
+        <v>845</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>197</v>
+        <v>846</v>
+      </c>
+      <c r="G12" s="1" t="s">
+        <v>847</v>
+      </c>
+      <c r="H12" s="1" t="s">
+        <v>848</v>
       </c>
     </row>
     <row r="13" ht="57">
       <c r="A13" s="1" t="s">
-        <v>198</v>
+        <v>849</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>194</v>
+        <v>815</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>199</v>
+        <v>850</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>200</v>
+        <v>851</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>159</v>
+        <v>852</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>197</v>
-      </c>
-    </row>
-    <row r="14" ht="57">
+        <v>853</v>
+      </c>
+      <c r="G13" s="1" t="s">
+        <v>854</v>
+      </c>
+      <c r="H13" s="1" t="s">
+        <v>694</v>
+      </c>
+    </row>
+    <row r="14" ht="60">
       <c r="A14" s="1" t="s">
-        <v>201</v>
+        <v>855</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>202</v>
+        <v>856</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>203</v>
+        <v>857</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>204</v>
+        <v>858</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>159</v>
+        <v>859</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="15" ht="42.75">
+        <v>860</v>
+      </c>
+      <c r="G14" s="1" t="s">
+        <v>861</v>
+      </c>
+      <c r="H14" s="1" t="s">
+        <v>862</v>
+      </c>
+      <c r="I14" s="7" t="s">
+        <v>863</v>
+      </c>
+    </row>
+    <row r="15" ht="60">
       <c r="A15" s="1" t="s">
-        <v>205</v>
+        <v>864</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>202</v>
+        <v>856</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>206</v>
+        <v>865</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>207</v>
+        <v>866</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>159</v>
+        <v>867</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="16" ht="57">
+        <v>868</v>
+      </c>
+      <c r="G15" s="1" t="s">
+        <v>869</v>
+      </c>
+      <c r="H15" s="1" t="s">
+        <v>870</v>
+      </c>
+      <c r="I15" s="7" t="s">
+        <v>863</v>
+      </c>
+    </row>
+    <row r="16" ht="60">
       <c r="A16" s="1" t="s">
-        <v>208</v>
+        <v>871</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>209</v>
+        <v>856</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>210</v>
+        <v>872</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>211</v>
+        <v>873</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>164</v>
+        <v>874</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="17" ht="57">
+        <v>875</v>
+      </c>
+      <c r="G16" s="1" t="s">
+        <v>876</v>
+      </c>
+      <c r="H16" s="1" t="s">
+        <v>877</v>
+      </c>
+      <c r="I16" s="7" t="s">
+        <v>863</v>
+      </c>
+    </row>
+    <row r="17" ht="60">
       <c r="A17" s="1" t="s">
-        <v>212</v>
+        <v>878</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>209</v>
+        <v>856</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>213</v>
+        <v>879</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>214</v>
+        <v>880</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>159</v>
+        <v>881</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>192</v>
+        <v>882</v>
+      </c>
+      <c r="G17" s="1" t="s">
+        <v>883</v>
+      </c>
+      <c r="H17" s="1" t="s">
+        <v>884</v>
+      </c>
+      <c r="I17" s="7" t="s">
+        <v>863</v>
       </c>
     </row>
     <row r="18" ht="71.25">
       <c r="A18" s="1" t="s">
-        <v>215</v>
+        <v>885</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>216</v>
+        <v>856</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>217</v>
+        <v>886</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>218</v>
+        <v>887</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>159</v>
-      </c>
-      <c r="F18" s="2" t="s">
-        <v>155</v>
-      </c>
-      <c r="G18" s="2"/>
-    </row>
-    <row r="19" ht="42.75">
+        <v>888</v>
+      </c>
+      <c r="F18" s="1" t="s">
+        <v>889</v>
+      </c>
+      <c r="G18" s="1" t="s">
+        <v>890</v>
+      </c>
+      <c r="H18" s="1" t="s">
+        <v>891</v>
+      </c>
+    </row>
+    <row r="19" ht="71.25">
       <c r="A19" s="1" t="s">
-        <v>219</v>
+        <v>892</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>216</v>
+        <v>856</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>220</v>
+        <v>195</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>221</v>
+        <v>893</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>164</v>
+        <v>894</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="20" ht="57">
+        <v>895</v>
+      </c>
+      <c r="G19" s="1" t="s">
+        <v>896</v>
+      </c>
+      <c r="H19" s="1" t="s">
+        <v>897</v>
+      </c>
+    </row>
+    <row r="20" ht="60">
       <c r="A20" s="1" t="s">
-        <v>222</v>
+        <v>898</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>223</v>
+        <v>856</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>224</v>
+        <v>899</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>225</v>
+        <v>900</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>159</v>
+        <v>901</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="21" ht="57">
+        <v>902</v>
+      </c>
+      <c r="G20" s="1" t="s">
+        <v>903</v>
+      </c>
+      <c r="H20" s="1" t="s">
+        <v>904</v>
+      </c>
+      <c r="I20" s="7" t="s">
+        <v>863</v>
+      </c>
+    </row>
+    <row r="21" ht="60">
       <c r="A21" s="1" t="s">
-        <v>226</v>
+        <v>905</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>227</v>
+        <v>856</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>228</v>
+        <v>906</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>229</v>
+        <v>907</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>159</v>
+        <v>908</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>192</v>
-      </c>
-    </row>
-    <row r="22" ht="71.25">
+        <v>909</v>
+      </c>
+      <c r="G21" s="1" t="s">
+        <v>910</v>
+      </c>
+      <c r="H21" s="1" t="s">
+        <v>911</v>
+      </c>
+      <c r="I21" s="7" t="s">
+        <v>863</v>
+      </c>
+    </row>
+    <row r="22" ht="57">
       <c r="A22" s="1" t="s">
-        <v>230</v>
+        <v>912</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>231</v>
+        <v>583</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>232</v>
+        <v>913</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>233</v>
+        <v>914</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>164</v>
-      </c>
-      <c r="F22" s="2" t="s">
-        <v>234</v>
+        <v>915</v>
+      </c>
+      <c r="F22" s="1" t="s">
+        <v>916</v>
       </c>
       <c r="G22" s="1" t="s">
-        <v>235</v>
-      </c>
-    </row>
-    <row r="23" ht="57">
+        <v>917</v>
+      </c>
+      <c r="H22" s="1" t="s">
+        <v>918</v>
+      </c>
+      <c r="I22" s="1" t="s">
+        <v>919</v>
+      </c>
+    </row>
+    <row r="23" ht="42.75">
       <c r="A23" s="1" t="s">
-        <v>236</v>
+        <v>920</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>231</v>
+        <v>583</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>237</v>
+        <v>921</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>238</v>
+        <v>922</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>159</v>
+        <v>923</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>169</v>
+        <v>924</v>
+      </c>
+      <c r="G23" s="1" t="s">
+        <v>925</v>
+      </c>
+      <c r="H23" s="1" t="s">
+        <v>926</v>
       </c>
     </row>
     <row r="24" ht="57">
       <c r="A24" s="1" t="s">
-        <v>239</v>
+        <v>927</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>240</v>
+        <v>583</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>241</v>
+        <v>928</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>242</v>
+        <v>929</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>159</v>
+        <v>930</v>
       </c>
       <c r="F24" s="1" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="25" ht="42.75">
+        <v>931</v>
+      </c>
+      <c r="G24" s="1" t="s">
+        <v>932</v>
+      </c>
+      <c r="H24" s="1" t="s">
+        <v>933</v>
+      </c>
+      <c r="I24" s="1" t="s">
+        <v>934</v>
+      </c>
+    </row>
+    <row r="25" ht="57">
       <c r="A25" s="1" t="s">
-        <v>243</v>
+        <v>935</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>240</v>
+        <v>583</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>244</v>
+        <v>936</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>245</v>
+        <v>937</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>164</v>
+        <v>938</v>
       </c>
       <c r="F25" s="1" t="s">
-        <v>192</v>
-      </c>
-    </row>
-  </sheetData>
-  <printOptions headings="0" gridLines="0"/>
-  <pageMargins left="0.70078740157480324" right="0.70078740157480324" top="0.75196850393700787" bottom="0.75196850393700787" header="0.29999999999999999" footer="0.29999999999999999"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" cellComments="none" useFirstPageNumber="0" errors="displayed" horizontalDpi="600" verticalDpi="600" copies="1"/>
-  <headerFooter/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac">
-  <sheetFormatPr baseColWidth="9" defaultRowHeight="14.25"/>
-  <cols>
-    <col min="1" max="3" style="1" width="10.28125"/>
-    <col customWidth="1" min="4" max="4" style="1" width="16.421875"/>
-    <col min="5" max="16384" style="1" width="10.28125"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="28.5">
-      <c r="B1" s="1" t="s">
-        <v>145</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>146</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>147</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>148</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="2" ht="57">
-      <c r="A2" s="1" t="s">
-        <v>150</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>151</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>152</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="E2" s="1" t="s">
-        <v>154</v>
-      </c>
-      <c r="F2" s="1" t="s">
-        <v>155</v>
-      </c>
-    </row>
-    <row r="3" ht="57">
-      <c r="A3" s="1" t="s">
-        <v>156</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>151</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>157</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>158</v>
-      </c>
-      <c r="E3" s="1" t="s">
-        <v>159</v>
-      </c>
-      <c r="F3" s="1" t="s">
-        <v>155</v>
-      </c>
-    </row>
-    <row r="4" ht="57">
-      <c r="A4" s="1" t="s">
-        <v>160</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>161</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>162</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>163</v>
-      </c>
-      <c r="E4" s="1" t="s">
-        <v>164</v>
-      </c>
-      <c r="F4" s="2" t="s">
-        <v>155</v>
-      </c>
-      <c r="G4" s="1" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="5" ht="57">
-      <c r="A5" s="1" t="s">
-        <v>166</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>161</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>167</v>
-      </c>
-      <c r="D5" s="1" t="s">
-        <v>168</v>
-      </c>
-      <c r="E5" s="1" t="s">
-        <v>159</v>
-      </c>
-      <c r="F5" s="1" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="6" ht="71.25">
-      <c r="A6" s="1" t="s">
-        <v>170</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>171</v>
-      </c>
-      <c r="C6" s="1" t="s">
-        <v>172</v>
-      </c>
-      <c r="D6" s="1" t="s">
-        <v>173</v>
-      </c>
-      <c r="E6" s="1" t="s">
-        <v>164</v>
-      </c>
-      <c r="F6" s="2" t="s">
-        <v>155</v>
-      </c>
-      <c r="G6" s="1" t="s">
-        <v>174</v>
-      </c>
-    </row>
-    <row r="7" ht="57">
-      <c r="A7" s="1" t="s">
-        <v>175</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>171</v>
-      </c>
-      <c r="C7" s="1" t="s">
-        <v>176</v>
-      </c>
-      <c r="D7" s="1" t="s">
-        <v>177</v>
-      </c>
-      <c r="E7" s="1" t="s">
-        <v>164</v>
-      </c>
-      <c r="F7" s="1" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="8" ht="57">
-      <c r="A8" s="1" t="s">
-        <v>178</v>
-      </c>
-      <c r="B8" s="1" t="s">
-        <v>179</v>
-      </c>
-      <c r="C8" s="1" t="s">
-        <v>180</v>
-      </c>
-      <c r="D8" s="1" t="s">
-        <v>181</v>
-      </c>
-      <c r="E8" s="1" t="s">
-        <v>159</v>
-      </c>
-      <c r="F8" s="1" t="s">
-        <v>155</v>
-      </c>
-    </row>
-    <row r="9" ht="42.75">
-      <c r="A9" s="1" t="s">
-        <v>182</v>
-      </c>
-      <c r="B9" s="1" t="s">
-        <v>179</v>
-      </c>
-      <c r="C9" s="1" t="s">
-        <v>183</v>
-      </c>
-      <c r="D9" s="1" t="s">
-        <v>184</v>
-      </c>
-      <c r="E9" s="1" t="s">
-        <v>159</v>
-      </c>
-      <c r="F9" s="1" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="10" ht="57">
-      <c r="A10" s="1" t="s">
-        <v>185</v>
-      </c>
-      <c r="B10" s="1" t="s">
-        <v>186</v>
-      </c>
-      <c r="C10" s="1" t="s">
-        <v>187</v>
-      </c>
-      <c r="D10" s="1" t="s">
-        <v>188</v>
-      </c>
-      <c r="E10" s="1" t="s">
-        <v>164</v>
-      </c>
-      <c r="F10" s="1" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="11" ht="57">
-      <c r="A11" s="1" t="s">
-        <v>189</v>
-      </c>
-      <c r="B11" s="1" t="s">
-        <v>186</v>
-      </c>
-      <c r="C11" s="1" t="s">
-        <v>190</v>
-      </c>
-      <c r="D11" s="1" t="s">
-        <v>191</v>
-      </c>
-      <c r="E11" s="1" t="s">
-        <v>164</v>
-      </c>
-      <c r="F11" s="1" t="s">
-        <v>192</v>
-      </c>
-    </row>
-    <row r="12" ht="57">
-      <c r="A12" s="1" t="s">
-        <v>193</v>
-      </c>
-      <c r="B12" s="1" t="s">
-        <v>194</v>
-      </c>
-      <c r="C12" s="1" t="s">
-        <v>195</v>
-      </c>
-      <c r="D12" s="1" t="s">
-        <v>196</v>
-      </c>
-      <c r="E12" s="1" t="s">
-        <v>159</v>
-      </c>
-      <c r="F12" s="1" t="s">
-        <v>197</v>
-      </c>
-    </row>
-    <row r="13" ht="57">
-      <c r="A13" s="1" t="s">
-        <v>198</v>
-      </c>
-      <c r="B13" s="1" t="s">
-        <v>194</v>
-      </c>
-      <c r="C13" s="1" t="s">
-        <v>199</v>
-      </c>
-      <c r="D13" s="1" t="s">
-        <v>200</v>
-      </c>
-      <c r="E13" s="1" t="s">
-        <v>159</v>
-      </c>
-      <c r="F13" s="1" t="s">
-        <v>197</v>
-      </c>
-    </row>
-    <row r="14" ht="57">
-      <c r="A14" s="1" t="s">
-        <v>201</v>
-      </c>
-      <c r="B14" s="1" t="s">
-        <v>202</v>
-      </c>
-      <c r="C14" s="1" t="s">
-        <v>203</v>
-      </c>
-      <c r="D14" s="1" t="s">
-        <v>204</v>
-      </c>
-      <c r="E14" s="1" t="s">
-        <v>159</v>
-      </c>
-      <c r="F14" s="1" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="15" ht="42.75">
-      <c r="A15" s="1" t="s">
-        <v>205</v>
-      </c>
-      <c r="B15" s="1" t="s">
-        <v>202</v>
-      </c>
-      <c r="C15" s="1" t="s">
-        <v>206</v>
-      </c>
-      <c r="D15" s="1" t="s">
-        <v>207</v>
-      </c>
-      <c r="E15" s="1" t="s">
-        <v>159</v>
-      </c>
-      <c r="F15" s="1" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="16" ht="57">
-      <c r="A16" s="1" t="s">
-        <v>208</v>
-      </c>
-      <c r="B16" s="1" t="s">
-        <v>209</v>
-      </c>
-      <c r="C16" s="1" t="s">
-        <v>210</v>
-      </c>
-      <c r="D16" s="1" t="s">
-        <v>211</v>
-      </c>
-      <c r="E16" s="1" t="s">
-        <v>164</v>
-      </c>
-      <c r="F16" s="1" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="17" ht="57">
-      <c r="A17" s="1" t="s">
-        <v>212</v>
-      </c>
-      <c r="B17" s="1" t="s">
-        <v>209</v>
-      </c>
-      <c r="C17" s="1" t="s">
-        <v>213</v>
-      </c>
-      <c r="D17" s="1" t="s">
-        <v>214</v>
-      </c>
-      <c r="E17" s="1" t="s">
-        <v>159</v>
-      </c>
-      <c r="F17" s="1" t="s">
-        <v>192</v>
-      </c>
-    </row>
-    <row r="18" ht="71.25">
-      <c r="A18" s="1" t="s">
-        <v>215</v>
-      </c>
-      <c r="B18" s="1" t="s">
-        <v>216</v>
-      </c>
-      <c r="C18" s="1" t="s">
-        <v>217</v>
-      </c>
-      <c r="D18" s="1" t="s">
-        <v>218</v>
-      </c>
-      <c r="E18" s="1" t="s">
-        <v>159</v>
-      </c>
-      <c r="F18" s="2" t="s">
-        <v>155</v>
-      </c>
-      <c r="G18" s="2"/>
-    </row>
-    <row r="19" ht="42.75">
-      <c r="A19" s="1" t="s">
-        <v>219</v>
-      </c>
-      <c r="B19" s="1" t="s">
-        <v>216</v>
-      </c>
-      <c r="C19" s="1" t="s">
-        <v>220</v>
-      </c>
-      <c r="D19" s="1" t="s">
-        <v>221</v>
-      </c>
-      <c r="E19" s="1" t="s">
-        <v>164</v>
-      </c>
-      <c r="F19" s="1" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="20" ht="57">
-      <c r="A20" s="1" t="s">
-        <v>222</v>
-      </c>
-      <c r="B20" s="1" t="s">
-        <v>223</v>
-      </c>
-      <c r="C20" s="1" t="s">
-        <v>224</v>
-      </c>
-      <c r="D20" s="1" t="s">
-        <v>225</v>
-      </c>
-      <c r="E20" s="1" t="s">
-        <v>159</v>
-      </c>
-      <c r="F20" s="1" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="21" ht="57">
-      <c r="A21" s="1" t="s">
-        <v>226</v>
-      </c>
-      <c r="B21" s="1" t="s">
-        <v>227</v>
-      </c>
-      <c r="C21" s="1" t="s">
-        <v>228</v>
-      </c>
-      <c r="D21" s="1" t="s">
-        <v>229</v>
-      </c>
-      <c r="E21" s="1" t="s">
-        <v>159</v>
-      </c>
-      <c r="F21" s="1" t="s">
-        <v>192</v>
-      </c>
-    </row>
-    <row r="22" ht="71.25">
-      <c r="A22" s="1" t="s">
-        <v>230</v>
-      </c>
-      <c r="B22" s="1" t="s">
-        <v>231</v>
-      </c>
-      <c r="C22" s="1" t="s">
-        <v>232</v>
-      </c>
-      <c r="D22" s="1" t="s">
-        <v>233</v>
-      </c>
-      <c r="E22" s="1" t="s">
-        <v>164</v>
-      </c>
-      <c r="F22" s="2" t="s">
-        <v>234</v>
-      </c>
-      <c r="G22" s="1" t="s">
-        <v>235</v>
-      </c>
-    </row>
-    <row r="23" ht="57">
-      <c r="A23" s="1" t="s">
-        <v>236</v>
-      </c>
-      <c r="B23" s="1" t="s">
-        <v>231</v>
-      </c>
-      <c r="C23" s="1" t="s">
-        <v>237</v>
-      </c>
-      <c r="D23" s="1" t="s">
-        <v>238</v>
-      </c>
-      <c r="E23" s="1" t="s">
-        <v>159</v>
-      </c>
-      <c r="F23" s="1" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="24" ht="57">
-      <c r="A24" s="1" t="s">
-        <v>239</v>
-      </c>
-      <c r="B24" s="1" t="s">
-        <v>240</v>
-      </c>
-      <c r="C24" s="1" t="s">
-        <v>241</v>
-      </c>
-      <c r="D24" s="1" t="s">
-        <v>242</v>
-      </c>
-      <c r="E24" s="1" t="s">
-        <v>159</v>
-      </c>
-      <c r="F24" s="1" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="25" ht="42.75">
-      <c r="A25" s="1" t="s">
-        <v>243</v>
-      </c>
-      <c r="B25" s="1" t="s">
-        <v>240</v>
-      </c>
-      <c r="C25" s="1" t="s">
-        <v>244</v>
-      </c>
-      <c r="D25" s="1" t="s">
-        <v>245</v>
-      </c>
-      <c r="E25" s="1" t="s">
-        <v>164</v>
-      </c>
-      <c r="F25" s="1" t="s">
-        <v>192</v>
+        <v>939</v>
+      </c>
+      <c r="G25" s="1" t="s">
+        <v>940</v>
+      </c>
+      <c r="H25" s="1" t="s">
+        <v>941</v>
+      </c>
+    </row>
+    <row r="26" ht="57">
+      <c r="A26" s="1" t="s">
+        <v>942</v>
+      </c>
+      <c r="B26" s="1" t="s">
+        <v>583</v>
+      </c>
+      <c r="C26" s="1" t="s">
+        <v>943</v>
+      </c>
+      <c r="D26" s="1" t="s">
+        <v>944</v>
+      </c>
+      <c r="E26" s="1" t="s">
+        <v>945</v>
+      </c>
+      <c r="F26" s="1" t="s">
+        <v>946</v>
+      </c>
+      <c r="G26" s="1" t="s">
+        <v>947</v>
+      </c>
+      <c r="H26" s="1" t="s">
+        <v>948</v>
       </c>
     </row>
   </sheetData>
